--- a/dados/Produtos_Agrupados_Completos_conciliados.xlsx
+++ b/dados/Produtos_Agrupados_Completos_conciliados.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Documents\AREA DE TRABALHO - MEDTEXTIL\CRM_APP\dados\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25603DAA-76F2-4F24-B5BB-1B38DE617100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73F97D86-7939-4962-9B45-D7BEB08E161E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{86B17377-32DB-438B-8A03-02E761646E6D}"/>
   </bookViews>
@@ -17,9 +17,9 @@
     <sheet name="Tabela de preços" sheetId="4" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="DadosExternos_1" localSheetId="0" hidden="1">CONCILIADA!$A$1:$G$364</definedName>
+    <definedName name="DadosExternos_1" localSheetId="0" hidden="1">CONCILIADA!$A$1:$G$365</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateCount="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2548" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2552" uniqueCount="444">
   <si>
     <t>Grupo</t>
   </si>
@@ -1377,6 +1377,12 @@
   </si>
   <si>
     <t>PRECO</t>
+  </si>
+  <si>
+    <t>TECIDO DE ALGODAO ALVEJADO 11 FIOS</t>
+  </si>
+  <si>
+    <t>Ultratextil</t>
   </si>
 </sst>
 </file>
@@ -1430,7 +1436,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -1440,6 +1446,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -1489,8 +1496,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5499586E-A189-44D8-9C58-8F69F4EC7CA4}" name="Tabela14" displayName="Tabela14" ref="A1:H364" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:H364" xr:uid="{5499586E-A189-44D8-9C58-8F69F4EC7CA4}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5499586E-A189-44D8-9C58-8F69F4EC7CA4}" name="Tabela14" displayName="Tabela14" ref="A1:H365" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:H365" xr:uid="{5499586E-A189-44D8-9C58-8F69F4EC7CA4}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{5387F357-AA02-4B91-B30F-AB45B122F19D}" uniqueName="1" name="Grupo" queryTableFieldId="1" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{3202AFED-4A11-4AD5-8FCF-B57F6545F53A}" uniqueName="2" name="ID_COD" queryTableFieldId="2"/>
@@ -1819,10 +1826,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{868BC1FE-16FA-4E4B-B34E-F84713378B87}">
-  <dimension ref="A1:H364"/>
+  <dimension ref="A1:H365"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.5703125" bestFit="1" customWidth="1"/>
@@ -11021,6 +11028,26 @@
       </c>
       <c r="H364" s="2" t="e">
         <v>#N/A</v>
+      </c>
+    </row>
+    <row r="365" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A365" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="B365">
+        <v>495</v>
+      </c>
+      <c r="C365" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="D365" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="G365" t="s">
+        <v>442</v>
+      </c>
+      <c r="H365" s="2">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/dados/Produtos_Agrupados_Completos_conciliados.xlsx
+++ b/dados/Produtos_Agrupados_Completos_conciliados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73F97D86-7939-4962-9B45-D7BEB08E161E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6CC61D4-1E7D-4F72-A519-7104F36F8068}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{86B17377-32DB-438B-8A03-02E761646E6D}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Tabela de preços" sheetId="4" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="DadosExternos_1" localSheetId="0" hidden="1">CONCILIADA!$A$1:$G$365</definedName>
+    <definedName name="DadosExternos_1" localSheetId="0" hidden="1">CONCILIADA!$A$1:$G$371</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2552" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2576" uniqueCount="445">
   <si>
     <t>Grupo</t>
   </si>
@@ -1382,7 +1382,10 @@
     <t>TECIDO DE ALGODAO ALVEJADO 11 FIOS</t>
   </si>
   <si>
-    <t>Ultratextil</t>
+    <t xml:space="preserve">GAZE NAO ESTERIL 13 FIOS </t>
+  </si>
+  <si>
+    <t>CAMPO OPERATORIO NAO ESTERIL 45X50 S/ RX - PCT 50 UND</t>
   </si>
 </sst>
 </file>
@@ -1496,8 +1499,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5499586E-A189-44D8-9C58-8F69F4EC7CA4}" name="Tabela14" displayName="Tabela14" ref="A1:H365" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:H365" xr:uid="{5499586E-A189-44D8-9C58-8F69F4EC7CA4}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5499586E-A189-44D8-9C58-8F69F4EC7CA4}" name="Tabela14" displayName="Tabela14" ref="A1:H371" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:H371" xr:uid="{5499586E-A189-44D8-9C58-8F69F4EC7CA4}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{5387F357-AA02-4B91-B30F-AB45B122F19D}" uniqueName="1" name="Grupo" queryTableFieldId="1" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{3202AFED-4A11-4AD5-8FCF-B57F6545F53A}" uniqueName="2" name="ID_COD" queryTableFieldId="2"/>
@@ -1826,10 +1829,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{868BC1FE-16FA-4E4B-B34E-F84713378B87}">
-  <dimension ref="A1:H365"/>
+  <dimension ref="A1:H371"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="55.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.5703125" bestFit="1" customWidth="1"/>
@@ -11041,13 +11044,151 @@
         <v>442</v>
       </c>
       <c r="D365" s="7" t="s">
-        <v>443</v>
+        <v>8</v>
       </c>
       <c r="G365" t="s">
         <v>442</v>
       </c>
       <c r="H365" s="2">
         <v>40</v>
+      </c>
+    </row>
+    <row r="366" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A366" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="B366">
+        <v>2019</v>
+      </c>
+      <c r="C366" t="s">
+        <v>21</v>
+      </c>
+      <c r="D366" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E366">
+        <v>350</v>
+      </c>
+      <c r="F366">
+        <v>1000</v>
+      </c>
+      <c r="G366" t="s">
+        <v>260</v>
+      </c>
+      <c r="H366" s="2">
+        <v>22.79</v>
+      </c>
+    </row>
+    <row r="367" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A367" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="B367">
+        <v>1819</v>
+      </c>
+      <c r="C367" t="s">
+        <v>27</v>
+      </c>
+      <c r="D367" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E367">
+        <v>210</v>
+      </c>
+      <c r="G367" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="H367" s="2">
+        <v>16.87</v>
+      </c>
+    </row>
+    <row r="368" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A368" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="B368">
+        <v>2011</v>
+      </c>
+      <c r="C368" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D368" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E368">
+        <v>900</v>
+      </c>
+      <c r="G368" t="s">
+        <v>229</v>
+      </c>
+      <c r="H368" s="2">
+        <v>58.6</v>
+      </c>
+    </row>
+    <row r="369" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A369" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="B369">
+        <v>2010</v>
+      </c>
+      <c r="C369" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D369" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E369">
+        <v>320</v>
+      </c>
+      <c r="G369" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="H369" s="2">
+        <v>25.71</v>
+      </c>
+    </row>
+    <row r="370" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A370" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="B370">
+        <v>1822</v>
+      </c>
+      <c r="C370" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D370" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E370">
+        <v>380</v>
+      </c>
+      <c r="G370" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="H370" s="2">
+        <v>24.51</v>
+      </c>
+    </row>
+    <row r="371" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A371" s="7" t="s">
+        <v>444</v>
+      </c>
+      <c r="B371">
+        <v>1797</v>
+      </c>
+      <c r="C371" t="s">
+        <v>14</v>
+      </c>
+      <c r="D371" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="G371" s="7" t="s">
+        <v>444</v>
+      </c>
+      <c r="H371" s="2">
+        <v>48.5</v>
       </c>
     </row>
   </sheetData>

--- a/dados/Produtos_Agrupados_Completos_conciliados.xlsx
+++ b/dados/Produtos_Agrupados_Completos_conciliados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{668C54E9-E84C-45B8-8A4D-4F094F53B8D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B85C097-CBAA-4AA0-99A2-11D81725F69E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{86B17377-32DB-438B-8A03-02E761646E6D}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="DadosExternos_1" localSheetId="0" hidden="1">CONCILIADA!$A$1:$G$371</definedName>
+    <definedName name="DadosExternos_1" localSheetId="0" hidden="1">CONCILIADA!$A$1:$G$374</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3068" uniqueCount="649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3080" uniqueCount="649">
   <si>
     <t>Grupo</t>
   </si>
@@ -2457,8 +2457,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5499586E-A189-44D8-9C58-8F69F4EC7CA4}" name="Tabela14" displayName="Tabela14" ref="A1:H371" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:H371" xr:uid="{5499586E-A189-44D8-9C58-8F69F4EC7CA4}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5499586E-A189-44D8-9C58-8F69F4EC7CA4}" name="Tabela14" displayName="Tabela14" ref="A1:H374" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:H374" xr:uid="{5499586E-A189-44D8-9C58-8F69F4EC7CA4}"/>
   <tableColumns count="8">
     <tableColumn id="2" xr3:uid="{3202AFED-4A11-4AD5-8FCF-B57F6545F53A}" uniqueName="2" name="ID_COD" queryTableFieldId="2" dataDxfId="15"/>
     <tableColumn id="1" xr3:uid="{5387F357-AA02-4B91-B30F-AB45B122F19D}" uniqueName="1" name="Grupo" queryTableFieldId="1" dataDxfId="14"/>
@@ -2803,7 +2803,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{868BC1FE-16FA-4E4B-B34E-F84713378B87}">
-  <dimension ref="A1:H371"/>
+  <dimension ref="A1:H374"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -2813,7 +2813,7 @@
     <col min="5" max="5" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="55.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6464,8 +6464,8 @@
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A136">
-        <v>1775</v>
+      <c r="A136" s="7">
+        <v>1960</v>
       </c>
       <c r="B136" t="s">
         <v>21</v>
@@ -6476,23 +6476,22 @@
       <c r="D136" t="s">
         <v>9</v>
       </c>
-      <c r="E136" s="1" t="s">
-        <v>335</v>
+      <c r="E136" s="3">
+        <v>1460</v>
       </c>
       <c r="F136">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G136" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H136" s="2">
-        <v>32.075675675675676</v>
+        <v>94.88</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="B137" t="s">
         <v>21</v>
@@ -6504,22 +6503,22 @@
         <v>9</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F137">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>0</v>
       </c>
       <c r="G137" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="H137" s="2">
-        <v>32.877567567567567</v>
+        <v>32.075675675675676</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="B138" t="s">
         <v>21</v>
@@ -6531,49 +6530,49 @@
         <v>9</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>141</v>
+        <v>336</v>
       </c>
       <c r="F138">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>0</v>
       </c>
       <c r="G138" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H138" s="2">
-        <v>33.679459459459466</v>
+        <v>32.877567567567567</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>357</v>
+        <v>1777</v>
       </c>
       <c r="B139" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C139" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D139" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>326</v>
+        <v>141</v>
       </c>
       <c r="F139">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G139" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="H139" s="2">
-        <v>15.8424</v>
+        <v>33.679459459459466</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B140" t="s">
         <v>23</v>
@@ -6585,22 +6584,22 @@
         <v>4</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F140">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G140" t="s">
         <v>207</v>
       </c>
       <c r="H140" s="2">
-        <v>16.596799999999998</v>
+        <v>15.8424</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>261</v>
+        <v>358</v>
       </c>
       <c r="B141" t="s">
         <v>23</v>
@@ -6612,22 +6611,22 @@
         <v>4</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F141">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>0</v>
       </c>
       <c r="G141" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H141" s="2">
-        <v>17.351200000000002</v>
+        <v>16.596799999999998</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B142" t="s">
         <v>23</v>
@@ -6639,22 +6638,22 @@
         <v>4</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F142">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>0</v>
       </c>
       <c r="G142" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H142" s="2">
-        <v>18.105599999999999</v>
+        <v>17.351200000000002</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B143" t="s">
         <v>23</v>
@@ -6666,22 +6665,22 @@
         <v>4</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F143">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G143" t="s">
         <v>207</v>
       </c>
       <c r="H143" s="2">
-        <v>18.86</v>
+        <v>18.105599999999999</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B144" t="s">
         <v>23</v>
@@ -6693,22 +6692,22 @@
         <v>4</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>262</v>
+        <v>330</v>
       </c>
       <c r="F144">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G144" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="H144" s="2">
-        <v>19.614399999999996</v>
+        <v>18.86</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B145" t="s">
         <v>23</v>
@@ -6720,22 +6719,22 @@
         <v>4</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>222</v>
+        <v>262</v>
       </c>
       <c r="F145">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G145" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="H145" s="2">
-        <v>20.3688</v>
+        <v>19.614399999999996</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B146" t="s">
         <v>23</v>
@@ -6747,22 +6746,22 @@
         <v>4</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
       <c r="F146">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G146" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="H146" s="2">
-        <v>21.123200000000001</v>
+        <v>20.3688</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B147" t="s">
         <v>23</v>
@@ -6774,22 +6773,22 @@
         <v>4</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>180</v>
+        <v>243</v>
       </c>
       <c r="F147">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G147" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="H147" s="2">
-        <v>21.877599999999997</v>
+        <v>21.123200000000001</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B148" t="s">
         <v>23</v>
@@ -6801,22 +6800,22 @@
         <v>4</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>233</v>
+        <v>180</v>
       </c>
       <c r="F148">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>0</v>
       </c>
       <c r="G148" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H148" s="2">
-        <v>22.632000000000001</v>
+        <v>21.877599999999997</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B149" t="s">
         <v>23</v>
@@ -6828,22 +6827,22 @@
         <v>4</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>281</v>
+        <v>233</v>
       </c>
       <c r="F149">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>0</v>
       </c>
       <c r="G149" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H149" s="2">
-        <v>23.386399999999998</v>
+        <v>22.632000000000001</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B150" t="s">
         <v>23</v>
@@ -6855,22 +6854,22 @@
         <v>4</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F150">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>0</v>
       </c>
       <c r="G150" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="H150" s="2">
-        <v>23.7636</v>
+        <v>23.386399999999998</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B151" t="s">
         <v>23</v>
@@ -6882,22 +6881,22 @@
         <v>4</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="F151">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>0</v>
       </c>
       <c r="G151" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="H151" s="2">
-        <v>24.140799999999999</v>
+        <v>23.7636</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B152" t="s">
         <v>23</v>
@@ -6909,22 +6908,22 @@
         <v>4</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>316</v>
+        <v>299</v>
       </c>
       <c r="F152">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>0</v>
       </c>
       <c r="G152" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H152" s="2">
-        <v>24.895199999999999</v>
+        <v>24.140799999999999</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153">
-        <v>1687</v>
+        <v>272</v>
       </c>
       <c r="B153" t="s">
         <v>23</v>
@@ -6933,25 +6932,25 @@
         <v>24</v>
       </c>
       <c r="D153" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>329</v>
+        <v>316</v>
       </c>
       <c r="F153">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>0</v>
       </c>
       <c r="G153" t="s">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="H153" s="2">
-        <v>19.313684210526315</v>
+        <v>24.895199999999999</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154">
-        <v>290</v>
+        <v>1687</v>
       </c>
       <c r="B154" t="s">
         <v>23</v>
@@ -6963,22 +6962,22 @@
         <v>8</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>285</v>
+        <v>329</v>
       </c>
       <c r="F154">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>0</v>
       </c>
       <c r="G154" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
       <c r="H154" s="2">
-        <v>27.361052631578943</v>
+        <v>19.313684210526315</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B155" t="s">
         <v>23</v>
@@ -6990,22 +6989,22 @@
         <v>8</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>302</v>
+        <v>285</v>
       </c>
       <c r="F155">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>0</v>
       </c>
       <c r="G155" t="s">
-        <v>212</v>
+        <v>181</v>
       </c>
       <c r="H155" s="2">
-        <v>28.16578947368421</v>
+        <v>27.361052631578943</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B156" t="s">
         <v>23</v>
@@ -7017,22 +7016,22 @@
         <v>8</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>331</v>
+        <v>302</v>
       </c>
       <c r="F156">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>0</v>
       </c>
       <c r="G156" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H156" s="2">
-        <v>28.970526315789471</v>
+        <v>28.16578947368421</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B157" t="s">
         <v>23</v>
@@ -7044,22 +7043,22 @@
         <v>8</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F157">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>0</v>
       </c>
       <c r="G157" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="H157" s="2">
-        <v>29.775263157894734</v>
+        <v>28.970526315789471</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B158" t="s">
         <v>23</v>
@@ -7071,22 +7070,22 @@
         <v>8</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F158">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>0</v>
       </c>
       <c r="G158" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="H158" s="2">
-        <v>30.58</v>
+        <v>29.775263157894734</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B159" t="s">
         <v>23</v>
@@ -7098,22 +7097,22 @@
         <v>8</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F159">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>0</v>
       </c>
       <c r="G159" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="H159" s="2">
-        <v>31.384736842105259</v>
+        <v>30.58</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B160" t="s">
         <v>23</v>
@@ -7125,22 +7124,22 @@
         <v>8</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F160">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G160" t="s">
-        <v>186</v>
+        <v>217</v>
       </c>
       <c r="H160" s="2">
-        <v>32.189473684210526</v>
+        <v>31.384736842105259</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161">
-        <v>1778</v>
+        <v>296</v>
       </c>
       <c r="B161" t="s">
         <v>23</v>
@@ -7149,25 +7148,25 @@
         <v>24</v>
       </c>
       <c r="D161" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>335</v>
       </c>
       <c r="F161">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G161" t="s">
-        <v>207</v>
-      </c>
-      <c r="H161" s="2" t="e">
-        <v>#N/A</v>
+        <v>186</v>
+      </c>
+      <c r="H161" s="2">
+        <v>32.189473684210526</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A162">
-        <v>1779</v>
+      <c r="A162" s="7">
+        <v>1961</v>
       </c>
       <c r="B162" t="s">
         <v>23</v>
@@ -7175,26 +7174,25 @@
       <c r="C162" t="s">
         <v>24</v>
       </c>
-      <c r="D162" t="s">
-        <v>9</v>
-      </c>
-      <c r="E162" s="1" t="s">
-        <v>336</v>
+      <c r="D162" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="E162" s="3">
+        <v>1530</v>
       </c>
       <c r="F162">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G162" t="s">
-        <v>210</v>
-      </c>
-      <c r="H162" s="2" t="e">
-        <v>#N/A</v>
+        <v>207</v>
+      </c>
+      <c r="H162" s="2">
+        <v>98.7</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163">
-        <v>1780</v>
+        <v>1778</v>
       </c>
       <c r="B163" t="s">
         <v>23</v>
@@ -7206,14 +7204,14 @@
         <v>9</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>141</v>
+        <v>335</v>
       </c>
       <c r="F163">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>0</v>
       </c>
       <c r="G163" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="H163" s="2" t="e">
         <v>#N/A</v>
@@ -7221,61 +7219,61 @@
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164">
-        <v>359</v>
+        <v>1779</v>
       </c>
       <c r="B164" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C164" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D164" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="F164">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G164" t="s">
-        <v>227</v>
-      </c>
-      <c r="H164" s="2">
-        <v>15.8</v>
+        <v>210</v>
+      </c>
+      <c r="H164" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165">
-        <v>273</v>
+        <v>1780</v>
       </c>
       <c r="B165" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C165" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D165" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>326</v>
+        <v>141</v>
       </c>
       <c r="F165">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G165" t="s">
-        <v>182</v>
-      </c>
-      <c r="H165" s="2">
-        <v>16.59</v>
+        <v>211</v>
+      </c>
+      <c r="H165" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166">
-        <v>274</v>
+        <v>359</v>
       </c>
       <c r="B166" t="s">
         <v>25</v>
@@ -7287,22 +7285,22 @@
         <v>4</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="F166">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G166" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H166" s="2">
-        <v>17.38</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B167" t="s">
         <v>25</v>
@@ -7314,22 +7312,22 @@
         <v>4</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="F167">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G167" t="s">
-        <v>228</v>
+        <v>182</v>
       </c>
       <c r="H167" s="2">
-        <v>18.170000000000002</v>
+        <v>16.59</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B168" t="s">
         <v>25</v>
@@ -7341,22 +7339,22 @@
         <v>4</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F168">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G168" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H168" s="2">
-        <v>18.959999999999997</v>
+        <v>17.38</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B169" t="s">
         <v>25</v>
@@ -7368,22 +7366,22 @@
         <v>4</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F169">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G169" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="H169" s="2">
-        <v>19.75</v>
+        <v>18.170000000000002</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B170" t="s">
         <v>25</v>
@@ -7395,22 +7393,22 @@
         <v>4</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>262</v>
+        <v>329</v>
       </c>
       <c r="F170">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G170" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="H170" s="2">
-        <v>20.54</v>
+        <v>18.959999999999997</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B171" t="s">
         <v>25</v>
@@ -7422,22 +7420,22 @@
         <v>4</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>222</v>
+        <v>330</v>
       </c>
       <c r="F171">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>30</v>
       </c>
       <c r="G171" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="H171" s="2">
-        <v>19.88</v>
+        <v>19.75</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B172" t="s">
         <v>25</v>
@@ -7449,22 +7447,22 @@
         <v>4</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>243</v>
+        <v>262</v>
       </c>
       <c r="F172">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G172" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="H172" s="2">
-        <v>22.12</v>
+        <v>20.54</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B173" t="s">
         <v>25</v>
@@ -7476,22 +7474,22 @@
         <v>4</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>180</v>
+        <v>222</v>
       </c>
       <c r="F173">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G173" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="H173" s="2">
-        <v>22.91</v>
+        <v>19.88</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B174" t="s">
         <v>25</v>
@@ -7503,22 +7501,22 @@
         <v>4</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F174">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G174" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="H174" s="2">
-        <v>23.7</v>
+        <v>22.12</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B175" t="s">
         <v>25</v>
@@ -7530,22 +7528,22 @@
         <v>4</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>281</v>
+        <v>180</v>
       </c>
       <c r="F175">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>0</v>
       </c>
       <c r="G175" t="s">
-        <v>247</v>
+        <v>228</v>
       </c>
       <c r="H175" s="2">
-        <v>24.490000000000002</v>
+        <v>22.91</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B176" t="s">
         <v>25</v>
@@ -7557,22 +7555,22 @@
         <v>4</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>299</v>
+        <v>233</v>
       </c>
       <c r="F176">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G176" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="H176" s="2">
-        <v>25.28</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B177" t="s">
         <v>25</v>
@@ -7584,49 +7582,49 @@
         <v>4</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>316</v>
+        <v>281</v>
       </c>
       <c r="F177">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>0</v>
       </c>
       <c r="G177" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="H177" s="2">
-        <v>26.069999999999997</v>
+        <v>24.490000000000002</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A178" s="4">
-        <v>286</v>
-      </c>
-      <c r="B178" s="4" t="s">
+      <c r="A178">
+        <v>284</v>
+      </c>
+      <c r="B178" t="s">
         <v>25</v>
       </c>
-      <c r="C178" s="4" t="s">
+      <c r="C178" t="s">
         <v>26</v>
       </c>
-      <c r="D178" s="4" t="s">
+      <c r="D178" t="s">
         <v>4</v>
       </c>
-      <c r="E178" s="5" t="s">
-        <v>285</v>
+      <c r="E178" s="1" t="s">
+        <v>299</v>
       </c>
       <c r="F178">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>20</v>
-      </c>
-      <c r="G178" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="H178" s="6">
-        <v>26.86</v>
+        <v>25</v>
+      </c>
+      <c r="G178" t="s">
+        <v>248</v>
+      </c>
+      <c r="H178" s="2">
+        <v>25.28</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B179" t="s">
         <v>25</v>
@@ -7638,49 +7636,49 @@
         <v>4</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="F179">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>0</v>
       </c>
       <c r="G179" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="H179" s="2">
-        <v>27.65</v>
+        <v>26.069999999999997</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A180">
-        <v>288</v>
-      </c>
-      <c r="B180" t="s">
+      <c r="A180" s="4">
+        <v>286</v>
+      </c>
+      <c r="B180" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C180" t="s">
+      <c r="C180" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D180" t="s">
+      <c r="D180" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E180" s="1" t="s">
-        <v>331</v>
+      <c r="E180" s="5" t="s">
+        <v>285</v>
       </c>
       <c r="F180">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="G180" t="s">
-        <v>251</v>
-      </c>
-      <c r="H180" s="2">
-        <v>28.44</v>
+        <v>20</v>
+      </c>
+      <c r="G180" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="H180" s="6">
+        <v>26.86</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B181" t="s">
         <v>25</v>
@@ -7692,22 +7690,22 @@
         <v>4</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>332</v>
+        <v>302</v>
       </c>
       <c r="F181">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>0</v>
       </c>
       <c r="G181" t="s">
-        <v>252</v>
+        <v>228</v>
       </c>
       <c r="H181" s="2">
-        <v>29.229999999999997</v>
+        <v>27.65</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182">
-        <v>1636</v>
+        <v>288</v>
       </c>
       <c r="B182" t="s">
         <v>25</v>
@@ -7716,25 +7714,25 @@
         <v>26</v>
       </c>
       <c r="D182" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="F182">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>0</v>
       </c>
       <c r="G182" t="s">
-        <v>227</v>
+        <v>251</v>
       </c>
       <c r="H182" s="2">
-        <v>16.068292682926828</v>
+        <v>28.44</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183">
-        <v>1637</v>
+        <v>289</v>
       </c>
       <c r="B183" t="s">
         <v>25</v>
@@ -7743,25 +7741,25 @@
         <v>26</v>
       </c>
       <c r="D183" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="F183" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>#N/A</v>
+        <v>332</v>
+      </c>
+      <c r="F183">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>0</v>
       </c>
       <c r="G183" t="s">
-        <v>227</v>
+        <v>252</v>
       </c>
       <c r="H183" s="2">
-        <v>18.478536585365852</v>
+        <v>29.229999999999997</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184">
-        <v>297</v>
+        <v>1636</v>
       </c>
       <c r="B184" t="s">
         <v>25</v>
@@ -7773,22 +7771,22 @@
         <v>8</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="F184">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>0</v>
       </c>
       <c r="G184" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H184" s="2">
-        <v>30.529756097560973</v>
+        <v>16.068292682926828</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185">
-        <v>298</v>
+        <v>1637</v>
       </c>
       <c r="B185" t="s">
         <v>25</v>
@@ -7800,22 +7798,22 @@
         <v>8</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="F185">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>328</v>
+      </c>
+      <c r="F185" t="e">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>#N/A</v>
       </c>
       <c r="G185" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="H185" s="2">
-        <v>31.333170731707312</v>
+        <v>18.478536585365852</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B186" t="s">
         <v>25</v>
@@ -7827,22 +7825,22 @@
         <v>8</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F186">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>0</v>
       </c>
       <c r="G186" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H186" s="2">
-        <v>32.136585365853655</v>
+        <v>30.529756097560973</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B187" t="s">
         <v>25</v>
@@ -7854,22 +7852,22 @@
         <v>8</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="F187">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G187" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="H187" s="2">
-        <v>32.94</v>
+        <v>31.333170731707312</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B188" t="s">
         <v>25</v>
@@ -7881,22 +7879,22 @@
         <v>8</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>141</v>
+        <v>335</v>
       </c>
       <c r="F188">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>0</v>
       </c>
       <c r="G188" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="H188" s="2">
-        <v>33.74341463414634</v>
+        <v>32.136585365853655</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B189" t="s">
         <v>25</v>
@@ -7908,22 +7906,22 @@
         <v>8</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>164</v>
+        <v>336</v>
       </c>
       <c r="F189">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G189" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="H189" s="2">
-        <v>34.546829268292683</v>
+        <v>32.94</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B190" t="s">
         <v>25</v>
@@ -7935,22 +7933,22 @@
         <v>8</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>337</v>
+        <v>141</v>
       </c>
       <c r="F190">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>0</v>
       </c>
       <c r="G190" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H190" s="2">
-        <v>35.350243902439018</v>
+        <v>33.74341463414634</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B191" t="s">
         <v>25</v>
@@ -7962,22 +7960,22 @@
         <v>8</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>338</v>
+        <v>164</v>
       </c>
       <c r="F191">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>0</v>
       </c>
       <c r="G191" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="H191" s="2">
-        <v>36.153658536585361</v>
+        <v>34.546829268292683</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192">
-        <v>1781</v>
+        <v>303</v>
       </c>
       <c r="B192" t="s">
         <v>25</v>
@@ -7986,25 +7984,25 @@
         <v>26</v>
       </c>
       <c r="D192" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F192">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>0</v>
       </c>
       <c r="G192" t="s">
-        <v>227</v>
-      </c>
-      <c r="H192" s="2" t="e">
-        <v>#N/A</v>
+        <v>239</v>
+      </c>
+      <c r="H192" s="2">
+        <v>35.350243902439018</v>
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193">
-        <v>1782</v>
+        <v>304</v>
       </c>
       <c r="B193" t="s">
         <v>25</v>
@@ -8013,112 +8011,111 @@
         <v>26</v>
       </c>
       <c r="D193" t="s">
+        <v>8</v>
+      </c>
+      <c r="E193" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="F193">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G193" t="s">
+        <v>242</v>
+      </c>
+      <c r="H193" s="2">
+        <v>36.153658536585361</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A194" s="7">
+        <v>1962</v>
+      </c>
+      <c r="B194" t="s">
+        <v>25</v>
+      </c>
+      <c r="C194" t="s">
+        <v>26</v>
+      </c>
+      <c r="D194" t="s">
         <v>9</v>
       </c>
-      <c r="E193" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="F193">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="G193" t="s">
-        <v>229</v>
-      </c>
-      <c r="H193" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A194">
-        <v>1644</v>
-      </c>
-      <c r="B194" t="s">
-        <v>27</v>
-      </c>
-      <c r="C194" t="s">
-        <v>29</v>
-      </c>
-      <c r="D194" t="s">
-        <v>28</v>
-      </c>
-      <c r="E194" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="F194" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>#N/A</v>
+      <c r="E194" s="3">
+        <v>1650</v>
+      </c>
+      <c r="F194">
+        <v>7</v>
       </c>
       <c r="G194" t="s">
-        <v>171</v>
+        <v>227</v>
       </c>
       <c r="H194" s="2">
-        <v>3.66</v>
+        <v>107.44</v>
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195">
-        <v>1589</v>
+        <v>1781</v>
       </c>
       <c r="B195" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C195" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D195" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="F195" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>335</v>
+      </c>
+      <c r="F195">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G195" t="s">
+        <v>227</v>
+      </c>
+      <c r="H195" s="2" t="e">
         <v>#N/A</v>
-      </c>
-      <c r="G195" t="s">
-        <v>111</v>
-      </c>
-      <c r="H195" s="2">
-        <v>3.97</v>
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196">
-        <v>1590</v>
+        <v>1782</v>
       </c>
       <c r="B196" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C196" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D196" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="F196" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>336</v>
+      </c>
+      <c r="F196">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G196" t="s">
+        <v>229</v>
+      </c>
+      <c r="H196" s="2" t="e">
         <v>#N/A</v>
-      </c>
-      <c r="G196" t="s">
-        <v>126</v>
-      </c>
-      <c r="H196" s="2">
-        <v>4.91</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197">
-        <v>1592</v>
+        <v>1644</v>
       </c>
       <c r="B197" t="s">
         <v>27</v>
       </c>
       <c r="C197" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D197" t="s">
         <v>28</v>
@@ -8131,21 +8128,21 @@
         <v>#N/A</v>
       </c>
       <c r="G197" t="s">
-        <v>81</v>
+        <v>171</v>
       </c>
       <c r="H197" s="2">
-        <v>5.63</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198">
-        <v>1593</v>
+        <v>1589</v>
       </c>
       <c r="B198" t="s">
         <v>27</v>
       </c>
       <c r="C198" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D198" t="s">
         <v>28</v>
@@ -8158,18 +8155,21 @@
         <v>#N/A</v>
       </c>
       <c r="G198" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="H198" s="2">
-        <v>7.25</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A199">
+        <v>1590</v>
+      </c>
       <c r="B199" t="s">
         <v>27</v>
       </c>
       <c r="C199" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D199" t="s">
         <v>28</v>
@@ -8181,19 +8181,22 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="H199" s="2" t="e">
-        <v>#N/A</v>
+      <c r="G199" t="s">
+        <v>126</v>
+      </c>
+      <c r="H199" s="2">
+        <v>4.91</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200">
-        <v>1594</v>
+        <v>1592</v>
       </c>
       <c r="B200" t="s">
         <v>27</v>
       </c>
       <c r="C200" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D200" t="s">
         <v>28</v>
@@ -8206,18 +8209,21 @@
         <v>#N/A</v>
       </c>
       <c r="G200" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="H200" s="2">
-        <v>10.74</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A201">
+        <v>1593</v>
+      </c>
       <c r="B201" t="s">
         <v>27</v>
       </c>
       <c r="C201" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D201" t="s">
         <v>28</v>
@@ -8229,19 +8235,19 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="H201" s="2" t="e">
-        <v>#N/A</v>
+      <c r="G201" t="s">
+        <v>88</v>
+      </c>
+      <c r="H201" s="2">
+        <v>7.25</v>
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A202">
-        <v>1595</v>
-      </c>
       <c r="B202" t="s">
         <v>27</v>
       </c>
       <c r="C202" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D202" t="s">
         <v>28</v>
@@ -8253,22 +8259,19 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="G202" t="s">
-        <v>120</v>
-      </c>
-      <c r="H202" s="2">
-        <v>5.38</v>
+      <c r="H202" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203">
-        <v>1596</v>
+        <v>1594</v>
       </c>
       <c r="B203" t="s">
         <v>27</v>
       </c>
       <c r="C203" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D203" t="s">
         <v>28</v>
@@ -8281,21 +8284,18 @@
         <v>#N/A</v>
       </c>
       <c r="G203" t="s">
-        <v>132</v>
+        <v>97</v>
       </c>
       <c r="H203" s="2">
-        <v>6.78</v>
+        <v>10.74</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A204">
-        <v>1597</v>
-      </c>
       <c r="B204" t="s">
         <v>27</v>
       </c>
       <c r="C204" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D204" t="s">
         <v>28</v>
@@ -8307,22 +8307,19 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="G204" t="s">
-        <v>84</v>
-      </c>
-      <c r="H204" s="2">
-        <v>7.94</v>
+      <c r="H204" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205">
-        <v>1598</v>
+        <v>1595</v>
       </c>
       <c r="B205" t="s">
         <v>27</v>
       </c>
       <c r="C205" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D205" t="s">
         <v>28</v>
@@ -8335,18 +8332,21 @@
         <v>#N/A</v>
       </c>
       <c r="G205" t="s">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="H205" s="2">
-        <v>10.3</v>
+        <v>5.38</v>
       </c>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A206">
+        <v>1596</v>
+      </c>
       <c r="B206" t="s">
         <v>27</v>
       </c>
       <c r="C206" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D206" t="s">
         <v>28</v>
@@ -8358,19 +8358,22 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="H206" s="2" t="e">
-        <v>#N/A</v>
+      <c r="G206" t="s">
+        <v>132</v>
+      </c>
+      <c r="H206" s="2">
+        <v>6.78</v>
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="B207" t="s">
         <v>27</v>
       </c>
       <c r="C207" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D207" t="s">
         <v>28</v>
@@ -8383,21 +8386,24 @@
         <v>#N/A</v>
       </c>
       <c r="G207" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="H207" s="2">
-        <v>14.74</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A208">
+        <v>1598</v>
+      </c>
       <c r="B208" t="s">
         <v>27</v>
       </c>
       <c r="C208" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D208" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="E208" s="1" t="s">
         <v>322</v>
@@ -8406,22 +8412,22 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
+      <c r="G208" t="s">
+        <v>92</v>
+      </c>
       <c r="H208" s="2">
-        <v>4.2699999999999996</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A209">
-        <v>1600</v>
-      </c>
       <c r="B209" t="s">
         <v>27</v>
       </c>
       <c r="C209" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D209" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="E209" s="1" t="s">
         <v>322</v>
@@ -8430,25 +8436,22 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="G209" t="s">
-        <v>112</v>
-      </c>
-      <c r="H209" s="2">
-        <v>4.6399999999999997</v>
+      <c r="H209" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="B210" t="s">
         <v>27</v>
       </c>
       <c r="C210" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D210" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="E210" s="1" t="s">
         <v>322</v>
@@ -8458,21 +8461,18 @@
         <v>#N/A</v>
       </c>
       <c r="G210" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="H210" s="2">
-        <v>5.74</v>
+        <v>14.74</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A211">
-        <v>1602</v>
-      </c>
       <c r="B211" t="s">
         <v>27</v>
       </c>
       <c r="C211" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D211" t="s">
         <v>43</v>
@@ -8484,22 +8484,19 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="G211" t="s">
-        <v>139</v>
-      </c>
       <c r="H211" s="2">
-        <v>6.57</v>
+        <v>4.2699999999999996</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212">
-        <v>1603</v>
+        <v>1600</v>
       </c>
       <c r="B212" t="s">
         <v>27</v>
       </c>
       <c r="C212" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D212" t="s">
         <v>43</v>
@@ -8512,18 +8509,21 @@
         <v>#N/A</v>
       </c>
       <c r="G212" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="H212" s="2">
-        <v>8.4499999999999993</v>
+        <v>4.6399999999999997</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A213">
+        <v>1601</v>
+      </c>
       <c r="B213" t="s">
         <v>27</v>
       </c>
       <c r="C213" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D213" t="s">
         <v>43</v>
@@ -8535,19 +8535,22 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="H213" s="2" t="e">
-        <v>#N/A</v>
+      <c r="G213" t="s">
+        <v>74</v>
+      </c>
+      <c r="H213" s="2">
+        <v>5.74</v>
       </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="B214" t="s">
         <v>27</v>
       </c>
       <c r="C214" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D214" t="s">
         <v>43</v>
@@ -8560,18 +8563,21 @@
         <v>#N/A</v>
       </c>
       <c r="G214" t="s">
-        <v>98</v>
+        <v>139</v>
       </c>
       <c r="H214" s="2">
-        <v>12.58</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A215">
+        <v>1603</v>
+      </c>
       <c r="B215" t="s">
         <v>27</v>
       </c>
       <c r="C215" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D215" t="s">
         <v>43</v>
@@ -8583,19 +8589,19 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="H215" s="2" t="e">
-        <v>#N/A</v>
+      <c r="G215" t="s">
+        <v>89</v>
+      </c>
+      <c r="H215" s="2">
+        <v>8.4499999999999993</v>
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A216">
-        <v>1605</v>
-      </c>
       <c r="B216" t="s">
         <v>27</v>
       </c>
       <c r="C216" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D216" t="s">
         <v>43</v>
@@ -8607,22 +8613,19 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="G216" t="s">
-        <v>72</v>
-      </c>
-      <c r="H216" s="2">
-        <v>6.41</v>
+      <c r="H216" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="B217" t="s">
         <v>27</v>
       </c>
       <c r="C217" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D217" t="s">
         <v>43</v>
@@ -8635,21 +8638,18 @@
         <v>#N/A</v>
       </c>
       <c r="G217" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="H217" s="2">
-        <v>7.92</v>
+        <v>12.58</v>
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A218">
-        <v>1608</v>
-      </c>
       <c r="B218" t="s">
         <v>27</v>
       </c>
       <c r="C218" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D218" t="s">
         <v>43</v>
@@ -8661,22 +8661,19 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="G218" t="s">
-        <v>85</v>
-      </c>
-      <c r="H218" s="2">
-        <v>9.3699999999999992</v>
+      <c r="H218" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219">
-        <v>1609</v>
+        <v>1605</v>
       </c>
       <c r="B219" t="s">
         <v>27</v>
       </c>
       <c r="C219" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D219" t="s">
         <v>43</v>
@@ -8689,18 +8686,21 @@
         <v>#N/A</v>
       </c>
       <c r="G219" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="H219" s="2">
-        <v>12.03</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A220">
+        <v>1606</v>
+      </c>
       <c r="B220" t="s">
         <v>27</v>
       </c>
       <c r="C220" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D220" t="s">
         <v>43</v>
@@ -8712,19 +8712,22 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="H220" s="2" t="e">
-        <v>#N/A</v>
+      <c r="G220" t="s">
+        <v>78</v>
+      </c>
+      <c r="H220" s="2">
+        <v>7.92</v>
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="B221" t="s">
         <v>27</v>
       </c>
       <c r="C221" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D221" t="s">
         <v>43</v>
@@ -8737,21 +8740,24 @@
         <v>#N/A</v>
       </c>
       <c r="G221" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="H221" s="2">
-        <v>17.34</v>
+        <v>9.3699999999999992</v>
       </c>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A222">
+        <v>1609</v>
+      </c>
       <c r="B222" t="s">
         <v>27</v>
       </c>
       <c r="C222" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="D222" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="E222" s="1" t="s">
         <v>322</v>
@@ -8760,73 +8766,67 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
+      <c r="G222" t="s">
+        <v>93</v>
+      </c>
       <c r="H222" s="2">
-        <v>3.66</v>
+        <v>12.03</v>
       </c>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A223">
-        <v>163</v>
-      </c>
       <c r="B223" t="s">
         <v>27</v>
       </c>
       <c r="C223" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="D223" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="E223" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F223">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>110</v>
-      </c>
-      <c r="G223" t="s">
-        <v>111</v>
-      </c>
-      <c r="H223" s="2">
-        <v>3.97</v>
+      <c r="F223" t="e">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H223" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224">
-        <v>480</v>
+        <v>1610</v>
       </c>
       <c r="B224" t="s">
         <v>27</v>
       </c>
       <c r="C224" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="D224" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="E224" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F224">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>110</v>
+      <c r="F224" t="e">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>#N/A</v>
       </c>
       <c r="G224" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="H224" s="2">
-        <v>4.91</v>
+        <v>17.34</v>
       </c>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A225">
-        <v>164</v>
-      </c>
       <c r="B225" t="s">
         <v>27</v>
       </c>
       <c r="C225" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D225" t="s">
         <v>58</v>
@@ -8834,26 +8834,23 @@
       <c r="E225" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F225">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>90</v>
-      </c>
-      <c r="G225" t="s">
-        <v>137</v>
+      <c r="F225" t="e">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>#N/A</v>
       </c>
       <c r="H225" s="2">
-        <v>5.63</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B226" t="s">
         <v>27</v>
       </c>
       <c r="C226" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D226" t="s">
         <v>58</v>
@@ -8863,21 +8860,24 @@
       </c>
       <c r="F226">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="G226" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="H226" s="2">
-        <v>7.25</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A227">
+        <v>480</v>
+      </c>
       <c r="B227" t="s">
         <v>27</v>
       </c>
       <c r="C227" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D227" t="s">
         <v>58</v>
@@ -8885,23 +8885,26 @@
       <c r="E227" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F227" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H227" s="2" t="e">
-        <v>#N/A</v>
+      <c r="F227">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>110</v>
+      </c>
+      <c r="G227" t="s">
+        <v>126</v>
+      </c>
+      <c r="H227" s="2">
+        <v>4.91</v>
       </c>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B228" t="s">
         <v>27</v>
       </c>
       <c r="C228" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D228" t="s">
         <v>58</v>
@@ -8911,21 +8914,24 @@
       </c>
       <c r="F228">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="G228" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="H228" s="2">
-        <v>10.74</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A229">
+        <v>165</v>
+      </c>
       <c r="B229" t="s">
         <v>27</v>
       </c>
       <c r="C229" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D229" t="s">
         <v>58</v>
@@ -8933,23 +8939,23 @@
       <c r="E229" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F229" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H229" s="2" t="e">
-        <v>#N/A</v>
+      <c r="F229">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>70</v>
+      </c>
+      <c r="G229" t="s">
+        <v>149</v>
+      </c>
+      <c r="H229" s="2">
+        <v>7.25</v>
       </c>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A230">
-        <v>171</v>
-      </c>
       <c r="B230" t="s">
         <v>27</v>
       </c>
       <c r="C230" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D230" t="s">
         <v>58</v>
@@ -8957,26 +8963,23 @@
       <c r="E230" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F230">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>100</v>
-      </c>
-      <c r="G230" t="s">
-        <v>117</v>
-      </c>
-      <c r="H230" s="2">
-        <v>5.38</v>
+      <c r="F230" t="e">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H230" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231">
-        <v>478</v>
+        <v>166</v>
       </c>
       <c r="B231" t="s">
         <v>27</v>
       </c>
       <c r="C231" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D231" t="s">
         <v>58</v>
@@ -8986,24 +8989,21 @@
       </c>
       <c r="F231">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="G231" t="s">
-        <v>132</v>
+        <v>157</v>
       </c>
       <c r="H231" s="2">
-        <v>6.78</v>
+        <v>10.74</v>
       </c>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A232">
-        <v>172</v>
-      </c>
       <c r="B232" t="s">
         <v>27</v>
       </c>
       <c r="C232" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D232" t="s">
         <v>58</v>
@@ -9011,26 +9011,23 @@
       <c r="E232" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F232">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>75</v>
-      </c>
-      <c r="G232" t="s">
-        <v>145</v>
-      </c>
-      <c r="H232" s="2">
-        <v>7.94</v>
+      <c r="F232" t="e">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H232" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B233" t="s">
         <v>27</v>
       </c>
       <c r="C233" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D233" t="s">
         <v>58</v>
@@ -9040,21 +9037,24 @@
       </c>
       <c r="F233">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="G233" t="s">
-        <v>155</v>
+        <v>117</v>
       </c>
       <c r="H233" s="2">
-        <v>10.3</v>
+        <v>5.38</v>
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A234">
+        <v>478</v>
+      </c>
       <c r="B234" t="s">
         <v>27</v>
       </c>
       <c r="C234" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D234" t="s">
         <v>58</v>
@@ -9062,23 +9062,26 @@
       <c r="E234" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F234" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H234" s="2" t="e">
-        <v>#N/A</v>
+      <c r="F234">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>90</v>
+      </c>
+      <c r="G234" t="s">
+        <v>132</v>
+      </c>
+      <c r="H234" s="2">
+        <v>6.78</v>
       </c>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B235" t="s">
         <v>27</v>
       </c>
       <c r="C235" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D235" t="s">
         <v>58</v>
@@ -9088,99 +9091,96 @@
       </c>
       <c r="F235">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="G235" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="H235" s="2">
-        <v>14.74</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A236">
+        <v>173</v>
+      </c>
       <c r="B236" t="s">
         <v>27</v>
       </c>
       <c r="C236" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D236" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E236" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F236" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>#N/A</v>
+      <c r="F236">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>60</v>
+      </c>
+      <c r="G236" t="s">
+        <v>155</v>
       </c>
       <c r="H236" s="2">
-        <v>4.2699999999999996</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A237">
-        <v>159</v>
-      </c>
       <c r="B237" t="s">
         <v>27</v>
       </c>
       <c r="C237" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D237" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E237" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F237">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>110</v>
-      </c>
-      <c r="G237" t="s">
-        <v>112</v>
-      </c>
-      <c r="H237" s="2">
-        <v>4.6399999999999997</v>
+      <c r="F237" t="e">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H237" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238">
-        <v>481</v>
+        <v>174</v>
       </c>
       <c r="B238" t="s">
         <v>27</v>
       </c>
       <c r="C238" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D238" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E238" s="1" t="s">
         <v>322</v>
       </c>
       <c r="F238">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="G238" t="s">
-        <v>127</v>
+        <v>165</v>
       </c>
       <c r="H238" s="2">
-        <v>5.74</v>
+        <v>14.74</v>
       </c>
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A239">
-        <v>160</v>
-      </c>
       <c r="B239" t="s">
         <v>27</v>
       </c>
       <c r="C239" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D239" t="s">
         <v>59</v>
@@ -9188,26 +9188,23 @@
       <c r="E239" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F239">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>80</v>
-      </c>
-      <c r="G239" t="s">
-        <v>139</v>
+      <c r="F239" t="e">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>#N/A</v>
       </c>
       <c r="H239" s="2">
-        <v>6.57</v>
+        <v>4.2699999999999996</v>
       </c>
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B240" t="s">
         <v>27</v>
       </c>
       <c r="C240" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D240" t="s">
         <v>59</v>
@@ -9217,21 +9214,24 @@
       </c>
       <c r="F240">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="G240" t="s">
-        <v>152</v>
+        <v>112</v>
       </c>
       <c r="H240" s="2">
-        <v>8.4499999999999993</v>
+        <v>4.6399999999999997</v>
       </c>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A241">
+        <v>481</v>
+      </c>
       <c r="B241" t="s">
         <v>27</v>
       </c>
       <c r="C241" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D241" t="s">
         <v>59</v>
@@ -9239,23 +9239,26 @@
       <c r="E241" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F241" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H241" s="2" t="e">
-        <v>#N/A</v>
+      <c r="F241">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>110</v>
+      </c>
+      <c r="G241" t="s">
+        <v>127</v>
+      </c>
+      <c r="H241" s="2">
+        <v>5.74</v>
       </c>
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B242" t="s">
         <v>27</v>
       </c>
       <c r="C242" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D242" t="s">
         <v>59</v>
@@ -9265,21 +9268,24 @@
       </c>
       <c r="F242">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="G242" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="H242" s="2">
-        <v>12.58</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A243">
+        <v>161</v>
+      </c>
       <c r="B243" t="s">
         <v>27</v>
       </c>
       <c r="C243" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D243" t="s">
         <v>59</v>
@@ -9287,23 +9293,23 @@
       <c r="E243" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F243" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H243" s="2" t="e">
-        <v>#N/A</v>
+      <c r="F243">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>70</v>
+      </c>
+      <c r="G243" t="s">
+        <v>152</v>
+      </c>
+      <c r="H243" s="2">
+        <v>8.4499999999999993</v>
       </c>
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A244">
-        <v>167</v>
-      </c>
       <c r="B244" t="s">
         <v>27</v>
       </c>
       <c r="C244" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D244" t="s">
         <v>59</v>
@@ -9311,26 +9317,23 @@
       <c r="E244" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F244">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>90</v>
-      </c>
-      <c r="G244" t="s">
-        <v>121</v>
-      </c>
-      <c r="H244" s="2">
-        <v>6.41</v>
+      <c r="F244" t="e">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H244" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245">
-        <v>479</v>
+        <v>162</v>
       </c>
       <c r="B245" t="s">
         <v>27</v>
       </c>
       <c r="C245" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D245" t="s">
         <v>59</v>
@@ -9340,24 +9343,21 @@
       </c>
       <c r="F245">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="G245" t="s">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="H245" s="2">
-        <v>7.92</v>
+        <v>12.58</v>
       </c>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A246">
-        <v>168</v>
-      </c>
       <c r="B246" t="s">
         <v>27</v>
       </c>
       <c r="C246" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D246" t="s">
         <v>59</v>
@@ -9365,26 +9365,23 @@
       <c r="E246" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F246">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>70</v>
-      </c>
-      <c r="G246" t="s">
-        <v>172</v>
-      </c>
-      <c r="H246" s="2">
-        <v>9.3699999999999992</v>
+      <c r="F246" t="e">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H246" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B247" t="s">
         <v>27</v>
       </c>
       <c r="C247" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D247" t="s">
         <v>59</v>
@@ -9394,21 +9391,24 @@
       </c>
       <c r="F247">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="G247" t="s">
-        <v>173</v>
+        <v>121</v>
       </c>
       <c r="H247" s="2">
-        <v>12.03</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A248">
+        <v>479</v>
+      </c>
       <c r="B248" t="s">
         <v>27</v>
       </c>
       <c r="C248" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D248" t="s">
         <v>59</v>
@@ -9416,23 +9416,26 @@
       <c r="E248" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F248" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H248" s="2" t="e">
-        <v>#N/A</v>
+      <c r="F248">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>80</v>
+      </c>
+      <c r="G248" t="s">
+        <v>133</v>
+      </c>
+      <c r="H248" s="2">
+        <v>7.92</v>
       </c>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B249" t="s">
         <v>27</v>
       </c>
       <c r="C249" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D249" t="s">
         <v>59</v>
@@ -9442,48 +9445,51 @@
       </c>
       <c r="F249">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="G249" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="H249" s="2">
-        <v>17.34</v>
+        <v>9.3699999999999992</v>
       </c>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A250">
+        <v>169</v>
+      </c>
       <c r="B250" t="s">
         <v>27</v>
       </c>
       <c r="C250" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="D250" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E250" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F250" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>#N/A</v>
+      <c r="F250">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>60</v>
+      </c>
+      <c r="G250" t="s">
+        <v>173</v>
       </c>
       <c r="H250" s="2">
-        <v>3.66</v>
+        <v>12.03</v>
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A251">
-        <v>1646</v>
-      </c>
       <c r="B251" t="s">
         <v>27</v>
       </c>
       <c r="C251" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="D251" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E251" s="1" t="s">
         <v>322</v>
@@ -9492,49 +9498,43 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="G251" t="s">
-        <v>110</v>
-      </c>
-      <c r="H251" s="2">
-        <v>3.97</v>
+      <c r="H251" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252">
-        <v>1647</v>
+        <v>170</v>
       </c>
       <c r="B252" t="s">
         <v>27</v>
       </c>
       <c r="C252" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="D252" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E252" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F252" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>#N/A</v>
+      <c r="F252">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>35</v>
       </c>
       <c r="G252" t="s">
-        <v>73</v>
+        <v>167</v>
       </c>
       <c r="H252" s="2">
-        <v>4.91</v>
+        <v>17.34</v>
       </c>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A253">
-        <v>1648</v>
-      </c>
       <c r="B253" t="s">
         <v>27</v>
       </c>
       <c r="C253" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D253" t="s">
         <v>60</v>
@@ -9546,22 +9546,19 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="G253" t="s">
-        <v>80</v>
-      </c>
       <c r="H253" s="2">
-        <v>5.63</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A254">
-        <v>1649</v>
+        <v>1646</v>
       </c>
       <c r="B254" t="s">
         <v>27</v>
       </c>
       <c r="C254" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D254" t="s">
         <v>60</v>
@@ -9574,18 +9571,21 @@
         <v>#N/A</v>
       </c>
       <c r="G254" t="s">
-        <v>148</v>
+        <v>110</v>
       </c>
       <c r="H254" s="2">
-        <v>7.25</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A255">
+        <v>1647</v>
+      </c>
       <c r="B255" t="s">
         <v>27</v>
       </c>
       <c r="C255" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D255" t="s">
         <v>60</v>
@@ -9597,19 +9597,22 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="H255" s="2" t="e">
-        <v>#N/A</v>
+      <c r="G255" t="s">
+        <v>73</v>
+      </c>
+      <c r="H255" s="2">
+        <v>4.91</v>
       </c>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256">
-        <v>1650</v>
+        <v>1648</v>
       </c>
       <c r="B256" t="s">
         <v>27</v>
       </c>
       <c r="C256" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D256" t="s">
         <v>60</v>
@@ -9622,18 +9625,21 @@
         <v>#N/A</v>
       </c>
       <c r="G256" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="H256" s="2">
-        <v>10.74</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A257">
+        <v>1649</v>
+      </c>
       <c r="B257" t="s">
         <v>27</v>
       </c>
       <c r="C257" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D257" t="s">
         <v>60</v>
@@ -9645,19 +9651,19 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="H257" s="2" t="e">
-        <v>#N/A</v>
+      <c r="G257" t="s">
+        <v>148</v>
+      </c>
+      <c r="H257" s="2">
+        <v>7.25</v>
       </c>
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A258">
-        <v>1651</v>
-      </c>
       <c r="B258" t="s">
         <v>27</v>
       </c>
       <c r="C258" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D258" t="s">
         <v>60</v>
@@ -9669,22 +9675,19 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="G258" t="s">
-        <v>71</v>
-      </c>
-      <c r="H258" s="2">
-        <v>5.38</v>
+      <c r="H258" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A259">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="B259" t="s">
         <v>27</v>
       </c>
       <c r="C259" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D259" t="s">
         <v>60</v>
@@ -9697,21 +9700,18 @@
         <v>#N/A</v>
       </c>
       <c r="G259" t="s">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="H259" s="2">
-        <v>6.78</v>
+        <v>10.74</v>
       </c>
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A260">
-        <v>1653</v>
-      </c>
       <c r="B260" t="s">
         <v>27</v>
       </c>
       <c r="C260" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D260" t="s">
         <v>60</v>
@@ -9723,22 +9723,19 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="G260" t="s">
-        <v>143</v>
-      </c>
-      <c r="H260" s="2">
-        <v>7.94</v>
+      <c r="H260" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261">
-        <v>1654</v>
+        <v>1651</v>
       </c>
       <c r="B261" t="s">
         <v>27</v>
       </c>
       <c r="C261" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D261" t="s">
         <v>60</v>
@@ -9751,18 +9748,21 @@
         <v>#N/A</v>
       </c>
       <c r="G261" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="H261" s="2">
-        <v>10.3</v>
+        <v>5.38</v>
       </c>
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A262">
+        <v>1652</v>
+      </c>
       <c r="B262" t="s">
         <v>27</v>
       </c>
       <c r="C262" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D262" t="s">
         <v>60</v>
@@ -9774,19 +9774,22 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="H262" s="2" t="e">
-        <v>#N/A</v>
+      <c r="G262" t="s">
+        <v>129</v>
+      </c>
+      <c r="H262" s="2">
+        <v>6.78</v>
       </c>
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A263">
-        <v>1655</v>
+        <v>1653</v>
       </c>
       <c r="B263" t="s">
         <v>27</v>
       </c>
       <c r="C263" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D263" t="s">
         <v>60</v>
@@ -9799,24 +9802,24 @@
         <v>#N/A</v>
       </c>
       <c r="G263" t="s">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="H263" s="2">
-        <v>14.74</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A264">
-        <v>1787</v>
+        <v>1654</v>
       </c>
       <c r="B264" t="s">
         <v>27</v>
       </c>
       <c r="C264" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D264" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E264" s="1" t="s">
         <v>322</v>
@@ -9826,51 +9829,45 @@
         <v>#N/A</v>
       </c>
       <c r="G264" t="s">
-        <v>170</v>
+        <v>91</v>
       </c>
       <c r="H264" s="2">
-        <v>4.2699999999999996</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A265">
-        <v>1656</v>
-      </c>
       <c r="B265" t="s">
         <v>27</v>
       </c>
       <c r="C265" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D265" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E265" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F265">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>110</v>
-      </c>
-      <c r="G265" t="s">
-        <v>69</v>
-      </c>
-      <c r="H265" s="2">
-        <v>4.6399999999999997</v>
+      <c r="F265" t="e">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H265" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A266">
-        <v>1657</v>
+        <v>1655</v>
       </c>
       <c r="B266" t="s">
         <v>27</v>
       </c>
       <c r="C266" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D266" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E266" s="1" t="s">
         <v>322</v>
@@ -9880,21 +9877,21 @@
         <v>#N/A</v>
       </c>
       <c r="G266" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="H266" s="2">
-        <v>5.74</v>
+        <v>14.74</v>
       </c>
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A267">
-        <v>1658</v>
+        <v>1787</v>
       </c>
       <c r="B267" t="s">
         <v>27</v>
       </c>
       <c r="C267" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D267" t="s">
         <v>61</v>
@@ -9907,21 +9904,21 @@
         <v>#N/A</v>
       </c>
       <c r="G267" t="s">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="H267" s="2">
-        <v>6.57</v>
+        <v>4.2699999999999996</v>
       </c>
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A268">
-        <v>1659</v>
+        <v>1656</v>
       </c>
       <c r="B268" t="s">
         <v>27</v>
       </c>
       <c r="C268" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D268" t="s">
         <v>61</v>
@@ -9929,23 +9926,26 @@
       <c r="E268" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F268" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>#N/A</v>
+      <c r="F268">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>110</v>
       </c>
       <c r="G268" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="H268" s="2">
-        <v>8.4499999999999993</v>
+        <v>4.6399999999999997</v>
       </c>
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A269">
+        <v>1657</v>
+      </c>
       <c r="B269" t="s">
         <v>27</v>
       </c>
       <c r="C269" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D269" t="s">
         <v>61</v>
@@ -9957,19 +9957,22 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="H269" s="2" t="e">
-        <v>#N/A</v>
+      <c r="G269" t="s">
+        <v>73</v>
+      </c>
+      <c r="H269" s="2">
+        <v>5.74</v>
       </c>
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A270">
-        <v>1660</v>
+        <v>1658</v>
       </c>
       <c r="B270" t="s">
         <v>27</v>
       </c>
       <c r="C270" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D270" t="s">
         <v>61</v>
@@ -9982,18 +9985,21 @@
         <v>#N/A</v>
       </c>
       <c r="G270" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="H270" s="2">
-        <v>12.58</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A271">
+        <v>1659</v>
+      </c>
       <c r="B271" t="s">
         <v>27</v>
       </c>
       <c r="C271" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D271" t="s">
         <v>61</v>
@@ -10005,19 +10011,19 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="H271" s="2" t="e">
-        <v>#N/A</v>
+      <c r="G271" t="s">
+        <v>87</v>
+      </c>
+      <c r="H271" s="2">
+        <v>8.4499999999999993</v>
       </c>
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A272">
-        <v>1661</v>
-      </c>
       <c r="B272" t="s">
         <v>27</v>
       </c>
       <c r="C272" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D272" t="s">
         <v>61</v>
@@ -10029,22 +10035,19 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="G272" t="s">
-        <v>116</v>
-      </c>
-      <c r="H272" s="2">
-        <v>6.41</v>
+      <c r="H272" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="273" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A273">
-        <v>1662</v>
+        <v>1660</v>
       </c>
       <c r="B273" t="s">
         <v>27</v>
       </c>
       <c r="C273" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D273" t="s">
         <v>61</v>
@@ -10057,21 +10060,18 @@
         <v>#N/A</v>
       </c>
       <c r="G273" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="H273" s="2">
-        <v>7.92</v>
+        <v>12.58</v>
       </c>
     </row>
     <row r="274" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A274">
-        <v>1663</v>
-      </c>
       <c r="B274" t="s">
         <v>27</v>
       </c>
       <c r="C274" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D274" t="s">
         <v>61</v>
@@ -10083,22 +10083,19 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="G274" t="s">
-        <v>104</v>
-      </c>
-      <c r="H274" s="2">
-        <v>9.3699999999999992</v>
+      <c r="H274" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A275">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="B275" t="s">
         <v>27</v>
       </c>
       <c r="C275" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D275" t="s">
         <v>61</v>
@@ -10111,18 +10108,21 @@
         <v>#N/A</v>
       </c>
       <c r="G275" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="H275" s="2">
-        <v>12.03</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A276">
+        <v>1662</v>
+      </c>
       <c r="B276" t="s">
         <v>27</v>
       </c>
       <c r="C276" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D276" t="s">
         <v>61</v>
@@ -10134,19 +10134,22 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="H276" s="2" t="e">
-        <v>#N/A</v>
+      <c r="G276" t="s">
+        <v>77</v>
+      </c>
+      <c r="H276" s="2">
+        <v>7.92</v>
       </c>
     </row>
     <row r="277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A277">
-        <v>1665</v>
+        <v>1663</v>
       </c>
       <c r="B277" t="s">
         <v>27</v>
       </c>
       <c r="C277" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D277" t="s">
         <v>61</v>
@@ -10159,21 +10162,24 @@
         <v>#N/A</v>
       </c>
       <c r="G277" t="s">
-        <v>161</v>
+        <v>104</v>
       </c>
       <c r="H277" s="2">
-        <v>17.34</v>
+        <v>9.3699999999999992</v>
       </c>
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A278">
+        <v>1664</v>
+      </c>
       <c r="B278" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="C278" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="D278" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="E278" s="1" t="s">
         <v>322</v>
@@ -10182,22 +10188,22 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="H278" s="2" t="e">
-        <v>#N/A</v>
+      <c r="G278" t="s">
+        <v>105</v>
+      </c>
+      <c r="H278" s="2">
+        <v>12.03</v>
       </c>
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A279">
-        <v>1616</v>
-      </c>
       <c r="B279" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="C279" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="D279" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="E279" s="1" t="s">
         <v>322</v>
@@ -10206,25 +10212,22 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="G279" t="s">
-        <v>70</v>
-      </c>
-      <c r="H279" s="2">
-        <v>3.85</v>
+      <c r="H279" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="280" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A280">
-        <v>1617</v>
+        <v>1665</v>
       </c>
       <c r="B280" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="C280" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="D280" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="E280" s="1" t="s">
         <v>322</v>
@@ -10234,21 +10237,18 @@
         <v>#N/A</v>
       </c>
       <c r="G280" t="s">
-        <v>75</v>
+        <v>161</v>
       </c>
       <c r="H280" s="2">
-        <v>4.76</v>
+        <v>17.34</v>
       </c>
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A281">
-        <v>1618</v>
-      </c>
       <c r="B281" t="s">
         <v>62</v>
       </c>
       <c r="C281" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D281" t="s">
         <v>28</v>
@@ -10260,22 +10260,19 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="G281" t="s">
-        <v>140</v>
-      </c>
-      <c r="H281" s="2">
-        <v>5.47</v>
+      <c r="H281" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="282" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A282">
-        <v>1619</v>
+        <v>1616</v>
       </c>
       <c r="B282" t="s">
         <v>62</v>
       </c>
       <c r="C282" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D282" t="s">
         <v>28</v>
@@ -10288,18 +10285,21 @@
         <v>#N/A</v>
       </c>
       <c r="G282" t="s">
-        <v>153</v>
+        <v>70</v>
       </c>
       <c r="H282" s="2">
-        <v>7.03</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A283">
+        <v>1617</v>
+      </c>
       <c r="B283" t="s">
         <v>62</v>
       </c>
       <c r="C283" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D283" t="s">
         <v>28</v>
@@ -10311,19 +10311,22 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="H283" s="2" t="e">
-        <v>#N/A</v>
+      <c r="G283" t="s">
+        <v>75</v>
+      </c>
+      <c r="H283" s="2">
+        <v>4.76</v>
       </c>
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A284">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="B284" t="s">
         <v>62</v>
       </c>
       <c r="C284" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D284" t="s">
         <v>28</v>
@@ -10336,18 +10339,21 @@
         <v>#N/A</v>
       </c>
       <c r="G284" t="s">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="H284" s="2">
-        <v>10.42</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A285">
+        <v>1619</v>
+      </c>
       <c r="B285" t="s">
         <v>62</v>
       </c>
       <c r="C285" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D285" t="s">
         <v>28</v>
@@ -10359,19 +10365,19 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="H285" s="2" t="e">
-        <v>#N/A</v>
+      <c r="G285" t="s">
+        <v>153</v>
+      </c>
+      <c r="H285" s="2">
+        <v>7.03</v>
       </c>
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A286">
-        <v>1611</v>
-      </c>
       <c r="B286" t="s">
         <v>62</v>
       </c>
       <c r="C286" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D286" t="s">
         <v>28</v>
@@ -10383,22 +10389,19 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="G286" t="s">
-        <v>122</v>
-      </c>
-      <c r="H286" s="2">
-        <v>5.21</v>
+      <c r="H286" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="287" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A287">
-        <v>1612</v>
+        <v>1620</v>
       </c>
       <c r="B287" t="s">
         <v>62</v>
       </c>
       <c r="C287" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D287" t="s">
         <v>28</v>
@@ -10411,21 +10414,18 @@
         <v>#N/A</v>
       </c>
       <c r="G287" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="H287" s="2">
-        <v>6.58</v>
+        <v>10.42</v>
       </c>
     </row>
     <row r="288" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A288">
-        <v>1613</v>
-      </c>
       <c r="B288" t="s">
         <v>62</v>
       </c>
       <c r="C288" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D288" t="s">
         <v>28</v>
@@ -10437,22 +10437,19 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="G288" t="s">
-        <v>86</v>
-      </c>
-      <c r="H288" s="2">
-        <v>7.7</v>
+      <c r="H288" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A289">
-        <v>1614</v>
+        <v>1611</v>
       </c>
       <c r="B289" t="s">
         <v>62</v>
       </c>
       <c r="C289" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D289" t="s">
         <v>28</v>
@@ -10465,18 +10462,21 @@
         <v>#N/A</v>
       </c>
       <c r="G289" t="s">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="H289" s="2">
-        <v>9.99</v>
+        <v>5.21</v>
       </c>
     </row>
     <row r="290" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A290">
+        <v>1612</v>
+      </c>
       <c r="B290" t="s">
         <v>62</v>
       </c>
       <c r="C290" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D290" t="s">
         <v>28</v>
@@ -10488,19 +10488,22 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="H290" s="2" t="e">
-        <v>#N/A</v>
+      <c r="G290" t="s">
+        <v>79</v>
+      </c>
+      <c r="H290" s="2">
+        <v>6.58</v>
       </c>
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A291">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="B291" t="s">
         <v>62</v>
       </c>
       <c r="C291" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D291" t="s">
         <v>28</v>
@@ -10513,21 +10516,24 @@
         <v>#N/A</v>
       </c>
       <c r="G291" t="s">
-        <v>168</v>
+        <v>86</v>
       </c>
       <c r="H291" s="2">
-        <v>14.3</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A292">
+        <v>1614</v>
+      </c>
       <c r="B292" t="s">
         <v>62</v>
       </c>
       <c r="C292" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D292" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="E292" s="1" t="s">
         <v>322</v>
@@ -10536,22 +10542,22 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
+      <c r="G292" t="s">
+        <v>94</v>
+      </c>
       <c r="H292" s="2">
-        <v>4.2699999999999996</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A293">
-        <v>1621</v>
-      </c>
       <c r="B293" t="s">
         <v>62</v>
       </c>
       <c r="C293" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D293" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="E293" s="1" t="s">
         <v>322</v>
@@ -10560,25 +10566,22 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="G293" t="s">
-        <v>113</v>
-      </c>
-      <c r="H293" s="2">
-        <v>4.6399999999999997</v>
+      <c r="H293" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A294">
-        <v>1622</v>
+        <v>1615</v>
       </c>
       <c r="B294" t="s">
         <v>62</v>
       </c>
       <c r="C294" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D294" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="E294" s="1" t="s">
         <v>322</v>
@@ -10588,21 +10591,18 @@
         <v>#N/A</v>
       </c>
       <c r="G294" t="s">
-        <v>76</v>
+        <v>168</v>
       </c>
       <c r="H294" s="2">
-        <v>5.74</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A295">
-        <v>1623</v>
-      </c>
       <c r="B295" t="s">
         <v>62</v>
       </c>
       <c r="C295" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D295" t="s">
         <v>43</v>
@@ -10614,22 +10614,19 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="G295" t="s">
-        <v>82</v>
-      </c>
       <c r="H295" s="2">
-        <v>6.57</v>
+        <v>4.2699999999999996</v>
       </c>
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A296">
-        <v>1624</v>
+        <v>1621</v>
       </c>
       <c r="B296" t="s">
         <v>62</v>
       </c>
       <c r="C296" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D296" t="s">
         <v>43</v>
@@ -10642,18 +10639,21 @@
         <v>#N/A</v>
       </c>
       <c r="G296" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="H296" s="2">
-        <v>8.4499999999999993</v>
+        <v>4.6399999999999997</v>
       </c>
     </row>
     <row r="297" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A297">
+        <v>1622</v>
+      </c>
       <c r="B297" t="s">
         <v>62</v>
       </c>
       <c r="C297" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D297" t="s">
         <v>43</v>
@@ -10665,19 +10665,22 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="H297" s="2" t="e">
-        <v>#N/A</v>
+      <c r="G297" t="s">
+        <v>76</v>
+      </c>
+      <c r="H297" s="2">
+        <v>5.74</v>
       </c>
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A298">
-        <v>1625</v>
+        <v>1623</v>
       </c>
       <c r="B298" t="s">
         <v>62</v>
       </c>
       <c r="C298" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D298" t="s">
         <v>43</v>
@@ -10690,18 +10693,21 @@
         <v>#N/A</v>
       </c>
       <c r="G298" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="H298" s="2">
-        <v>12.58</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="299" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A299">
+        <v>1624</v>
+      </c>
       <c r="B299" t="s">
         <v>62</v>
       </c>
       <c r="C299" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D299" t="s">
         <v>43</v>
@@ -10713,19 +10719,19 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="H299" s="2" t="e">
-        <v>#N/A</v>
+      <c r="G299" t="s">
+        <v>90</v>
+      </c>
+      <c r="H299" s="2">
+        <v>8.4499999999999993</v>
       </c>
     </row>
     <row r="300" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A300">
-        <v>1626</v>
-      </c>
       <c r="B300" t="s">
         <v>62</v>
       </c>
       <c r="C300" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D300" t="s">
         <v>43</v>
@@ -10737,22 +10743,19 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="G300" t="s">
-        <v>123</v>
-      </c>
-      <c r="H300" s="2">
-        <v>6.41</v>
+      <c r="H300" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="301" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A301">
-        <v>1627</v>
+        <v>1625</v>
       </c>
       <c r="B301" t="s">
         <v>62</v>
       </c>
       <c r="C301" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D301" t="s">
         <v>43</v>
@@ -10765,21 +10768,18 @@
         <v>#N/A</v>
       </c>
       <c r="G301" t="s">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="H301" s="2">
-        <v>7.92</v>
+        <v>12.58</v>
       </c>
     </row>
     <row r="302" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A302">
-        <v>1628</v>
-      </c>
       <c r="B302" t="s">
         <v>62</v>
       </c>
       <c r="C302" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D302" t="s">
         <v>43</v>
@@ -10791,22 +10791,19 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="G302" t="s">
-        <v>147</v>
-      </c>
-      <c r="H302" s="2">
-        <v>9.3699999999999992</v>
+      <c r="H302" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="303" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A303">
-        <v>1629</v>
+        <v>1626</v>
       </c>
       <c r="B303" t="s">
         <v>62</v>
       </c>
       <c r="C303" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D303" t="s">
         <v>43</v>
@@ -10819,18 +10816,21 @@
         <v>#N/A</v>
       </c>
       <c r="G303" t="s">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="H303" s="2">
-        <v>12.03</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="304" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A304">
+        <v>1627</v>
+      </c>
       <c r="B304" t="s">
         <v>62</v>
       </c>
       <c r="C304" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D304" t="s">
         <v>43</v>
@@ -10842,19 +10842,22 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="H304" s="2" t="e">
-        <v>#N/A</v>
+      <c r="G304" t="s">
+        <v>134</v>
+      </c>
+      <c r="H304" s="2">
+        <v>7.92</v>
       </c>
     </row>
     <row r="305" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A305">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="B305" t="s">
         <v>62</v>
       </c>
       <c r="C305" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D305" t="s">
         <v>43</v>
@@ -10867,21 +10870,24 @@
         <v>#N/A</v>
       </c>
       <c r="G305" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="H305" s="2">
-        <v>17.34</v>
+        <v>9.3699999999999992</v>
       </c>
     </row>
     <row r="306" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A306">
+        <v>1629</v>
+      </c>
       <c r="B306" t="s">
         <v>62</v>
       </c>
       <c r="C306" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="D306" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="E306" s="1" t="s">
         <v>322</v>
@@ -10890,73 +10896,67 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="H306">
-        <v>3.66</v>
+      <c r="G306" t="s">
+        <v>95</v>
+      </c>
+      <c r="H306" s="2">
+        <v>12.03</v>
       </c>
     </row>
     <row r="307" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A307">
-        <v>414</v>
-      </c>
       <c r="B307" t="s">
         <v>62</v>
       </c>
       <c r="C307" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="D307" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="E307" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F307">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>110</v>
-      </c>
-      <c r="G307" t="s">
-        <v>114</v>
-      </c>
-      <c r="H307" s="2">
-        <v>3.85</v>
+      <c r="F307" t="e">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H307" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="308" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A308">
-        <v>476</v>
+        <v>1630</v>
       </c>
       <c r="B308" t="s">
         <v>62</v>
       </c>
       <c r="C308" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="D308" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="E308" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F308">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>86</v>
+      <c r="F308" t="e">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>#N/A</v>
       </c>
       <c r="G308" t="s">
-        <v>125</v>
-      </c>
-      <c r="H308">
-        <v>4.91</v>
+        <v>169</v>
+      </c>
+      <c r="H308" s="2">
+        <v>17.34</v>
       </c>
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A309">
-        <v>419</v>
-      </c>
       <c r="B309" t="s">
         <v>62</v>
       </c>
       <c r="C309" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D309" t="s">
         <v>58</v>
@@ -10964,26 +10964,23 @@
       <c r="E309" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F309">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>70</v>
-      </c>
-      <c r="G309" t="s">
-        <v>136</v>
-      </c>
-      <c r="H309" s="2">
-        <v>5.47</v>
+      <c r="F309" t="e">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H309">
+        <v>3.66</v>
       </c>
     </row>
     <row r="310" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A310">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="B310" t="s">
         <v>62</v>
       </c>
       <c r="C310" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D310" t="s">
         <v>58</v>
@@ -10993,21 +10990,24 @@
       </c>
       <c r="F310">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>52</v>
+        <v>110</v>
       </c>
       <c r="G310" t="s">
-        <v>150</v>
+        <v>114</v>
       </c>
       <c r="H310" s="2">
-        <v>7.03</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="311" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A311">
+        <v>476</v>
+      </c>
       <c r="B311" t="s">
         <v>62</v>
       </c>
       <c r="C311" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D311" t="s">
         <v>58</v>
@@ -11015,23 +11015,26 @@
       <c r="E311" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F311" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H311" s="2" t="e">
-        <v>#N/A</v>
+      <c r="F311">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>86</v>
+      </c>
+      <c r="G311" t="s">
+        <v>125</v>
+      </c>
+      <c r="H311">
+        <v>4.91</v>
       </c>
     </row>
     <row r="312" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A312">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="B312" t="s">
         <v>62</v>
       </c>
       <c r="C312" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D312" t="s">
         <v>58</v>
@@ -11041,21 +11044,24 @@
       </c>
       <c r="F312">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="G312" t="s">
-        <v>158</v>
-      </c>
-      <c r="H312">
-        <v>10.74</v>
+        <v>136</v>
+      </c>
+      <c r="H312" s="2">
+        <v>5.47</v>
       </c>
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A313">
+        <v>423</v>
+      </c>
       <c r="B313" t="s">
         <v>62</v>
       </c>
       <c r="C313" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D313" t="s">
         <v>58</v>
@@ -11063,23 +11069,23 @@
       <c r="E313" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F313" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H313" s="2" t="e">
-        <v>#N/A</v>
+      <c r="F313">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>52</v>
+      </c>
+      <c r="G313" t="s">
+        <v>150</v>
+      </c>
+      <c r="H313" s="2">
+        <v>7.03</v>
       </c>
     </row>
     <row r="314" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A314">
-        <v>417</v>
-      </c>
       <c r="B314" t="s">
         <v>62</v>
       </c>
       <c r="C314" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D314" t="s">
         <v>58</v>
@@ -11087,26 +11093,23 @@
       <c r="E314" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F314">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>86</v>
-      </c>
-      <c r="G314" t="s">
-        <v>118</v>
-      </c>
-      <c r="H314" s="2">
-        <v>5.38</v>
+      <c r="F314" t="e">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H314" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="315" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A315">
-        <v>474</v>
+        <v>427</v>
       </c>
       <c r="B315" t="s">
         <v>62</v>
       </c>
       <c r="C315" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D315" t="s">
         <v>58</v>
@@ -11116,24 +11119,21 @@
       </c>
       <c r="F315">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="G315" t="s">
-        <v>130</v>
-      </c>
-      <c r="H315" s="2">
-        <v>6.78</v>
+        <v>158</v>
+      </c>
+      <c r="H315">
+        <v>10.74</v>
       </c>
     </row>
     <row r="316" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A316">
-        <v>421</v>
-      </c>
       <c r="B316" t="s">
         <v>62</v>
       </c>
       <c r="C316" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D316" t="s">
         <v>58</v>
@@ -11141,26 +11141,23 @@
       <c r="E316" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F316">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>60</v>
-      </c>
-      <c r="G316" t="s">
-        <v>144</v>
-      </c>
-      <c r="H316" s="2">
-        <v>7.94</v>
+      <c r="F316" t="e">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H316" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="317" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A317">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="B317" t="s">
         <v>62</v>
       </c>
       <c r="C317" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D317" t="s">
         <v>58</v>
@@ -11170,21 +11167,24 @@
       </c>
       <c r="F317">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>44</v>
+        <v>86</v>
       </c>
       <c r="G317" t="s">
-        <v>154</v>
+        <v>118</v>
       </c>
       <c r="H317" s="2">
-        <v>10.3</v>
+        <v>5.38</v>
       </c>
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A318">
+        <v>474</v>
+      </c>
       <c r="B318" t="s">
         <v>62</v>
       </c>
       <c r="C318" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D318" t="s">
         <v>58</v>
@@ -11192,23 +11192,26 @@
       <c r="E318" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F318" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H318" s="2" t="e">
-        <v>#N/A</v>
+      <c r="F318">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>70</v>
+      </c>
+      <c r="G318" t="s">
+        <v>130</v>
+      </c>
+      <c r="H318" s="2">
+        <v>6.78</v>
       </c>
     </row>
     <row r="319" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A319">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="B319" t="s">
         <v>62</v>
       </c>
       <c r="C319" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D319" t="s">
         <v>58</v>
@@ -11218,99 +11221,96 @@
       </c>
       <c r="F319">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="G319" t="s">
-        <v>162</v>
-      </c>
-      <c r="H319">
-        <v>14.74</v>
+        <v>144</v>
+      </c>
+      <c r="H319" s="2">
+        <v>7.94</v>
       </c>
     </row>
     <row r="320" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A320">
+        <v>425</v>
+      </c>
       <c r="B320" t="s">
         <v>62</v>
       </c>
       <c r="C320" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D320" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E320" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F320" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>#N/A</v>
+      <c r="F320">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>44</v>
+      </c>
+      <c r="G320" t="s">
+        <v>154</v>
       </c>
       <c r="H320" s="2">
-        <v>4.2699999999999996</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="321" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A321">
-        <v>416</v>
-      </c>
       <c r="B321" t="s">
         <v>62</v>
       </c>
       <c r="C321" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D321" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E321" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F321">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>100</v>
-      </c>
-      <c r="G321" t="s">
-        <v>115</v>
-      </c>
-      <c r="H321" s="2">
-        <v>4.6399999999999997</v>
+      <c r="F321" t="e">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H321" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="322" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A322">
-        <v>477</v>
+        <v>429</v>
       </c>
       <c r="B322" t="s">
         <v>62</v>
       </c>
       <c r="C322" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D322" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E322" s="1" t="s">
         <v>322</v>
       </c>
       <c r="F322">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G322" t="s">
-        <v>128</v>
-      </c>
-      <c r="H322" s="2">
-        <v>5.74</v>
+        <v>162</v>
+      </c>
+      <c r="H322">
+        <v>14.74</v>
       </c>
     </row>
     <row r="323" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A323">
-        <v>420</v>
-      </c>
       <c r="B323" t="s">
         <v>62</v>
       </c>
       <c r="C323" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D323" t="s">
         <v>59</v>
@@ -11318,26 +11318,23 @@
       <c r="E323" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F323">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>66</v>
-      </c>
-      <c r="G323" t="s">
-        <v>142</v>
+      <c r="F323" t="e">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>#N/A</v>
       </c>
       <c r="H323" s="2">
-        <v>6.57</v>
+        <v>4.2699999999999996</v>
       </c>
     </row>
     <row r="324" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A324">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="B324" t="s">
         <v>62</v>
       </c>
       <c r="C324" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D324" t="s">
         <v>59</v>
@@ -11347,21 +11344,24 @@
       </c>
       <c r="F324">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="G324" t="s">
-        <v>151</v>
+        <v>115</v>
       </c>
       <c r="H324" s="2">
-        <v>8.4499999999999993</v>
+        <v>4.6399999999999997</v>
       </c>
     </row>
     <row r="325" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A325">
+        <v>477</v>
+      </c>
       <c r="B325" t="s">
         <v>62</v>
       </c>
       <c r="C325" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D325" t="s">
         <v>59</v>
@@ -11369,23 +11369,26 @@
       <c r="E325" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F325" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H325" s="2" t="e">
-        <v>#N/A</v>
+      <c r="F325">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G325" t="s">
+        <v>128</v>
+      </c>
+      <c r="H325" s="2">
+        <v>5.74</v>
       </c>
     </row>
     <row r="326" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A326">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="B326" t="s">
         <v>62</v>
       </c>
       <c r="C326" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D326" t="s">
         <v>59</v>
@@ -11395,21 +11398,24 @@
       </c>
       <c r="F326">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="G326" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="H326" s="2">
-        <v>12.58</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="327" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A327">
+        <v>424</v>
+      </c>
       <c r="B327" t="s">
         <v>62</v>
       </c>
       <c r="C327" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D327" t="s">
         <v>59</v>
@@ -11417,23 +11423,23 @@
       <c r="E327" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F327" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H327" s="2" t="e">
-        <v>#N/A</v>
+      <c r="F327">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>48</v>
+      </c>
+      <c r="G327" t="s">
+        <v>151</v>
+      </c>
+      <c r="H327" s="2">
+        <v>8.4499999999999993</v>
       </c>
     </row>
     <row r="328" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A328">
-        <v>418</v>
-      </c>
       <c r="B328" t="s">
         <v>62</v>
       </c>
       <c r="C328" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D328" t="s">
         <v>59</v>
@@ -11441,26 +11447,23 @@
       <c r="E328" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F328">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="G328" t="s">
-        <v>119</v>
-      </c>
-      <c r="H328" s="2">
-        <v>6.41</v>
+      <c r="F328" t="e">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H328" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="329" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A329">
-        <v>475</v>
+        <v>428</v>
       </c>
       <c r="B329" t="s">
         <v>62</v>
       </c>
       <c r="C329" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D329" t="s">
         <v>59</v>
@@ -11470,24 +11473,21 @@
       </c>
       <c r="F329">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G329" t="s">
-        <v>131</v>
+        <v>159</v>
       </c>
       <c r="H329" s="2">
-        <v>7.92</v>
+        <v>12.58</v>
       </c>
     </row>
     <row r="330" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A330">
-        <v>422</v>
-      </c>
       <c r="B330" t="s">
         <v>62</v>
       </c>
       <c r="C330" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D330" t="s">
         <v>59</v>
@@ -11495,26 +11495,23 @@
       <c r="E330" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F330">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="G330" t="s">
-        <v>146</v>
-      </c>
-      <c r="H330" s="2">
-        <v>9.3699999999999992</v>
+      <c r="F330" t="e">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H330" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="331" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A331">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="B331" t="s">
         <v>62</v>
       </c>
       <c r="C331" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D331" t="s">
         <v>59</v>
@@ -11527,18 +11524,21 @@
         <v>0</v>
       </c>
       <c r="G331" t="s">
-        <v>156</v>
+        <v>119</v>
       </c>
       <c r="H331" s="2">
-        <v>12.03</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="332" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A332">
+        <v>475</v>
+      </c>
       <c r="B332" t="s">
         <v>62</v>
       </c>
       <c r="C332" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D332" t="s">
         <v>59</v>
@@ -11546,23 +11546,26 @@
       <c r="E332" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F332" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H332" s="2" t="e">
-        <v>#N/A</v>
+      <c r="F332">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G332" t="s">
+        <v>131</v>
+      </c>
+      <c r="H332" s="2">
+        <v>7.92</v>
       </c>
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A333">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="B333" t="s">
         <v>62</v>
       </c>
       <c r="C333" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D333" t="s">
         <v>59</v>
@@ -11575,45 +11578,48 @@
         <v>0</v>
       </c>
       <c r="G333" t="s">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="H333" s="2">
-        <v>17.34</v>
+        <v>9.3699999999999992</v>
       </c>
     </row>
     <row r="334" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A334">
+        <v>426</v>
+      </c>
       <c r="B334" t="s">
         <v>62</v>
       </c>
       <c r="C334" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="D334" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E334" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F334" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>#N/A</v>
+      <c r="F334">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G334" t="s">
+        <v>156</v>
       </c>
       <c r="H334" s="2">
-        <v>3.66</v>
+        <v>12.03</v>
       </c>
     </row>
     <row r="335" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A335">
-        <v>1666</v>
-      </c>
       <c r="B335" t="s">
         <v>62</v>
       </c>
       <c r="C335" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="D335" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E335" s="1" t="s">
         <v>322</v>
@@ -11622,49 +11628,43 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="G335" t="s">
-        <v>69</v>
-      </c>
-      <c r="H335" s="2">
-        <v>3.97</v>
+      <c r="H335" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="336" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A336">
-        <v>1667</v>
+        <v>430</v>
       </c>
       <c r="B336" t="s">
         <v>62</v>
       </c>
       <c r="C336" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="D336" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E336" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F336" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>#N/A</v>
+      <c r="F336">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>0</v>
       </c>
       <c r="G336" t="s">
-        <v>124</v>
+        <v>163</v>
       </c>
       <c r="H336" s="2">
-        <v>4.91</v>
+        <v>17.34</v>
       </c>
     </row>
     <row r="337" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A337">
-        <v>1668</v>
-      </c>
       <c r="B337" t="s">
         <v>62</v>
       </c>
       <c r="C337" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D337" t="s">
         <v>60</v>
@@ -11676,22 +11676,19 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="G337" t="s">
-        <v>80</v>
-      </c>
       <c r="H337" s="2">
-        <v>5.63</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="338" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A338">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="B338" t="s">
         <v>62</v>
       </c>
       <c r="C338" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D338" t="s">
         <v>60</v>
@@ -11704,18 +11701,21 @@
         <v>#N/A</v>
       </c>
       <c r="G338" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="H338" s="2">
-        <v>7.25</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="339" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A339">
+        <v>1667</v>
+      </c>
       <c r="B339" t="s">
         <v>62</v>
       </c>
       <c r="C339" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D339" t="s">
         <v>60</v>
@@ -11727,19 +11727,22 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="H339" s="2" t="e">
-        <v>#N/A</v>
+      <c r="G339" t="s">
+        <v>124</v>
+      </c>
+      <c r="H339" s="2">
+        <v>4.91</v>
       </c>
     </row>
     <row r="340" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A340">
-        <v>1670</v>
+        <v>1668</v>
       </c>
       <c r="B340" t="s">
         <v>62</v>
       </c>
       <c r="C340" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D340" t="s">
         <v>60</v>
@@ -11752,18 +11755,21 @@
         <v>#N/A</v>
       </c>
       <c r="G340" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="H340" s="2">
-        <v>10.74</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="341" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A341">
+        <v>1669</v>
+      </c>
       <c r="B341" t="s">
         <v>62</v>
       </c>
       <c r="C341" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D341" t="s">
         <v>60</v>
@@ -11775,19 +11781,19 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="H341" s="2" t="e">
-        <v>#N/A</v>
+      <c r="G341" t="s">
+        <v>87</v>
+      </c>
+      <c r="H341" s="2">
+        <v>7.25</v>
       </c>
     </row>
     <row r="342" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A342">
-        <v>1671</v>
-      </c>
       <c r="B342" t="s">
         <v>62</v>
       </c>
       <c r="C342" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D342" t="s">
         <v>60</v>
@@ -11799,22 +11805,19 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="G342" t="s">
-        <v>71</v>
-      </c>
-      <c r="H342" s="2">
-        <v>5.38</v>
+      <c r="H342" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="343" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A343">
-        <v>1672</v>
+        <v>1670</v>
       </c>
       <c r="B343" t="s">
         <v>62</v>
       </c>
       <c r="C343" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D343" t="s">
         <v>60</v>
@@ -11827,21 +11830,18 @@
         <v>#N/A</v>
       </c>
       <c r="G343" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="H343" s="2">
-        <v>6.78</v>
+        <v>10.74</v>
       </c>
     </row>
     <row r="344" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A344">
-        <v>1673</v>
-      </c>
       <c r="B344" t="s">
         <v>62</v>
       </c>
       <c r="C344" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D344" t="s">
         <v>60</v>
@@ -11853,22 +11853,19 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="G344" t="s">
-        <v>83</v>
-      </c>
-      <c r="H344" s="2">
-        <v>7.94</v>
+      <c r="H344" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A345">
-        <v>1674</v>
+        <v>1671</v>
       </c>
       <c r="B345" t="s">
         <v>62</v>
       </c>
       <c r="C345" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D345" t="s">
         <v>60</v>
@@ -11881,18 +11878,21 @@
         <v>#N/A</v>
       </c>
       <c r="G345" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="H345" s="2">
-        <v>10.3</v>
+        <v>5.38</v>
       </c>
     </row>
     <row r="346" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A346">
+        <v>1672</v>
+      </c>
       <c r="B346" t="s">
         <v>62</v>
       </c>
       <c r="C346" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D346" t="s">
         <v>60</v>
@@ -11904,19 +11904,22 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="H346" s="2" t="e">
-        <v>#N/A</v>
+      <c r="G346" t="s">
+        <v>77</v>
+      </c>
+      <c r="H346" s="2">
+        <v>6.78</v>
       </c>
     </row>
     <row r="347" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A347">
-        <v>1675</v>
+        <v>1673</v>
       </c>
       <c r="B347" t="s">
         <v>62</v>
       </c>
       <c r="C347" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D347" t="s">
         <v>60</v>
@@ -11929,21 +11932,24 @@
         <v>#N/A</v>
       </c>
       <c r="G347" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="H347" s="2">
-        <v>14.74</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="348" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A348">
+        <v>1674</v>
+      </c>
       <c r="B348" t="s">
         <v>62</v>
       </c>
       <c r="C348" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D348" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E348" s="1" t="s">
         <v>322</v>
@@ -11952,22 +11958,22 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
+      <c r="G348" t="s">
+        <v>91</v>
+      </c>
       <c r="H348" s="2">
-        <v>4.2699999999999996</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="349" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A349">
-        <v>1676</v>
-      </c>
       <c r="B349" t="s">
         <v>62</v>
       </c>
       <c r="C349" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D349" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E349" s="1" t="s">
         <v>322</v>
@@ -11976,25 +11982,22 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="G349" t="s">
-        <v>110</v>
-      </c>
-      <c r="H349" s="2">
-        <v>4.6399999999999997</v>
+      <c r="H349" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="350" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A350">
-        <v>1677</v>
+        <v>1675</v>
       </c>
       <c r="B350" t="s">
         <v>62</v>
       </c>
       <c r="C350" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D350" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E350" s="1" t="s">
         <v>322</v>
@@ -12004,21 +12007,18 @@
         <v>#N/A</v>
       </c>
       <c r="G350" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="H350" s="2">
-        <v>5.74</v>
+        <v>14.74</v>
       </c>
     </row>
     <row r="351" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A351">
-        <v>1678</v>
-      </c>
       <c r="B351" t="s">
         <v>62</v>
       </c>
       <c r="C351" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D351" t="s">
         <v>61</v>
@@ -12030,22 +12030,19 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="G351" t="s">
-        <v>135</v>
-      </c>
       <c r="H351" s="2">
-        <v>6.57</v>
+        <v>4.2699999999999996</v>
       </c>
     </row>
     <row r="352" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A352">
-        <v>1679</v>
+        <v>1676</v>
       </c>
       <c r="B352" t="s">
         <v>62</v>
       </c>
       <c r="C352" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D352" t="s">
         <v>61</v>
@@ -12058,18 +12055,21 @@
         <v>#N/A</v>
       </c>
       <c r="G352" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="H352" s="2">
-        <v>8.4499999999999993</v>
+        <v>4.6399999999999997</v>
       </c>
     </row>
     <row r="353" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A353">
+        <v>1677</v>
+      </c>
       <c r="B353" t="s">
         <v>62</v>
       </c>
       <c r="C353" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D353" t="s">
         <v>61</v>
@@ -12081,19 +12081,22 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="H353" s="2" t="e">
-        <v>#N/A</v>
+      <c r="G353" t="s">
+        <v>73</v>
+      </c>
+      <c r="H353" s="2">
+        <v>5.74</v>
       </c>
     </row>
     <row r="354" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A354">
-        <v>1680</v>
+        <v>1678</v>
       </c>
       <c r="B354" t="s">
         <v>62</v>
       </c>
       <c r="C354" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D354" t="s">
         <v>61</v>
@@ -12106,18 +12109,21 @@
         <v>#N/A</v>
       </c>
       <c r="G354" t="s">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="H354" s="2">
-        <v>12.58</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="355" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A355">
+        <v>1679</v>
+      </c>
       <c r="B355" t="s">
         <v>62</v>
       </c>
       <c r="C355" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D355" t="s">
         <v>61</v>
@@ -12129,19 +12135,19 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="H355" s="2" t="e">
-        <v>#N/A</v>
+      <c r="G355" t="s">
+        <v>87</v>
+      </c>
+      <c r="H355" s="2">
+        <v>8.4499999999999993</v>
       </c>
     </row>
     <row r="356" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A356">
-        <v>1681</v>
-      </c>
       <c r="B356" t="s">
         <v>62</v>
       </c>
       <c r="C356" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D356" t="s">
         <v>61</v>
@@ -12153,22 +12159,19 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="G356" t="s">
-        <v>116</v>
-      </c>
-      <c r="H356" s="2">
-        <v>6.41</v>
+      <c r="H356" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="357" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A357">
-        <v>1682</v>
+        <v>1680</v>
       </c>
       <c r="B357" t="s">
         <v>62</v>
       </c>
       <c r="C357" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D357" t="s">
         <v>61</v>
@@ -12181,21 +12184,18 @@
         <v>#N/A</v>
       </c>
       <c r="G357" t="s">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="H357" s="2">
-        <v>7.92</v>
+        <v>12.58</v>
       </c>
     </row>
     <row r="358" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A358">
-        <v>1683</v>
-      </c>
       <c r="B358" t="s">
         <v>62</v>
       </c>
       <c r="C358" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D358" t="s">
         <v>61</v>
@@ -12207,22 +12207,19 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="G358" t="s">
-        <v>143</v>
-      </c>
-      <c r="H358" s="2">
-        <v>9.3699999999999992</v>
+      <c r="H358" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="359" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A359">
-        <v>1684</v>
+        <v>1681</v>
       </c>
       <c r="B359" t="s">
         <v>62</v>
       </c>
       <c r="C359" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D359" t="s">
         <v>61</v>
@@ -12235,18 +12232,21 @@
         <v>#N/A</v>
       </c>
       <c r="G359" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="H359" s="2">
-        <v>12.03</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="360" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A360">
+        <v>1682</v>
+      </c>
       <c r="B360" t="s">
         <v>62</v>
       </c>
       <c r="C360" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D360" t="s">
         <v>61</v>
@@ -12258,19 +12258,22 @@
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="H360" s="2" t="e">
-        <v>#N/A</v>
+      <c r="G360" t="s">
+        <v>129</v>
+      </c>
+      <c r="H360" s="2">
+        <v>7.92</v>
       </c>
     </row>
     <row r="361" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A361">
-        <v>1685</v>
+        <v>1683</v>
       </c>
       <c r="B361" t="s">
         <v>62</v>
       </c>
       <c r="C361" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D361" t="s">
         <v>61</v>
@@ -12283,61 +12286,55 @@
         <v>#N/A</v>
       </c>
       <c r="G361" t="s">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="H361" s="2">
-        <v>17.34</v>
+        <v>9.3699999999999992</v>
       </c>
     </row>
     <row r="362" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A362">
-        <v>4</v>
+        <v>1684</v>
       </c>
       <c r="B362" t="s">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="C362" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="D362" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E362" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F362">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>1000</v>
+      <c r="F362" t="e">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>#N/A</v>
       </c>
       <c r="G362" t="s">
-        <v>261</v>
-      </c>
-      <c r="H362" s="2" t="e">
-        <v>#N/A</v>
+        <v>91</v>
+      </c>
+      <c r="H362" s="2">
+        <v>12.03</v>
       </c>
     </row>
     <row r="363" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A363">
-        <v>731</v>
-      </c>
       <c r="B363" t="s">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="C363" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="D363" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E363" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F363">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>1000</v>
-      </c>
-      <c r="G363" t="s">
-        <v>260</v>
+      <c r="F363" t="e">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>#N/A</v>
       </c>
       <c r="H363" s="2" t="e">
         <v>#N/A</v>
@@ -12345,211 +12342,292 @@
     </row>
     <row r="364" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A364">
-        <v>730</v>
+        <v>1685</v>
       </c>
       <c r="B364" t="s">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="C364" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="D364" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E364" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F364">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>900</v>
+      <c r="F364" t="e">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>#N/A</v>
       </c>
       <c r="G364" t="s">
-        <v>263</v>
-      </c>
-      <c r="H364" s="2" t="e">
-        <v>#N/A</v>
+        <v>101</v>
+      </c>
+      <c r="H364" s="2">
+        <v>17.34</v>
       </c>
     </row>
     <row r="365" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A365">
-        <v>495</v>
-      </c>
-      <c r="B365" s="7" t="s">
-        <v>441</v>
-      </c>
-      <c r="C365" s="7" t="s">
-        <v>441</v>
-      </c>
-      <c r="D365" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F365" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>4</v>
+      </c>
+      <c r="B365" t="s">
+        <v>3</v>
+      </c>
+      <c r="C365" t="s">
+        <v>64</v>
+      </c>
+      <c r="D365" t="s">
+        <v>63</v>
+      </c>
+      <c r="E365" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="F365">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>1000</v>
+      </c>
+      <c r="G365" t="s">
+        <v>261</v>
+      </c>
+      <c r="H365" s="2" t="e">
         <v>#N/A</v>
-      </c>
-      <c r="G365" t="s">
-        <v>441</v>
-      </c>
-      <c r="H365" s="2">
-        <v>40</v>
       </c>
     </row>
     <row r="366" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A366">
-        <v>2019</v>
-      </c>
-      <c r="B366" s="7" t="s">
-        <v>442</v>
+        <v>731</v>
+      </c>
+      <c r="B366" t="s">
+        <v>3</v>
       </c>
       <c r="C366" t="s">
-        <v>20</v>
-      </c>
-      <c r="D366" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E366">
-        <v>350</v>
-      </c>
-      <c r="F366" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>66</v>
+      </c>
+      <c r="D366" t="s">
+        <v>65</v>
+      </c>
+      <c r="E366" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="F366">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>1000</v>
+      </c>
+      <c r="G366" t="s">
+        <v>260</v>
+      </c>
+      <c r="H366" s="2" t="e">
         <v>#N/A</v>
-      </c>
-      <c r="G366" t="s">
-        <v>259</v>
-      </c>
-      <c r="H366" s="2">
-        <v>22.79</v>
       </c>
     </row>
     <row r="367" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A367">
-        <v>1819</v>
-      </c>
-      <c r="B367" s="7" t="s">
-        <v>227</v>
+        <v>730</v>
+      </c>
+      <c r="B367" t="s">
+        <v>3</v>
       </c>
       <c r="C367" t="s">
-        <v>26</v>
-      </c>
-      <c r="D367" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E367">
-        <v>210</v>
+        <v>68</v>
+      </c>
+      <c r="D367" t="s">
+        <v>67</v>
+      </c>
+      <c r="E367" s="1" t="s">
+        <v>322</v>
       </c>
       <c r="F367">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>36</v>
-      </c>
-      <c r="G367" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="H367" s="2">
-        <v>16.87</v>
+        <v>900</v>
+      </c>
+      <c r="G367" t="s">
+        <v>263</v>
+      </c>
+      <c r="H367" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="368" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A368">
-        <v>2011</v>
+        <v>495</v>
       </c>
       <c r="B368" s="7" t="s">
-        <v>228</v>
+        <v>441</v>
       </c>
       <c r="C368" s="7" t="s">
-        <v>26</v>
+        <v>441</v>
       </c>
       <c r="D368" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E368">
-        <v>900</v>
+        <v>8</v>
       </c>
       <c r="F368" t="e">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
       <c r="G368" t="s">
-        <v>228</v>
+        <v>441</v>
       </c>
       <c r="H368" s="2">
-        <v>58.6</v>
+        <v>40</v>
       </c>
     </row>
     <row r="369" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A369">
-        <v>2010</v>
+        <v>2019</v>
       </c>
       <c r="B369" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="C369" s="7" t="s">
-        <v>26</v>
+        <v>442</v>
+      </c>
+      <c r="C369" t="s">
+        <v>20</v>
       </c>
       <c r="D369" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E369">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="F369" t="e">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="G369" s="7" t="s">
-        <v>228</v>
+      <c r="G369" t="s">
+        <v>259</v>
       </c>
       <c r="H369" s="2">
-        <v>25.71</v>
+        <v>22.79</v>
       </c>
     </row>
     <row r="370" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A370">
-        <v>1822</v>
+        <v>1819</v>
       </c>
       <c r="B370" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="C370" s="7" t="s">
-        <v>24</v>
+        <v>227</v>
+      </c>
+      <c r="C370" t="s">
+        <v>26</v>
       </c>
       <c r="D370" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E370">
-        <v>380</v>
+        <v>210</v>
       </c>
       <c r="F370">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G370" s="7" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="H370" s="2">
-        <v>24.51</v>
+        <v>16.87</v>
       </c>
     </row>
     <row r="371" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A371">
+        <v>2011</v>
+      </c>
+      <c r="B371" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="C371" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D371" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E371">
+        <v>900</v>
+      </c>
+      <c r="F371" t="e">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G371" t="s">
+        <v>228</v>
+      </c>
+      <c r="H371" s="2">
+        <v>58.6</v>
+      </c>
+    </row>
+    <row r="372" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A372">
+        <v>2010</v>
+      </c>
+      <c r="B372" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="C372" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D372" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E372">
+        <v>320</v>
+      </c>
+      <c r="F372" t="e">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G372" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="H372" s="2">
+        <v>25.71</v>
+      </c>
+    </row>
+    <row r="373" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A373">
+        <v>1822</v>
+      </c>
+      <c r="B373" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="C373" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D373" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E373">
+        <v>380</v>
+      </c>
+      <c r="F373">
+        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G373" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="H373" s="2">
+        <v>24.51</v>
+      </c>
+    </row>
+    <row r="374" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A374">
         <v>1797</v>
       </c>
-      <c r="B371" s="7" t="s">
+      <c r="B374" s="7" t="s">
         <v>443</v>
       </c>
-      <c r="C371" t="s">
+      <c r="C374" t="s">
         <v>13</v>
       </c>
-      <c r="D371" s="7" t="s">
+      <c r="D374" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F371">
+      <c r="F374">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
         <v>12</v>
       </c>
-      <c r="G371" s="7" t="s">
+      <c r="G374" s="7" t="s">
         <v>443</v>
       </c>
-      <c r="H371" s="2">
+      <c r="H374" s="2">
         <v>48.5</v>
       </c>
     </row>

--- a/dados/Produtos_Agrupados_Completos_conciliados.xlsx
+++ b/dados/Produtos_Agrupados_Completos_conciliados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B85C097-CBAA-4AA0-99A2-11D81725F69E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC66A33-4CD7-4298-8955-862545762BEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{86B17377-32DB-438B-8A03-02E761646E6D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{86B17377-32DB-438B-8A03-02E761646E6D}"/>
   </bookViews>
   <sheets>
     <sheet name="CONCILIADA" sheetId="3" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3080" uniqueCount="649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3081" uniqueCount="649">
   <si>
     <t>Grupo</t>
   </si>
@@ -2458,7 +2458,14 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5499586E-A189-44D8-9C58-8F69F4EC7CA4}" name="Tabela14" displayName="Tabela14" ref="A1:H374" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:H374" xr:uid="{5499586E-A189-44D8-9C58-8F69F4EC7CA4}"/>
+  <autoFilter ref="A1:H374" xr:uid="{5499586E-A189-44D8-9C58-8F69F4EC7CA4}">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="0"/>
+        <filter val="#N/D"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="8">
     <tableColumn id="2" xr3:uid="{3202AFED-4A11-4AD5-8FCF-B57F6545F53A}" uniqueName="2" name="ID_COD" queryTableFieldId="2" dataDxfId="15"/>
     <tableColumn id="1" xr3:uid="{5387F357-AA02-4B91-B30F-AB45B122F19D}" uniqueName="1" name="Grupo" queryTableFieldId="1" dataDxfId="14"/>
@@ -2492,7 +2499,13 @@
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B6E4AB22-CC81-46A5-8E9D-BA15DF99BBB0}" name="Tabela2" displayName="Tabela2" ref="A1:G331" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
-  <autoFilter ref="A1:G331" xr:uid="{B6E4AB22-CC81-46A5-8E9D-BA15DF99BBB0}"/>
+  <autoFilter ref="A1:G331" xr:uid="{B6E4AB22-CC81-46A5-8E9D-BA15DF99BBB0}">
+    <filterColumn colId="5">
+      <filters blank="1">
+        <filter val="0"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{49F9A101-1F65-4A1E-A291-21E325604A24}" name="COD" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{B6B5DE3B-A99A-4156-AA8B-3D83F4E34F3F}" name="DESCRIÇÃO" dataDxfId="5"/>
@@ -2842,7 +2855,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2869,7 +2882,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2896,7 +2909,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2923,7 +2936,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>152</v>
       </c>
@@ -2950,7 +2963,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>153</v>
       </c>
@@ -2977,7 +2990,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>154</v>
       </c>
@@ -3022,7 +3035,7 @@
       </c>
       <c r="F8">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G8" t="s">
         <v>253</v>
@@ -3031,7 +3044,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1642</v>
       </c>
@@ -3058,7 +3071,7 @@
         <v>0.62</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1643</v>
       </c>
@@ -3085,7 +3098,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>1587</v>
       </c>
@@ -3112,7 +3125,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>1588</v>
       </c>
@@ -3139,7 +3152,7 @@
         <v>5.18</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>1586</v>
       </c>
@@ -3166,7 +3179,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>157</v>
       </c>
@@ -3193,7 +3206,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>158</v>
       </c>
@@ -3220,7 +3233,7 @@
         <v>6.98</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>155</v>
       </c>
@@ -3274,7 +3287,7 @@
         <v>4.28</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>1640</v>
       </c>
@@ -3301,7 +3314,7 @@
         <v>7.96</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>1209</v>
       </c>
@@ -3412,7 +3425,7 @@
         <v>5.991428571428572</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>8</v>
       </c>
@@ -3466,7 +3479,7 @@
         <v>7.322857142857143</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>10</v>
       </c>
@@ -3493,7 +3506,7 @@
         <v>7.9885714285714293</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>11</v>
       </c>
@@ -3547,7 +3560,7 @@
         <v>9.32</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>13</v>
       </c>
@@ -3628,7 +3641,7 @@
         <v>11.317142857142857</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>16</v>
       </c>
@@ -3709,7 +3722,7 @@
         <v>13.314285714285715</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>51</v>
       </c>
@@ -3817,7 +3830,7 @@
         <v>16.525714285714287</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>55</v>
       </c>
@@ -3925,7 +3938,7 @@
         <v>19.28</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>59</v>
       </c>
@@ -4033,7 +4046,7 @@
         <v>22.034285714285719</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>1754</v>
       </c>
@@ -4078,7 +4091,7 @@
       </c>
       <c r="F47">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G47" t="s">
         <v>267</v>
@@ -4087,7 +4100,7 @@
         <v>29.207619047619044</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>307</v>
       </c>
@@ -4141,7 +4154,7 @@
         <v>8.2415384615384628</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>309</v>
       </c>
@@ -4249,7 +4262,7 @@
         <v>11.238461538461538</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>313</v>
       </c>
@@ -4276,7 +4289,7 @@
         <v>11.98</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>314</v>
       </c>
@@ -4411,7 +4424,7 @@
         <v>15.733846153846155</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>319</v>
       </c>
@@ -4438,7 +4451,7 @@
         <v>16.483076923076926</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>320</v>
       </c>
@@ -4483,7 +4496,7 @@
       </c>
       <c r="F62">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G62" t="s">
         <v>108</v>
@@ -4492,7 +4505,7 @@
         <v>18.73076923076923</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>339</v>
       </c>
@@ -4519,7 +4532,7 @@
         <v>16.579999999999998</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -4564,7 +4577,7 @@
       </c>
       <c r="F65">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G65" t="s">
         <v>286</v>
@@ -4591,7 +4604,7 @@
       </c>
       <c r="F66">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G66" t="s">
         <v>287</v>
@@ -4618,7 +4631,7 @@
       </c>
       <c r="F67">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G67" t="s">
         <v>289</v>
@@ -4807,7 +4820,7 @@
       </c>
       <c r="F74">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G74" t="s">
         <v>284</v>
@@ -4834,7 +4847,7 @@
       </c>
       <c r="F75">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G75" t="s">
         <v>280</v>
@@ -4843,7 +4856,7 @@
         <v>29.96875</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>321</v>
       </c>
@@ -4870,7 +4883,7 @@
         <v>7.9</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>322</v>
       </c>
@@ -4897,7 +4910,7 @@
         <v>8.69</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>323</v>
       </c>
@@ -4924,7 +4937,7 @@
         <v>9.48</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>324</v>
       </c>
@@ -4978,7 +4991,7 @@
         <v>11.06</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>326</v>
       </c>
@@ -5005,7 +5018,7 @@
         <v>11.85</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>327</v>
       </c>
@@ -5032,7 +5045,7 @@
         <v>12.64</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>328</v>
       </c>
@@ -5059,7 +5072,7 @@
         <v>13.43</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>329</v>
       </c>
@@ -5086,7 +5099,7 @@
         <v>14.22</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>330</v>
       </c>
@@ -5158,7 +5171,7 @@
       </c>
       <c r="F87">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G87" t="s">
         <v>319</v>
@@ -5167,7 +5180,7 @@
         <v>16.59</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>333</v>
       </c>
@@ -5221,7 +5234,7 @@
         <v>18.170000000000002</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>335</v>
       </c>
@@ -5248,7 +5261,7 @@
         <v>18.96</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>336</v>
       </c>
@@ -5275,7 +5288,7 @@
         <v>19.75</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>337</v>
       </c>
@@ -5320,7 +5333,7 @@
       </c>
       <c r="F93">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G93" t="s">
         <v>301</v>
@@ -5329,7 +5342,7 @@
         <v>13.525185185185185</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>1773</v>
       </c>
@@ -5356,7 +5369,7 @@
         <v>14.948888888888888</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>349</v>
       </c>
@@ -5401,7 +5414,7 @@
       </c>
       <c r="F96">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G96" t="s">
         <v>301</v>
@@ -5572,7 +5585,7 @@
         <v>24.20296296296296</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>73</v>
       </c>
@@ -5626,7 +5639,7 @@
         <v>31.909629629629631</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>75</v>
       </c>
@@ -5815,7 +5828,7 @@
         <v>12.499047619047618</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>82</v>
       </c>
@@ -5869,7 +5882,7 @@
         <v>13.969523809523809</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>84</v>
       </c>
@@ -5896,7 +5909,7 @@
         <v>14.704761904761904</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>85</v>
       </c>
@@ -5923,7 +5936,7 @@
         <v>15.440000000000001</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>86</v>
       </c>
@@ -5968,7 +5981,7 @@
       </c>
       <c r="F117">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G117" t="s">
         <v>195</v>
@@ -5977,7 +5990,7 @@
         <v>16.910476190476189</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>88</v>
       </c>
@@ -6004,7 +6017,7 @@
         <v>17.645714285714284</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>89</v>
       </c>
@@ -6049,7 +6062,7 @@
       </c>
       <c r="F120">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G120" t="s">
         <v>199</v>
@@ -6076,7 +6089,7 @@
       </c>
       <c r="F121">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G121" t="s">
         <v>200</v>
@@ -6103,7 +6116,7 @@
       </c>
       <c r="F122">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G122" t="s">
         <v>201</v>
@@ -6130,7 +6143,7 @@
       </c>
       <c r="F123">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G123" t="s">
         <v>202</v>
@@ -6139,7 +6152,7 @@
         <v>21.321904761904758</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>94</v>
       </c>
@@ -6184,7 +6197,7 @@
       </c>
       <c r="F125">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G125" t="s">
         <v>204</v>
@@ -6193,7 +6206,7 @@
         <v>22.792380952380952</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>96</v>
       </c>
@@ -6238,7 +6251,7 @@
       </c>
       <c r="F127">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G127" t="s">
         <v>206</v>
@@ -6247,7 +6260,7 @@
         <v>24.262857142857143</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>129</v>
       </c>
@@ -6328,7 +6341,7 @@
         <v>28.86810810810811</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>132</v>
       </c>
@@ -6373,7 +6386,7 @@
       </c>
       <c r="F132">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G132" t="s">
         <v>193</v>
@@ -6400,7 +6413,7 @@
       </c>
       <c r="F133">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G133" t="s">
         <v>184</v>
@@ -6427,7 +6440,7 @@
       </c>
       <c r="F134">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G134" t="s">
         <v>195</v>
@@ -6463,7 +6476,7 @@
         <v>32.877567567567567</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="7">
         <v>1960</v>
       </c>
@@ -6507,7 +6520,7 @@
       </c>
       <c r="F137">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G137" t="s">
         <v>188</v>
@@ -6570,7 +6583,7 @@
         <v>33.679459459459466</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>357</v>
       </c>
@@ -6615,7 +6628,7 @@
       </c>
       <c r="F141">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G141" t="s">
         <v>207</v>
@@ -6642,7 +6655,7 @@
       </c>
       <c r="F142">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G142" t="s">
         <v>209</v>
@@ -6669,7 +6682,7 @@
       </c>
       <c r="F143">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G143" t="s">
         <v>207</v>
@@ -6678,7 +6691,7 @@
         <v>18.105599999999999</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>263</v>
       </c>
@@ -6705,7 +6718,7 @@
         <v>18.86</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>264</v>
       </c>
@@ -6750,7 +6763,7 @@
       </c>
       <c r="F146">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G146" t="s">
         <v>218</v>
@@ -6759,7 +6772,7 @@
         <v>20.3688</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>266</v>
       </c>
@@ -6804,7 +6817,7 @@
       </c>
       <c r="F148">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G148" t="s">
         <v>219</v>
@@ -6831,7 +6844,7 @@
       </c>
       <c r="F149">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G149" t="s">
         <v>220</v>
@@ -6966,7 +6979,7 @@
       </c>
       <c r="F154">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G154" t="s">
         <v>207</v>
@@ -7137,7 +7150,7 @@
         <v>31.384736842105259</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>296</v>
       </c>
@@ -7164,7 +7177,7 @@
         <v>32.189473684210526</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="7">
         <v>1961</v>
       </c>
@@ -7208,7 +7221,7 @@
       </c>
       <c r="F163">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G163" t="s">
         <v>207</v>
@@ -7235,7 +7248,7 @@
       </c>
       <c r="F164">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G164" t="s">
         <v>210</v>
@@ -7271,7 +7284,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>359</v>
       </c>
@@ -7298,7 +7311,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>273</v>
       </c>
@@ -7343,7 +7356,7 @@
       </c>
       <c r="F168">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G168" t="s">
         <v>228</v>
@@ -7370,7 +7383,7 @@
       </c>
       <c r="F169">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G169" t="s">
         <v>228</v>
@@ -7379,7 +7392,7 @@
         <v>18.170000000000002</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>276</v>
       </c>
@@ -7406,7 +7419,7 @@
         <v>18.959999999999997</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>277</v>
       </c>
@@ -7451,7 +7464,7 @@
       </c>
       <c r="F172">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G172" t="s">
         <v>238</v>
@@ -7460,7 +7473,7 @@
         <v>20.54</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>279</v>
       </c>
@@ -7487,7 +7500,7 @@
         <v>19.88</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>280</v>
       </c>
@@ -7532,7 +7545,7 @@
       </c>
       <c r="F175">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G175" t="s">
         <v>228</v>
@@ -7595,7 +7608,7 @@
         <v>24.490000000000002</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>284</v>
       </c>
@@ -7649,7 +7662,7 @@
         <v>26.069999999999997</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="4">
         <v>286</v>
       </c>
@@ -7775,7 +7788,7 @@
       </c>
       <c r="F184">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G184" t="s">
         <v>227</v>
@@ -7829,7 +7842,7 @@
       </c>
       <c r="F186">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G186" t="s">
         <v>230</v>
@@ -7856,7 +7869,7 @@
       </c>
       <c r="F187">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G187" t="s">
         <v>231</v>
@@ -7883,7 +7896,7 @@
       </c>
       <c r="F188">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G188" t="s">
         <v>232</v>
@@ -7892,7 +7905,7 @@
         <v>32.136585365853655</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>300</v>
       </c>
@@ -8027,7 +8040,7 @@
         <v>36.153658536585361</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="7">
         <v>1962</v>
       </c>
@@ -8071,7 +8084,7 @@
       </c>
       <c r="F195">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G195" t="s">
         <v>227</v>
@@ -8842,7 +8855,7 @@
         <v>3.66</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>163</v>
       </c>
@@ -8869,7 +8882,7 @@
         <v>3.97</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>480</v>
       </c>
@@ -8896,7 +8909,7 @@
         <v>4.91</v>
       </c>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>164</v>
       </c>
@@ -8923,7 +8936,7 @@
         <v>5.63</v>
       </c>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>165</v>
       </c>
@@ -8971,7 +8984,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>166</v>
       </c>
@@ -9019,7 +9032,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>171</v>
       </c>
@@ -9046,7 +9059,7 @@
         <v>5.38</v>
       </c>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>478</v>
       </c>
@@ -9073,7 +9086,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>172</v>
       </c>
@@ -9100,7 +9113,7 @@
         <v>7.94</v>
       </c>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>173</v>
       </c>
@@ -9148,7 +9161,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>174</v>
       </c>
@@ -9196,7 +9209,7 @@
         <v>4.2699999999999996</v>
       </c>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>159</v>
       </c>
@@ -9223,7 +9236,7 @@
         <v>4.6399999999999997</v>
       </c>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>481</v>
       </c>
@@ -9250,7 +9263,7 @@
         <v>5.74</v>
       </c>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>160</v>
       </c>
@@ -9277,7 +9290,7 @@
         <v>6.57</v>
       </c>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>161</v>
       </c>
@@ -9325,7 +9338,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>162</v>
       </c>
@@ -9373,7 +9386,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>167</v>
       </c>
@@ -9400,7 +9413,7 @@
         <v>6.41</v>
       </c>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>479</v>
       </c>
@@ -9427,7 +9440,7 @@
         <v>7.92</v>
       </c>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>168</v>
       </c>
@@ -9454,7 +9467,7 @@
         <v>9.3699999999999992</v>
       </c>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>169</v>
       </c>
@@ -9502,7 +9515,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>170</v>
       </c>
@@ -9910,7 +9923,7 @@
         <v>4.2699999999999996</v>
       </c>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>1656</v>
       </c>
@@ -10972,7 +10985,7 @@
         <v>3.66</v>
       </c>
     </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>414</v>
       </c>
@@ -10999,7 +11012,7 @@
         <v>3.85</v>
       </c>
     </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>476</v>
       </c>
@@ -11026,7 +11039,7 @@
         <v>4.91</v>
       </c>
     </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>419</v>
       </c>
@@ -11053,7 +11066,7 @@
         <v>5.47</v>
       </c>
     </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>423</v>
       </c>
@@ -11101,7 +11114,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>427</v>
       </c>
@@ -11149,7 +11162,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>417</v>
       </c>
@@ -11176,7 +11189,7 @@
         <v>5.38</v>
       </c>
     </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>474</v>
       </c>
@@ -11203,7 +11216,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>421</v>
       </c>
@@ -11230,7 +11243,7 @@
         <v>7.94</v>
       </c>
     </row>
-    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>425</v>
       </c>
@@ -11278,7 +11291,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>429</v>
       </c>
@@ -11326,7 +11339,7 @@
         <v>4.2699999999999996</v>
       </c>
     </row>
-    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>416</v>
       </c>
@@ -11371,7 +11384,7 @@
       </c>
       <c r="F325">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="G325" t="s">
         <v>128</v>
@@ -11380,7 +11393,7 @@
         <v>5.74</v>
       </c>
     </row>
-    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>420</v>
       </c>
@@ -11407,7 +11420,7 @@
         <v>6.57</v>
       </c>
     </row>
-    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>424</v>
       </c>
@@ -11455,7 +11468,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>428</v>
       </c>
@@ -11521,7 +11534,7 @@
       </c>
       <c r="F331">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G331" t="s">
         <v>119</v>
@@ -11548,7 +11561,7 @@
       </c>
       <c r="F332">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G332" t="s">
         <v>131</v>
@@ -11575,7 +11588,7 @@
       </c>
       <c r="F333">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="G333" t="s">
         <v>146</v>
@@ -11602,7 +11615,7 @@
       </c>
       <c r="F334">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G334" t="s">
         <v>156</v>
@@ -11650,7 +11663,7 @@
       </c>
       <c r="F336">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G336" t="s">
         <v>163</v>
@@ -12367,7 +12380,7 @@
         <v>17.34</v>
       </c>
     </row>
-    <row r="365" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365">
         <v>4</v>
       </c>
@@ -12394,7 +12407,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="366" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366">
         <v>731</v>
       </c>
@@ -12421,7 +12434,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="367" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367">
         <v>730</v>
       </c>
@@ -12499,7 +12512,7 @@
         <v>22.79</v>
       </c>
     </row>
-    <row r="370" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370">
         <v>1819</v>
       </c>
@@ -12598,7 +12611,7 @@
       </c>
       <c r="F373">
         <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G373" s="7" t="s">
         <v>207</v>
@@ -12607,7 +12620,7 @@
         <v>24.51</v>
       </c>
     </row>
-    <row r="374" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374">
         <v>1797</v>
       </c>
@@ -14731,7 +14744,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9">
         <v>1</v>
       </c>
@@ -14753,7 +14766,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9">
         <v>2</v>
       </c>
@@ -14775,7 +14788,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9">
         <v>3</v>
       </c>
@@ -14797,7 +14810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <v>4</v>
       </c>
@@ -14885,7 +14898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <v>8</v>
       </c>
@@ -14931,7 +14944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
         <v>10</v>
       </c>
@@ -14955,7 +14968,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
         <v>11</v>
       </c>
@@ -15001,7 +15014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
         <v>13</v>
       </c>
@@ -15069,7 +15082,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
         <v>16</v>
       </c>
@@ -15159,7 +15172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
         <v>51</v>
       </c>
@@ -15249,7 +15262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="9">
         <v>55</v>
       </c>
@@ -15339,7 +15352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="9">
         <v>59</v>
       </c>
@@ -15407,7 +15420,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="9">
         <v>63</v>
       </c>
@@ -15431,7 +15444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="9">
         <v>73</v>
       </c>
@@ -15477,7 +15490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="9">
         <v>75</v>
       </c>
@@ -15611,7 +15624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="9">
         <v>307</v>
       </c>
@@ -15679,7 +15692,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="9">
         <v>309</v>
       </c>
@@ -15897,7 +15910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="9">
         <v>313</v>
       </c>
@@ -15921,7 +15934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="9">
         <v>313</v>
       </c>
@@ -15945,7 +15958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="9">
         <v>314</v>
       </c>
@@ -15969,7 +15982,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="9">
         <v>314</v>
       </c>
@@ -16189,7 +16202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="9">
         <v>319</v>
       </c>
@@ -16235,7 +16248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="9">
         <v>320</v>
       </c>
@@ -16281,7 +16294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="9">
         <v>321</v>
       </c>
@@ -16305,7 +16318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="9">
         <v>321</v>
       </c>
@@ -16329,7 +16342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="9">
         <v>322</v>
       </c>
@@ -16353,7 +16366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="9">
         <v>322</v>
       </c>
@@ -16377,7 +16390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="9">
         <v>323</v>
       </c>
@@ -16423,7 +16436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="9">
         <v>324</v>
       </c>
@@ -16447,7 +16460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="9">
         <v>324</v>
       </c>
@@ -16493,7 +16506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="9">
         <v>325</v>
       </c>
@@ -16517,7 +16530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="9">
         <v>326</v>
       </c>
@@ -16541,7 +16554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="9">
         <v>326</v>
       </c>
@@ -16585,7 +16598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="9">
         <v>82</v>
       </c>
@@ -16631,7 +16644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="9">
         <v>84</v>
       </c>
@@ -16655,7 +16668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="9">
         <v>85</v>
       </c>
@@ -16679,7 +16692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="9">
         <v>86</v>
       </c>
@@ -16719,13 +16732,15 @@
       <c r="E89" s="13">
         <v>0</v>
       </c>
-      <c r="F89" s="13"/>
+      <c r="F89" s="13">
+        <v>30</v>
+      </c>
       <c r="G89" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>72</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="9">
         <v>88</v>
       </c>
@@ -16749,7 +16764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="9">
         <v>89</v>
       </c>
@@ -16789,7 +16804,9 @@
       <c r="E92" s="13">
         <v>0</v>
       </c>
-      <c r="F92" s="13"/>
+      <c r="F92" s="13">
+        <v>30</v>
+      </c>
       <c r="G92" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
@@ -16811,7 +16828,9 @@
       <c r="E93" s="13">
         <v>0</v>
       </c>
-      <c r="F93" s="13"/>
+      <c r="F93" s="13">
+        <v>30</v>
+      </c>
       <c r="G93" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>120</v>
@@ -16833,7 +16852,9 @@
       <c r="E94" s="13">
         <v>0</v>
       </c>
-      <c r="F94" s="13"/>
+      <c r="F94" s="13">
+        <v>30</v>
+      </c>
       <c r="G94" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
@@ -16855,13 +16876,15 @@
       <c r="E95" s="13">
         <v>0</v>
       </c>
-      <c r="F95" s="13"/>
+      <c r="F95" s="13">
+        <v>25</v>
+      </c>
       <c r="G95" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="9">
         <v>94</v>
       </c>
@@ -16901,13 +16924,15 @@
       <c r="E97" s="13">
         <v>0</v>
       </c>
-      <c r="F97" s="13"/>
+      <c r="F97" s="13">
+        <v>25</v>
+      </c>
       <c r="G97" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="9">
         <v>96</v>
       </c>
@@ -16946,13 +16971,15 @@
       <c r="E99" s="13">
         <v>0</v>
       </c>
-      <c r="F99" s="13"/>
+      <c r="F99" s="13">
+        <v>30</v>
+      </c>
       <c r="G99" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="9">
         <v>357</v>
       </c>
@@ -16992,7 +17019,9 @@
       <c r="E101" s="13">
         <v>0</v>
       </c>
-      <c r="F101" s="13"/>
+      <c r="F101" s="13">
+        <v>30</v>
+      </c>
       <c r="G101" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
@@ -17014,7 +17043,9 @@
       <c r="E102" s="13">
         <v>0</v>
       </c>
-      <c r="F102" s="13"/>
+      <c r="F102" s="13">
+        <v>30</v>
+      </c>
       <c r="G102" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
@@ -17036,13 +17067,15 @@
       <c r="E103" s="13">
         <v>0</v>
       </c>
-      <c r="F103" s="13"/>
+      <c r="F103" s="13">
+        <v>30</v>
+      </c>
       <c r="G103" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="9">
         <v>263</v>
       </c>
@@ -17066,7 +17099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="9">
         <v>264</v>
       </c>
@@ -17106,13 +17139,15 @@
       <c r="E106" s="13">
         <v>0</v>
       </c>
-      <c r="F106" s="13"/>
+      <c r="F106" s="13">
+        <v>30</v>
+      </c>
       <c r="G106" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>30</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="9">
         <v>266</v>
       </c>
@@ -17152,7 +17187,9 @@
       <c r="E108" s="13">
         <v>0</v>
       </c>
-      <c r="F108" s="13"/>
+      <c r="F108" s="13">
+        <v>25</v>
+      </c>
       <c r="G108" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
@@ -17174,7 +17211,9 @@
       <c r="E109" s="13">
         <v>0</v>
       </c>
-      <c r="F109" s="13"/>
+      <c r="F109" s="13">
+        <v>25</v>
+      </c>
       <c r="G109" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
@@ -17268,7 +17307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="9">
         <v>273</v>
       </c>
@@ -17308,7 +17347,9 @@
       <c r="E115" s="13">
         <v>0</v>
       </c>
-      <c r="F115" s="13"/>
+      <c r="F115" s="13">
+        <v>36</v>
+      </c>
       <c r="G115" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
@@ -17330,13 +17371,15 @@
       <c r="E116" s="13">
         <v>0</v>
       </c>
-      <c r="F116" s="13"/>
+      <c r="F116" s="13">
+        <v>30</v>
+      </c>
       <c r="G116" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="9">
         <v>276</v>
       </c>
@@ -17360,7 +17403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="9">
         <v>277</v>
       </c>
@@ -17400,13 +17443,15 @@
       <c r="E119" s="13">
         <v>0</v>
       </c>
-      <c r="F119" s="13"/>
+      <c r="F119" s="13">
+        <v>30</v>
+      </c>
       <c r="G119" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="9">
         <v>279</v>
       </c>
@@ -17430,7 +17475,7 @@
         <v>2790</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="9">
         <v>280</v>
       </c>
@@ -17470,7 +17515,9 @@
       <c r="E122" s="13">
         <v>0</v>
       </c>
-      <c r="F122" s="13"/>
+      <c r="F122" s="13">
+        <v>25</v>
+      </c>
       <c r="G122" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
@@ -17520,7 +17567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="9">
         <v>284</v>
       </c>
@@ -17566,7 +17613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="9">
         <v>286</v>
       </c>
@@ -17656,7 +17703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="9">
         <v>129</v>
       </c>
@@ -17724,7 +17771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="9">
         <v>132</v>
       </c>
@@ -17764,7 +17811,9 @@
       <c r="E135" s="13">
         <v>0</v>
       </c>
-      <c r="F135" s="13"/>
+      <c r="F135" s="13">
+        <v>20</v>
+      </c>
       <c r="G135" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
@@ -17786,7 +17835,9 @@
       <c r="E136" s="13">
         <v>0</v>
       </c>
-      <c r="F136" s="13"/>
+      <c r="F136" s="13">
+        <v>20</v>
+      </c>
       <c r="G136" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>260</v>
@@ -17808,7 +17859,9 @@
       <c r="E137" s="13">
         <v>0</v>
       </c>
-      <c r="F137" s="13"/>
+      <c r="F137" s="13">
+        <v>20</v>
+      </c>
       <c r="G137" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
@@ -17850,7 +17903,9 @@
         <v>617</v>
       </c>
       <c r="E139" s="13"/>
-      <c r="F139" s="13"/>
+      <c r="F139" s="13">
+        <v>20</v>
+      </c>
       <c r="G139" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
@@ -17912,7 +17967,9 @@
       <c r="E142" s="13">
         <v>1</v>
       </c>
-      <c r="F142" s="13"/>
+      <c r="F142" s="13">
+        <v>20</v>
+      </c>
       <c r="G142" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
@@ -17934,13 +17991,15 @@
       <c r="E143" s="13">
         <v>0</v>
       </c>
-      <c r="F143" s="13"/>
+      <c r="F143" s="13">
+        <v>20</v>
+      </c>
       <c r="G143" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="9">
         <v>1779</v>
       </c>
@@ -17954,7 +18013,9 @@
         <v>617</v>
       </c>
       <c r="E144" s="13"/>
-      <c r="F144" s="13"/>
+      <c r="F144" s="13">
+        <v>20</v>
+      </c>
       <c r="G144" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
@@ -17980,7 +18041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="10">
         <v>152</v>
       </c>
@@ -18002,7 +18063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="9">
         <v>153</v>
       </c>
@@ -18024,7 +18085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="9">
         <v>154</v>
       </c>
@@ -18046,7 +18107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="9">
         <v>155</v>
       </c>
@@ -18068,7 +18129,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="9">
         <v>1586</v>
       </c>
@@ -18090,7 +18151,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="9">
         <v>1587</v>
       </c>
@@ -18112,7 +18173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="9">
         <v>1797</v>
       </c>
@@ -18134,7 +18195,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="9">
         <v>157</v>
       </c>
@@ -18156,7 +18217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="9">
         <v>158</v>
       </c>
@@ -18178,7 +18239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="9">
         <v>1656</v>
       </c>
@@ -18200,7 +18261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="9">
         <v>159</v>
       </c>
@@ -18220,7 +18281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="9">
         <v>160</v>
       </c>
@@ -18240,7 +18301,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="9">
         <v>161</v>
       </c>
@@ -18260,7 +18321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="9">
         <v>162</v>
       </c>
@@ -18280,7 +18341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="9">
         <v>163</v>
       </c>
@@ -18300,7 +18361,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="9">
         <v>164</v>
       </c>
@@ -18320,7 +18381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="9">
         <v>165</v>
       </c>
@@ -18340,7 +18401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="9">
         <v>166</v>
       </c>
@@ -18360,7 +18421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="9">
         <v>167</v>
       </c>
@@ -18380,7 +18441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="9">
         <v>168</v>
       </c>
@@ -18400,7 +18461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="9">
         <v>169</v>
       </c>
@@ -18422,7 +18483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="9">
         <v>170</v>
       </c>
@@ -18442,7 +18503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="9">
         <v>171</v>
       </c>
@@ -18462,7 +18523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="9">
         <v>172</v>
       </c>
@@ -18482,7 +18543,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="9">
         <v>173</v>
       </c>
@@ -18502,7 +18563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="9">
         <v>174</v>
       </c>
@@ -18524,7 +18585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="9">
         <v>359</v>
       </c>
@@ -18564,7 +18625,9 @@
       <c r="E173" s="13">
         <v>0</v>
       </c>
-      <c r="F173" s="13"/>
+      <c r="F173" s="13">
+        <v>30</v>
+      </c>
       <c r="G173" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>40</v>
@@ -18586,13 +18649,15 @@
       <c r="E174" s="13">
         <v>0</v>
       </c>
-      <c r="F174" s="13"/>
+      <c r="F174" s="13">
+        <v>30</v>
+      </c>
       <c r="G174" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="9">
         <v>1819</v>
       </c>
@@ -18632,7 +18697,9 @@
       <c r="E176" s="13">
         <v>0</v>
       </c>
-      <c r="F176" s="13"/>
+      <c r="F176" s="13">
+        <v>36</v>
+      </c>
       <c r="G176" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
@@ -18654,7 +18721,9 @@
       <c r="E177" s="13">
         <v>0</v>
       </c>
-      <c r="F177" s="13"/>
+      <c r="F177" s="13">
+        <v>20</v>
+      </c>
       <c r="G177" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
@@ -18814,7 +18883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="9">
         <v>296</v>
       </c>
@@ -18854,7 +18923,9 @@
       <c r="E186" s="13">
         <v>0</v>
       </c>
-      <c r="F186" s="13"/>
+      <c r="F186" s="13">
+        <v>20</v>
+      </c>
       <c r="G186" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
@@ -18876,7 +18947,9 @@
       <c r="E187" s="13">
         <v>0</v>
       </c>
-      <c r="F187" s="13"/>
+      <c r="F187" s="13">
+        <v>20</v>
+      </c>
       <c r="G187" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>40</v>
@@ -18898,13 +18971,15 @@
       <c r="E188" s="13">
         <v>0</v>
       </c>
-      <c r="F188" s="13"/>
+      <c r="F188" s="13">
+        <v>20</v>
+      </c>
       <c r="G188" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="9">
         <v>300</v>
       </c>
@@ -19024,15 +19099,19 @@
         <v>549</v>
       </c>
       <c r="C194" s="16"/>
-      <c r="D194" s="9"/>
+      <c r="D194" s="9" t="s">
+        <v>617</v>
+      </c>
       <c r="E194" s="13"/>
-      <c r="F194" s="13"/>
+      <c r="F194" s="13">
+        <v>1000</v>
+      </c>
       <c r="G194" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="9">
         <v>1642</v>
       </c>
@@ -19054,7 +19133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="9">
         <v>1643</v>
       </c>
@@ -19076,7 +19155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="9">
         <v>327</v>
       </c>
@@ -19100,7 +19179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="9">
         <v>327</v>
       </c>
@@ -19124,7 +19203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="9">
         <v>328</v>
       </c>
@@ -19164,13 +19243,15 @@
       <c r="E200" s="13">
         <v>0</v>
       </c>
-      <c r="F200" s="13"/>
+      <c r="F200" s="13">
+        <v>50</v>
+      </c>
       <c r="G200" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="9">
         <v>329</v>
       </c>
@@ -19194,7 +19275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="9">
         <v>329</v>
       </c>
@@ -19218,7 +19299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="9">
         <v>330</v>
       </c>
@@ -19242,7 +19323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="9">
         <v>330</v>
       </c>
@@ -19326,13 +19407,15 @@
       <c r="E207" s="13">
         <v>0</v>
       </c>
-      <c r="F207" s="13"/>
+      <c r="F207" s="13">
+        <v>40</v>
+      </c>
       <c r="G207" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="9">
         <v>332</v>
       </c>
@@ -19356,7 +19439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="9">
         <v>333</v>
       </c>
@@ -19418,13 +19501,15 @@
       <c r="E211" s="13">
         <v>0</v>
       </c>
-      <c r="F211" s="13"/>
+      <c r="F211" s="13">
+        <v>32</v>
+      </c>
       <c r="G211" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="9">
         <v>334</v>
       </c>
@@ -19448,7 +19533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="9">
         <v>335</v>
       </c>
@@ -19472,7 +19557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="9">
         <v>335</v>
       </c>
@@ -19496,7 +19581,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="9">
         <v>336</v>
       </c>
@@ -19520,7 +19605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="9">
         <v>336</v>
       </c>
@@ -19544,7 +19629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="9">
         <v>337</v>
       </c>
@@ -19584,13 +19669,15 @@
       <c r="E218" s="13">
         <v>0</v>
       </c>
-      <c r="F218" s="13"/>
+      <c r="F218" s="13">
+        <v>32</v>
+      </c>
       <c r="G218" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="9">
         <v>339</v>
       </c>
@@ -19614,7 +19701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="9">
         <v>339</v>
       </c>
@@ -19654,7 +19741,9 @@
       <c r="E221" s="13">
         <v>0</v>
       </c>
-      <c r="F221" s="13"/>
+      <c r="F221" s="13">
+        <v>32</v>
+      </c>
       <c r="G221" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>128</v>
@@ -19676,7 +19765,9 @@
       <c r="E222" s="13">
         <v>0</v>
       </c>
-      <c r="F222" s="13"/>
+      <c r="F222" s="13">
+        <v>32</v>
+      </c>
       <c r="G222" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
@@ -19698,7 +19789,9 @@
       <c r="E223" s="13">
         <v>0</v>
       </c>
-      <c r="F223" s="13"/>
+      <c r="F223" s="13">
+        <v>32</v>
+      </c>
       <c r="G223" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
@@ -19720,7 +19813,9 @@
       <c r="E224" s="13">
         <v>0</v>
       </c>
-      <c r="F224" s="13"/>
+      <c r="F224" s="13">
+        <v>32</v>
+      </c>
       <c r="G224" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
@@ -19742,7 +19837,9 @@
       <c r="E225" s="13">
         <v>0</v>
       </c>
-      <c r="F225" s="13"/>
+      <c r="F225" s="13">
+        <v>32</v>
+      </c>
       <c r="G225" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
@@ -19764,7 +19861,9 @@
       <c r="E226" s="13">
         <v>0</v>
       </c>
-      <c r="F226" s="13"/>
+      <c r="F226" s="13">
+        <v>32</v>
+      </c>
       <c r="G226" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
@@ -20048,7 +20147,9 @@
         <v>617</v>
       </c>
       <c r="E239" s="13"/>
-      <c r="F239" s="13"/>
+      <c r="F239" s="13">
+        <v>32</v>
+      </c>
       <c r="G239" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
@@ -20068,13 +20169,15 @@
         <v>617</v>
       </c>
       <c r="E240" s="13"/>
-      <c r="F240" s="13"/>
+      <c r="F240" s="13">
+        <v>32</v>
+      </c>
       <c r="G240" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="9">
         <v>349</v>
       </c>
@@ -20114,7 +20217,9 @@
       <c r="E242" s="13">
         <v>0</v>
       </c>
-      <c r="F242" s="13"/>
+      <c r="F242" s="13">
+        <v>32</v>
+      </c>
       <c r="G242" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
@@ -20252,7 +20357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="9">
         <v>359</v>
       </c>
@@ -20276,7 +20381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="9">
         <v>414</v>
       </c>
@@ -20296,7 +20401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="9">
         <v>416</v>
       </c>
@@ -20316,7 +20421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="9">
         <v>417</v>
       </c>
@@ -20348,13 +20453,15 @@
       <c r="E253" s="13">
         <v>0</v>
       </c>
-      <c r="F253" s="13"/>
+      <c r="F253" s="13">
+        <v>90</v>
+      </c>
       <c r="G253" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" s="9">
         <v>419</v>
       </c>
@@ -20374,7 +20481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" s="9">
         <v>420</v>
       </c>
@@ -20394,7 +20501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="9">
         <v>421</v>
       </c>
@@ -20426,13 +20533,15 @@
       <c r="E257" s="13">
         <v>0</v>
       </c>
-      <c r="F257" s="13"/>
+      <c r="F257" s="13">
+        <v>70</v>
+      </c>
       <c r="G257" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="9">
         <v>423</v>
       </c>
@@ -20452,7 +20561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" s="9">
         <v>424</v>
       </c>
@@ -20472,7 +20581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="9">
         <v>425</v>
       </c>
@@ -20504,13 +20613,15 @@
       <c r="E261" s="13">
         <v>0</v>
       </c>
-      <c r="F261" s="13"/>
+      <c r="F261" s="13">
+        <v>60</v>
+      </c>
       <c r="G261" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" s="9">
         <v>427</v>
       </c>
@@ -20530,7 +20641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" s="9">
         <v>428</v>
       </c>
@@ -20550,7 +20661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" s="11">
         <v>429</v>
       </c>
@@ -20582,13 +20693,15 @@
       <c r="E265" s="13">
         <v>0</v>
       </c>
-      <c r="F265" s="13"/>
+      <c r="F265" s="13">
+        <v>35</v>
+      </c>
       <c r="G265" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="9">
         <v>434</v>
       </c>
@@ -20610,7 +20723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" s="9">
         <v>474</v>
       </c>
@@ -20642,13 +20755,15 @@
       <c r="E268" s="13">
         <v>0</v>
       </c>
-      <c r="F268" s="13"/>
+      <c r="F268" s="13">
+        <v>80</v>
+      </c>
       <c r="G268" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>21150</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" s="9">
         <v>476</v>
       </c>
@@ -20680,13 +20795,15 @@
       <c r="E270" s="13">
         <v>0</v>
       </c>
-      <c r="F270" s="13"/>
+      <c r="F270" s="13">
+        <v>85</v>
+      </c>
       <c r="G270" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" s="9">
         <v>478</v>
       </c>
@@ -20706,7 +20823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" s="9">
         <v>479</v>
       </c>
@@ -20726,7 +20843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" s="9">
         <v>480</v>
       </c>
@@ -20748,7 +20865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" s="9">
         <v>481</v>
       </c>
@@ -20768,7 +20885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" s="9">
         <v>584</v>
       </c>
@@ -20804,13 +20921,15 @@
       <c r="E276" s="13">
         <v>0</v>
       </c>
-      <c r="F276" s="13"/>
+      <c r="F276" s="13">
+        <v>110</v>
+      </c>
       <c r="G276" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" s="9">
         <v>586</v>
       </c>
@@ -20832,7 +20951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" s="9">
         <v>587</v>
       </c>
@@ -20868,13 +20987,15 @@
       <c r="E279" s="13">
         <v>0</v>
       </c>
-      <c r="F279" s="13"/>
+      <c r="F279" s="13">
+        <v>50</v>
+      </c>
       <c r="G279" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" s="9">
         <v>589</v>
       </c>
@@ -20910,13 +21031,15 @@
       <c r="E281" s="13">
         <v>0</v>
       </c>
-      <c r="F281" s="13"/>
+      <c r="F281" s="13">
+        <v>90</v>
+      </c>
       <c r="G281" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" s="9">
         <v>591</v>
       </c>
@@ -20938,7 +21061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" s="9">
         <v>592</v>
       </c>
@@ -20960,7 +21083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" s="9">
         <v>593</v>
       </c>
@@ -20996,7 +21119,9 @@
       <c r="E285" s="13">
         <v>0</v>
       </c>
-      <c r="F285" s="13"/>
+      <c r="F285" s="13">
+        <v>110</v>
+      </c>
       <c r="G285" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
@@ -21016,7 +21141,9 @@
       <c r="E286" s="13">
         <v>0</v>
       </c>
-      <c r="F286" s="13"/>
+      <c r="F286" s="13">
+        <v>85</v>
+      </c>
       <c r="G286" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
@@ -21036,7 +21163,9 @@
       <c r="E287" s="13">
         <v>0</v>
       </c>
-      <c r="F287" s="13"/>
+      <c r="F287" s="13">
+        <v>80</v>
+      </c>
       <c r="G287" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
@@ -21056,7 +21185,9 @@
       <c r="E288" s="13">
         <v>0</v>
       </c>
-      <c r="F288" s="13"/>
+      <c r="F288" s="13">
+        <v>70</v>
+      </c>
       <c r="G288" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
@@ -21076,7 +21207,9 @@
       <c r="E289" s="13">
         <v>0</v>
       </c>
-      <c r="F289" s="13"/>
+      <c r="F289" s="13">
+        <v>45</v>
+      </c>
       <c r="G289" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
@@ -21096,7 +21229,9 @@
       <c r="E290" s="13">
         <v>0</v>
       </c>
-      <c r="F290" s="13"/>
+      <c r="F290" s="13">
+        <v>90</v>
+      </c>
       <c r="G290" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
@@ -21116,7 +21251,9 @@
       <c r="E291" s="13">
         <v>0</v>
       </c>
-      <c r="F291" s="13"/>
+      <c r="F291" s="13">
+        <v>80</v>
+      </c>
       <c r="G291" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
@@ -21136,7 +21273,9 @@
       <c r="E292" s="13">
         <v>0</v>
       </c>
-      <c r="F292" s="13"/>
+      <c r="F292" s="13">
+        <v>70</v>
+      </c>
       <c r="G292" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
@@ -21156,7 +21295,9 @@
       <c r="E293" s="13">
         <v>0</v>
       </c>
-      <c r="F293" s="13"/>
+      <c r="F293" s="13">
+        <v>60</v>
+      </c>
       <c r="G293" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
@@ -21176,7 +21317,9 @@
       <c r="E294" s="13">
         <v>0</v>
       </c>
-      <c r="F294" s="13"/>
+      <c r="F294" s="13">
+        <v>35</v>
+      </c>
       <c r="G294" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
@@ -21196,7 +21339,9 @@
       <c r="E295" s="13">
         <v>0</v>
       </c>
-      <c r="F295" s="13"/>
+      <c r="F295" s="13">
+        <v>110</v>
+      </c>
       <c r="G295" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
@@ -21216,13 +21361,15 @@
       <c r="E296" s="13">
         <v>0</v>
       </c>
-      <c r="F296" s="13"/>
+      <c r="F296" s="13">
+        <v>110</v>
+      </c>
       <c r="G296" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" s="9">
         <v>606</v>
       </c>
@@ -21244,7 +21391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" s="9">
         <v>607</v>
       </c>
@@ -21280,13 +21427,15 @@
       <c r="E299" s="13">
         <v>0</v>
       </c>
-      <c r="F299" s="13"/>
+      <c r="F299" s="13">
+        <v>50</v>
+      </c>
       <c r="G299" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" s="9">
         <v>609</v>
       </c>
@@ -21322,13 +21471,15 @@
       <c r="E301" s="13">
         <v>0</v>
       </c>
-      <c r="F301" s="13"/>
+      <c r="F301" s="13">
+        <v>90</v>
+      </c>
       <c r="G301" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" s="9">
         <v>611</v>
       </c>
@@ -21364,13 +21515,15 @@
       <c r="E303" s="13">
         <v>0</v>
       </c>
-      <c r="F303" s="13"/>
+      <c r="F303" s="13">
+        <v>60</v>
+      </c>
       <c r="G303" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" s="9">
         <v>613</v>
       </c>
@@ -21406,7 +21559,9 @@
       <c r="E305" s="13">
         <v>0</v>
       </c>
-      <c r="F305" s="13"/>
+      <c r="F305" s="13">
+        <v>110</v>
+      </c>
       <c r="G305" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
@@ -21426,7 +21581,9 @@
       <c r="E306" s="13">
         <v>0</v>
       </c>
-      <c r="F306" s="13"/>
+      <c r="F306" s="13">
+        <v>85</v>
+      </c>
       <c r="G306" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
@@ -21446,7 +21603,9 @@
       <c r="E307" s="13">
         <v>0</v>
       </c>
-      <c r="F307" s="13"/>
+      <c r="F307" s="13">
+        <v>80</v>
+      </c>
       <c r="G307" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
@@ -21466,7 +21625,9 @@
       <c r="E308" s="13">
         <v>0</v>
       </c>
-      <c r="F308" s="13"/>
+      <c r="F308" s="13">
+        <v>70</v>
+      </c>
       <c r="G308" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
@@ -21486,7 +21647,9 @@
       <c r="E309" s="13">
         <v>0</v>
       </c>
-      <c r="F309" s="13"/>
+      <c r="F309" s="13">
+        <v>45</v>
+      </c>
       <c r="G309" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
@@ -21506,7 +21669,9 @@
       <c r="E310" s="13">
         <v>0</v>
       </c>
-      <c r="F310" s="13"/>
+      <c r="F310" s="13">
+        <v>90</v>
+      </c>
       <c r="G310" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
@@ -21526,7 +21691,9 @@
       <c r="E311" s="13">
         <v>0</v>
       </c>
-      <c r="F311" s="13"/>
+      <c r="F311" s="13">
+        <v>80</v>
+      </c>
       <c r="G311" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
@@ -21546,7 +21713,9 @@
       <c r="E312" s="13">
         <v>0</v>
       </c>
-      <c r="F312" s="13"/>
+      <c r="F312" s="13">
+        <v>70</v>
+      </c>
       <c r="G312" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
@@ -21566,7 +21735,9 @@
       <c r="E313" s="13">
         <v>0</v>
       </c>
-      <c r="F313" s="13"/>
+      <c r="F313" s="13">
+        <v>60</v>
+      </c>
       <c r="G313" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
@@ -21586,13 +21757,15 @@
       <c r="E314" s="13">
         <v>0</v>
       </c>
-      <c r="F314" s="13"/>
+      <c r="F314" s="13">
+        <v>35</v>
+      </c>
       <c r="G314" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" s="9">
         <v>730</v>
       </c>
@@ -21614,7 +21787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" s="9">
         <v>731</v>
       </c>
@@ -21646,13 +21819,15 @@
       <c r="C317" s="16"/>
       <c r="D317" s="9"/>
       <c r="E317" s="13"/>
-      <c r="F317" s="13"/>
+      <c r="F317" s="13">
+        <v>12</v>
+      </c>
       <c r="G317" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>900</v>
       </c>
     </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" s="9">
         <v>1209</v>
       </c>
@@ -21674,7 +21849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" s="9">
         <v>1588</v>
       </c>
@@ -21712,7 +21887,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" s="9">
         <v>1640</v>
       </c>
@@ -21734,7 +21909,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" s="9">
         <v>1701</v>
       </c>
@@ -21774,13 +21949,15 @@
       <c r="E323" s="13">
         <v>0</v>
       </c>
-      <c r="F323" s="13"/>
+      <c r="F323" s="13">
+        <v>40</v>
+      </c>
       <c r="G323" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" s="9">
         <v>1754</v>
       </c>
@@ -21818,7 +21995,9 @@
         <v>610</v>
       </c>
       <c r="E325" s="13"/>
-      <c r="F325" s="13"/>
+      <c r="F325" s="13">
+        <v>1000</v>
+      </c>
       <c r="G325" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
@@ -21838,7 +22017,9 @@
         <v>610</v>
       </c>
       <c r="E326" s="13"/>
-      <c r="F326" s="13"/>
+      <c r="F326" s="13">
+        <v>1000</v>
+      </c>
       <c r="G326" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>560</v>
@@ -21858,13 +22039,15 @@
         <v>610</v>
       </c>
       <c r="E327" s="13"/>
-      <c r="F327" s="13"/>
+      <c r="F327" s="13">
+        <v>1000</v>
+      </c>
       <c r="G327" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" s="9">
         <v>1773</v>
       </c>
@@ -21905,14 +22088,14 @@
         <v>0</v>
       </c>
       <c r="F329" s="13">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G329" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" s="9">
         <v>222</v>
       </c>
@@ -21932,7 +22115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" s="9">
         <v>223</v>
       </c>

--- a/dados/Produtos_Agrupados_Completos_conciliados.xlsx
+++ b/dados/Produtos_Agrupados_Completos_conciliados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC66A33-4CD7-4298-8955-862545762BEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54654794-D809-45BA-AD5C-F648611AF00B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{86B17377-32DB-438B-8A03-02E761646E6D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{86B17377-32DB-438B-8A03-02E761646E6D}"/>
   </bookViews>
   <sheets>
     <sheet name="CONCILIADA" sheetId="3" r:id="rId1"/>
@@ -2008,11 +2008,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
+    <numFmt numFmtId="8" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="&quot;gramas&quot;"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2054,6 +2055,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -2069,7 +2084,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -2086,12 +2101,126 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -2130,12 +2259,95 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="8" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="7" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="17">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="12" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="medium">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2467,11 +2679,11 @@
     </filterColumn>
   </autoFilter>
   <tableColumns count="8">
-    <tableColumn id="2" xr3:uid="{3202AFED-4A11-4AD5-8FCF-B57F6545F53A}" uniqueName="2" name="ID_COD" queryTableFieldId="2" dataDxfId="15"/>
-    <tableColumn id="1" xr3:uid="{5387F357-AA02-4B91-B30F-AB45B122F19D}" uniqueName="1" name="Grupo" queryTableFieldId="1" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{AF8B37DC-8D9E-415B-8540-844DCFD3C2C2}" uniqueName="3" name="Descrição" queryTableFieldId="3" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{15BCD1FE-6E96-4337-BF2C-1D0977BEE2EA}" uniqueName="4" name="Linha" queryTableFieldId="4" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{5AEAA593-AC57-42D0-80C6-A7ADC3170E25}" uniqueName="5" name="Gramatura" queryTableFieldId="5" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{3202AFED-4A11-4AD5-8FCF-B57F6545F53A}" uniqueName="2" name="ID_COD" queryTableFieldId="2" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{5387F357-AA02-4B91-B30F-AB45B122F19D}" uniqueName="1" name="Grupo" queryTableFieldId="1" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{AF8B37DC-8D9E-415B-8540-844DCFD3C2C2}" uniqueName="3" name="Descrição" queryTableFieldId="3" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{15BCD1FE-6E96-4337-BF2C-1D0977BEE2EA}" uniqueName="4" name="Linha" queryTableFieldId="4" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{5AEAA593-AC57-42D0-80C6-A7ADC3170E25}" uniqueName="5" name="Gramatura" queryTableFieldId="5" dataDxfId="12"/>
     <tableColumn id="6" xr3:uid="{F34DF2E2-4CF9-47F8-995C-D81C98BE9A01}" uniqueName="6" name="CX_EMB" queryTableFieldId="6"/>
     <tableColumn id="7" xr3:uid="{A488A8F9-38D4-4F27-9DEA-CC2F81D9C55C}" uniqueName="7" name="DESCRICAONF" queryTableFieldId="7"/>
     <tableColumn id="9" xr3:uid="{079BA53C-EB2B-4DA2-B65C-026F685E0107}" uniqueName="9" name="PRECO" queryTableFieldId="9" dataCellStyle="Moeda"/>
@@ -2491,14 +2703,14 @@
     <tableColumn id="5" xr3:uid="{03935235-5821-4D37-9442-36D791826C89}" name="Unid_Caixa"/>
     <tableColumn id="6" xr3:uid="{D35B3B9C-9008-4300-92B8-8167B4A2CCB6}" name="Linha"/>
     <tableColumn id="7" xr3:uid="{AC4BD377-A729-4B2F-8A6E-77B18350EAA3}" name="Gramat"/>
-    <tableColumn id="8" xr3:uid="{774C2D1E-0273-4A4C-B69B-084FE44C378A}" name="Preco"/>
+    <tableColumn id="8" xr3:uid="{774C2D1E-0273-4A4C-B69B-084FE44C378A}" name="Preco" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B6E4AB22-CC81-46A5-8E9D-BA15DF99BBB0}" name="Tabela2" displayName="Tabela2" ref="A1:G331" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B6E4AB22-CC81-46A5-8E9D-BA15DF99BBB0}" name="Tabela2" displayName="Tabela2" ref="A1:G331" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
   <autoFilter ref="A1:G331" xr:uid="{B6E4AB22-CC81-46A5-8E9D-BA15DF99BBB0}">
     <filterColumn colId="5">
       <filters blank="1">
@@ -2507,13 +2719,13 @@
     </filterColumn>
   </autoFilter>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{49F9A101-1F65-4A1E-A291-21E325604A24}" name="COD" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{B6B5DE3B-A99A-4156-AA8B-3D83F4E34F3F}" name="DESCRIÇÃO" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{3D38594D-4732-42D1-8F09-82A15D4753CB}" name="PESO" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{73AD5E7C-295D-4E24-AF22-1C03AAA6FE04}" name="TIPO" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{897DAD0D-6A3C-443B-BCC5-B43C099F2C1B}" name="VOL." dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{5A2A3043-C96F-46DD-B142-DEB2458C1999}" name="UNID." dataDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{9BDA27C3-1490-4741-A5E9-29B583E36E56}" name="TOTAL" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{49F9A101-1F65-4A1E-A291-21E325604A24}" name="COD" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{B6B5DE3B-A99A-4156-AA8B-3D83F4E34F3F}" name="DESCRIÇÃO" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{3D38594D-4732-42D1-8F09-82A15D4753CB}" name="PESO" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{73AD5E7C-295D-4E24-AF22-1C03AAA6FE04}" name="TIPO" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{897DAD0D-6A3C-443B-BCC5-B43C099F2C1B}" name="VOL." dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{5A2A3043-C96F-46DD-B142-DEB2458C1999}" name="UNID." dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{9BDA27C3-1490-4741-A5E9-29B583E36E56}" name="TOTAL" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12695,7 +12907,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>8</v>
       </c>
@@ -12717,11 +12929,11 @@
       <c r="G2" t="s">
         <v>346</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="24">
         <v>6.99</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>310</v>
       </c>
@@ -12743,11 +12955,11 @@
       <c r="G3" t="s">
         <v>348</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="24">
         <v>9.74</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>326</v>
       </c>
@@ -12769,11 +12981,11 @@
       <c r="G4" t="s">
         <v>350</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="24">
         <v>11.85</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>13</v>
       </c>
@@ -12795,11 +13007,11 @@
       <c r="G5" t="s">
         <v>350</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="24">
         <v>10.88</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>313</v>
       </c>
@@ -12821,7 +13033,7 @@
       <c r="G6" t="s">
         <v>351</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="24">
         <v>11.98</v>
       </c>
     </row>
@@ -12847,11 +13059,11 @@
       <c r="G7" t="s">
         <v>352</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="36">
         <v>14.22</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>85</v>
       </c>
@@ -12873,11 +13085,11 @@
       <c r="G8" t="s">
         <v>355</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="24">
         <v>15.44</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>263</v>
       </c>
@@ -12899,11 +13111,11 @@
       <c r="G9" t="s">
         <v>356</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="24">
         <v>18.86</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>279</v>
       </c>
@@ -12925,11 +13137,11 @@
       <c r="G10" t="s">
         <v>357</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="24">
         <v>19.88</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>94</v>
       </c>
@@ -12951,11 +13163,11 @@
       <c r="G11" t="s">
         <v>358</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="24">
         <v>22.8</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>271</v>
       </c>
@@ -12977,11 +13189,11 @@
       <c r="G12" t="s">
         <v>359</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="24">
         <v>24.86</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>286</v>
       </c>
@@ -13003,11 +13215,11 @@
       <c r="G13" t="s">
         <v>360</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="24">
         <v>26.86</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1</v>
       </c>
@@ -13026,11 +13238,11 @@
       <c r="F14" t="s">
         <v>4</v>
       </c>
-      <c r="H14">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H14" s="29">
+        <v>0.41039999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2</v>
       </c>
@@ -13049,8 +13261,8 @@
       <c r="F15" t="s">
         <v>4</v>
       </c>
-      <c r="H15">
-        <v>0.4</v>
+      <c r="H15" s="26">
+        <v>0.43200000000000005</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -13072,11 +13284,11 @@
       <c r="F16" t="s">
         <v>4</v>
       </c>
-      <c r="H16">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H16" s="25">
+        <v>0.4536</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>1586</v>
       </c>
@@ -13092,11 +13304,11 @@
       <c r="F17" t="s">
         <v>4</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="35">
         <v>49.5</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1797</v>
       </c>
@@ -13112,11 +13324,11 @@
       <c r="F18" t="s">
         <v>4</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="35">
         <v>48.5</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1588</v>
       </c>
@@ -13132,8 +13344,8 @@
       <c r="F19" t="s">
         <v>4</v>
       </c>
-      <c r="H19">
-        <v>5.18</v>
+      <c r="H19" s="24">
+        <v>5.3353999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -13152,8 +13364,8 @@
       <c r="F20" t="s">
         <v>4</v>
       </c>
-      <c r="H20">
-        <v>2.8</v>
+      <c r="H20" s="23">
+        <v>2.8839999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -13175,11 +13387,11 @@
       <c r="F21" t="s">
         <v>4</v>
       </c>
-      <c r="H21">
-        <v>3.66</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H21" s="34">
+        <v>3.9528000000000003</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>1589</v>
       </c>
@@ -13198,11 +13410,11 @@
       <c r="F22" t="s">
         <v>4</v>
       </c>
-      <c r="H22">
-        <v>3.97</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H22" s="30">
+        <v>4.2876000000000003</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>1590</v>
       </c>
@@ -13221,11 +13433,11 @@
       <c r="F23" t="s">
         <v>4</v>
       </c>
-      <c r="H23">
-        <v>4.91</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H23" s="32">
+        <v>5.3028000000000004</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>1592</v>
       </c>
@@ -13244,11 +13456,11 @@
       <c r="F24" t="s">
         <v>4</v>
       </c>
-      <c r="H24">
-        <v>5.63</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H24" s="32">
+        <v>6.0804</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>1593</v>
       </c>
@@ -13267,11 +13479,11 @@
       <c r="F25" t="s">
         <v>4</v>
       </c>
-      <c r="H25">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H25" s="32">
+        <v>7.83</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>1594</v>
       </c>
@@ -13290,8 +13502,8 @@
       <c r="F26" t="s">
         <v>4</v>
       </c>
-      <c r="H26">
-        <v>10.74</v>
+      <c r="H26" s="32">
+        <v>11.5992</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -13313,11 +13525,11 @@
       <c r="F27" t="s">
         <v>4</v>
       </c>
-      <c r="H27">
-        <v>4.96</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H27" s="33">
+        <v>5.3567999999999998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>1595</v>
       </c>
@@ -13336,11 +13548,11 @@
       <c r="F28" t="s">
         <v>4</v>
       </c>
-      <c r="H28">
-        <v>5.38</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H28" s="32">
+        <v>5.8103999999999996</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>1596</v>
       </c>
@@ -13359,11 +13571,11 @@
       <c r="F29" t="s">
         <v>4</v>
       </c>
-      <c r="H29">
-        <v>6.78</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H29" s="32">
+        <v>7.3224</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>1597</v>
       </c>
@@ -13382,11 +13594,11 @@
       <c r="F30" t="s">
         <v>4</v>
       </c>
-      <c r="H30">
-        <v>7.94</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H30" s="32">
+        <v>8.5752000000000006</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>1598</v>
       </c>
@@ -13405,11 +13617,11 @@
       <c r="F31" t="s">
         <v>4</v>
       </c>
-      <c r="H31">
-        <v>10.3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H31" s="31">
+        <v>11.124000000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>1599</v>
       </c>
@@ -13428,11 +13640,11 @@
       <c r="F32" t="s">
         <v>4</v>
       </c>
-      <c r="H32">
-        <v>14.74</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H32" s="30">
+        <v>15.9192</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>1616</v>
       </c>
@@ -13451,11 +13663,11 @@
       <c r="F33" t="s">
         <v>4</v>
       </c>
-      <c r="H33">
-        <v>3.85</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H33" s="32">
+        <v>4.1580000000000004</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>1617</v>
       </c>
@@ -13474,11 +13686,11 @@
       <c r="F34" t="s">
         <v>4</v>
       </c>
-      <c r="H34">
-        <v>4.76</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H34" s="32">
+        <v>5.1407999999999996</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>1618</v>
       </c>
@@ -13497,11 +13709,11 @@
       <c r="F35" t="s">
         <v>4</v>
       </c>
-      <c r="H35">
-        <v>5.47</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H35" s="32">
+        <v>5.9075999999999995</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>1619</v>
       </c>
@@ -13520,11 +13732,11 @@
       <c r="F36" t="s">
         <v>4</v>
       </c>
-      <c r="H36">
-        <v>7.03</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H36" s="32">
+        <v>7.5924000000000005</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>1620</v>
       </c>
@@ -13543,11 +13755,11 @@
       <c r="F37" t="s">
         <v>4</v>
       </c>
-      <c r="H37">
-        <v>10.42</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H37" s="32">
+        <v>11.2536</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>1611</v>
       </c>
@@ -13566,11 +13778,11 @@
       <c r="F38" t="s">
         <v>4</v>
       </c>
-      <c r="H38">
-        <v>5.21</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H38" s="32">
+        <v>5.6268000000000002</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>1612</v>
       </c>
@@ -13589,11 +13801,11 @@
       <c r="F39" t="s">
         <v>4</v>
       </c>
-      <c r="H39">
-        <v>6.58</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H39" s="32">
+        <v>7.1063999999999998</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>1613</v>
       </c>
@@ -13612,11 +13824,11 @@
       <c r="F40" t="s">
         <v>4</v>
       </c>
-      <c r="H40">
-        <v>7.7</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H40" s="32">
+        <v>8.3160000000000007</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>1614</v>
       </c>
@@ -13635,11 +13847,11 @@
       <c r="F41" t="s">
         <v>4</v>
       </c>
-      <c r="H41">
-        <v>9.99</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H41" s="31">
+        <v>10.789200000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>1615</v>
       </c>
@@ -13658,11 +13870,11 @@
       <c r="F42" t="s">
         <v>4</v>
       </c>
-      <c r="H42">
-        <v>14.3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H42" s="30">
+        <v>15.444000000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>51</v>
       </c>
@@ -13684,11 +13896,11 @@
       <c r="G43" t="s">
         <v>403</v>
       </c>
-      <c r="H43">
+      <c r="H43" s="24">
         <v>14.46</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>339</v>
       </c>
@@ -13710,7 +13922,7 @@
       <c r="G44" t="s">
         <v>403</v>
       </c>
-      <c r="H44">
+      <c r="H44" s="24">
         <v>16.579999999999998</v>
       </c>
     </row>
@@ -13736,11 +13948,11 @@
       <c r="G45" t="s">
         <v>403</v>
       </c>
-      <c r="H45">
+      <c r="H45" s="23">
         <v>19.22</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>132</v>
       </c>
@@ -13762,11 +13974,11 @@
       <c r="G46" t="s">
         <v>404</v>
       </c>
-      <c r="H46">
+      <c r="H46" s="24">
         <v>29.67</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>294</v>
       </c>
@@ -13788,11 +14000,11 @@
       <c r="G47" t="s">
         <v>405</v>
       </c>
-      <c r="H47">
+      <c r="H47" s="24">
         <v>30.58</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>300</v>
       </c>
@@ -13814,11 +14026,11 @@
       <c r="G48" t="s">
         <v>406</v>
       </c>
-      <c r="H48">
+      <c r="H48" s="24">
         <v>32.94</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>152</v>
       </c>
@@ -13837,11 +14049,11 @@
       <c r="F49" t="s">
         <v>402</v>
       </c>
-      <c r="H49">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H49" s="29">
+        <v>0.47520000000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>153</v>
       </c>
@@ -13860,11 +14072,11 @@
       <c r="F50" t="s">
         <v>402</v>
       </c>
-      <c r="H50">
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H50" s="26">
+        <v>0.50759999999999994</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>154</v>
       </c>
@@ -13883,11 +14095,11 @@
       <c r="F51" t="s">
         <v>402</v>
       </c>
-      <c r="H51">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H51" s="26">
+        <v>0.5292</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>155</v>
       </c>
@@ -13906,11 +14118,11 @@
       <c r="G52" t="s">
         <v>408</v>
       </c>
-      <c r="H52">
+      <c r="H52" s="28">
         <v>71</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>158</v>
       </c>
@@ -13929,11 +14141,11 @@
       <c r="G53" t="s">
         <v>409</v>
       </c>
-      <c r="H53">
-        <v>6.98</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H53" s="27">
+        <v>7.1894</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>1957</v>
       </c>
@@ -13952,11 +14164,11 @@
       <c r="G54" t="s">
         <v>403</v>
       </c>
-      <c r="H54">
+      <c r="H54" s="24">
         <v>27.88</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>1958</v>
       </c>
@@ -13975,7 +14187,7 @@
       <c r="G55" t="s">
         <v>403</v>
       </c>
-      <c r="H55">
+      <c r="H55" s="24">
         <v>28.67</v>
       </c>
     </row>
@@ -13998,11 +14210,11 @@
       <c r="G56" t="s">
         <v>403</v>
       </c>
-      <c r="H56">
+      <c r="H56" s="23">
         <v>30.77</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>1960</v>
       </c>
@@ -14021,11 +14233,11 @@
       <c r="G57" t="s">
         <v>413</v>
       </c>
-      <c r="H57">
+      <c r="H57" s="24">
         <v>94.88</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>1961</v>
       </c>
@@ -14044,7 +14256,7 @@
       <c r="G58" t="s">
         <v>414</v>
       </c>
-      <c r="H58">
+      <c r="H58" s="24">
         <v>98.7</v>
       </c>
     </row>
@@ -14067,11 +14279,11 @@
       <c r="G59" t="s">
         <v>415</v>
       </c>
-      <c r="H59">
+      <c r="H59" s="23">
         <v>107.44</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>1641</v>
       </c>
@@ -14087,11 +14299,11 @@
       <c r="F60" t="s">
         <v>417</v>
       </c>
-      <c r="H60">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H60" s="26">
+        <v>0.64800000000000002</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>1642</v>
       </c>
@@ -14107,8 +14319,8 @@
       <c r="F61" t="s">
         <v>417</v>
       </c>
-      <c r="H61">
-        <v>0.62</v>
+      <c r="H61" s="26">
+        <v>0.66959999999999997</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
@@ -14127,11 +14339,11 @@
       <c r="F62" t="s">
         <v>417</v>
       </c>
-      <c r="H62">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H62" s="25">
+        <v>0.70200000000000007</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>1209</v>
       </c>
@@ -14147,11 +14359,11 @@
       <c r="G63" t="s">
         <v>421</v>
       </c>
-      <c r="H63">
+      <c r="H63" s="24">
         <v>86.5</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>1640</v>
       </c>
@@ -14167,8 +14379,8 @@
       <c r="G64" t="s">
         <v>408</v>
       </c>
-      <c r="H64">
-        <v>7.96</v>
+      <c r="H64" s="24">
+        <v>8.1988000000000003</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -14187,11 +14399,11 @@
       <c r="G65" t="s">
         <v>408</v>
       </c>
-      <c r="H65">
-        <v>4.28</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H65" s="23">
+        <v>4.4084000000000003</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>1787</v>
       </c>
@@ -14210,11 +14422,11 @@
       <c r="F66" t="s">
         <v>417</v>
       </c>
-      <c r="H66">
-        <v>4.2699999999999996</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H66" s="21">
+        <v>4.6115999999999993</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>1656</v>
       </c>
@@ -14233,11 +14445,11 @@
       <c r="F67" t="s">
         <v>417</v>
       </c>
-      <c r="H67">
-        <v>4.6399999999999997</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H67" s="21">
+        <v>5.0111999999999997</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>1657</v>
       </c>
@@ -14256,11 +14468,11 @@
       <c r="F68" t="s">
         <v>417</v>
       </c>
-      <c r="H68">
-        <v>5.74</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H68" s="20">
+        <v>6.1992000000000003</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>1658</v>
       </c>
@@ -14279,11 +14491,11 @@
       <c r="F69" t="s">
         <v>417</v>
       </c>
-      <c r="H69">
-        <v>6.57</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H69" s="20">
+        <v>7.0956000000000001</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>1659</v>
       </c>
@@ -14302,11 +14514,11 @@
       <c r="F70" t="s">
         <v>417</v>
       </c>
-      <c r="H70">
-        <v>8.4499999999999993</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H70" s="20">
+        <v>9.1259999999999994</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>1660</v>
       </c>
@@ -14325,11 +14537,11 @@
       <c r="F71" t="s">
         <v>417</v>
       </c>
-      <c r="H71">
-        <v>12.58</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H71" s="20">
+        <v>13.586399999999999</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>1974</v>
       </c>
@@ -14348,11 +14560,11 @@
       <c r="F72" t="s">
         <v>417</v>
       </c>
-      <c r="H72">
-        <v>5.9</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H72" s="20">
+        <v>6.3720000000000008</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>1661</v>
       </c>
@@ -14371,11 +14583,11 @@
       <c r="F73" t="s">
         <v>417</v>
       </c>
-      <c r="H73">
-        <v>6.41</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H73" s="20">
+        <v>6.9228000000000005</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>1662</v>
       </c>
@@ -14394,11 +14606,11 @@
       <c r="F74" t="s">
         <v>417</v>
       </c>
-      <c r="H74">
-        <v>7.92</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H74" s="20">
+        <v>8.5535999999999994</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>1663</v>
       </c>
@@ -14417,11 +14629,11 @@
       <c r="F75" t="s">
         <v>417</v>
       </c>
-      <c r="H75">
-        <v>9.3699999999999992</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H75" s="20">
+        <v>10.119599999999998</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>1664</v>
       </c>
@@ -14440,8 +14652,8 @@
       <c r="F76" t="s">
         <v>417</v>
       </c>
-      <c r="H76">
-        <v>12.03</v>
+      <c r="H76" s="20">
+        <v>12.9924</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
@@ -14463,11 +14675,11 @@
       <c r="F77" t="s">
         <v>417</v>
       </c>
-      <c r="H77">
-        <v>17.34</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H77" s="22">
+        <v>18.7272</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>1963</v>
       </c>
@@ -14486,11 +14698,11 @@
       <c r="F78" t="s">
         <v>417</v>
       </c>
-      <c r="H78">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H78" s="21">
+        <v>4.8600000000000003</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>1964</v>
       </c>
@@ -14509,11 +14721,11 @@
       <c r="F79" t="s">
         <v>417</v>
       </c>
-      <c r="H79">
-        <v>5.57</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H79" s="20">
+        <v>6.0156000000000001</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>1965</v>
       </c>
@@ -14532,11 +14744,11 @@
       <c r="F80" t="s">
         <v>417</v>
       </c>
-      <c r="H80">
-        <v>6.38</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H80" s="20">
+        <v>6.8903999999999996</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>1966</v>
       </c>
@@ -14555,11 +14767,11 @@
       <c r="F81" t="s">
         <v>417</v>
       </c>
-      <c r="H81">
-        <v>8.19</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H81" s="20">
+        <v>8.8452000000000002</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>1967</v>
       </c>
@@ -14578,11 +14790,11 @@
       <c r="F82" t="s">
         <v>417</v>
       </c>
-      <c r="H82">
-        <v>12.21</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H82" s="20">
+        <v>13.186800000000002</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>1968</v>
       </c>
@@ -14601,11 +14813,11 @@
       <c r="F83" t="s">
         <v>417</v>
       </c>
-      <c r="H83">
-        <v>6.23</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H83" s="20">
+        <v>6.7284000000000006</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>1969</v>
       </c>
@@ -14624,11 +14836,11 @@
       <c r="F84" t="s">
         <v>417</v>
       </c>
-      <c r="H84">
-        <v>7.67</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H84" s="20">
+        <v>8.2835999999999999</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>1970</v>
       </c>
@@ -14647,11 +14859,11 @@
       <c r="F85" t="s">
         <v>417</v>
       </c>
-      <c r="H85">
-        <v>9.08</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H85" s="20">
+        <v>9.8064</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>1971</v>
       </c>
@@ -14670,11 +14882,11 @@
       <c r="F86" t="s">
         <v>417</v>
       </c>
-      <c r="H86">
-        <v>11.67</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H86" s="20">
+        <v>12.6036</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>1972</v>
       </c>
@@ -14693,8 +14905,8 @@
       <c r="F87" t="s">
         <v>417</v>
       </c>
-      <c r="H87">
-        <v>16.829999999999998</v>
+      <c r="H87" s="20">
+        <v>18.176399999999997</v>
       </c>
     </row>
   </sheetData>

--- a/dados/Produtos_Agrupados_Completos_conciliados.xlsx
+++ b/dados/Produtos_Agrupados_Completos_conciliados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54654794-D809-45BA-AD5C-F648611AF00B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{415A69EE-A35D-40F2-B5B3-4C91B3AF6460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{86B17377-32DB-438B-8A03-02E761646E6D}"/>
   </bookViews>
@@ -2327,38 +2327,6 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="12" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="medium">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom style="medium">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
         <sz val="11"/>
         <color auto="1"/>
         <name val="Calibri"/>
@@ -2602,6 +2570,38 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="12" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="medium">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="164" formatCode="&quot;gramas&quot;"/>
     </dxf>
     <dxf>
@@ -2703,14 +2703,14 @@
     <tableColumn id="5" xr3:uid="{03935235-5821-4D37-9442-36D791826C89}" name="Unid_Caixa"/>
     <tableColumn id="6" xr3:uid="{D35B3B9C-9008-4300-92B8-8167B4A2CCB6}" name="Linha"/>
     <tableColumn id="7" xr3:uid="{AC4BD377-A729-4B2F-8A6E-77B18350EAA3}" name="Gramat"/>
-    <tableColumn id="8" xr3:uid="{774C2D1E-0273-4A4C-B69B-084FE44C378A}" name="Preco" dataDxfId="0"/>
+    <tableColumn id="8" xr3:uid="{774C2D1E-0273-4A4C-B69B-084FE44C378A}" name="Preco" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B6E4AB22-CC81-46A5-8E9D-BA15DF99BBB0}" name="Tabela2" displayName="Tabela2" ref="A1:G331" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B6E4AB22-CC81-46A5-8E9D-BA15DF99BBB0}" name="Tabela2" displayName="Tabela2" ref="A1:G331" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
   <autoFilter ref="A1:G331" xr:uid="{B6E4AB22-CC81-46A5-8E9D-BA15DF99BBB0}">
     <filterColumn colId="5">
       <filters blank="1">
@@ -2719,13 +2719,13 @@
     </filterColumn>
   </autoFilter>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{49F9A101-1F65-4A1E-A291-21E325604A24}" name="COD" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{B6B5DE3B-A99A-4156-AA8B-3D83F4E34F3F}" name="DESCRIÇÃO" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{3D38594D-4732-42D1-8F09-82A15D4753CB}" name="PESO" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{73AD5E7C-295D-4E24-AF22-1C03AAA6FE04}" name="TIPO" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{897DAD0D-6A3C-443B-BCC5-B43C099F2C1B}" name="VOL." dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{5A2A3043-C96F-46DD-B142-DEB2458C1999}" name="UNID." dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{9BDA27C3-1490-4741-A5E9-29B583E36E56}" name="TOTAL" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{49F9A101-1F65-4A1E-A291-21E325604A24}" name="COD" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{B6B5DE3B-A99A-4156-AA8B-3D83F4E34F3F}" name="DESCRIÇÃO" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{3D38594D-4732-42D1-8F09-82A15D4753CB}" name="PESO" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{73AD5E7C-295D-4E24-AF22-1C03AAA6FE04}" name="TIPO" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{897DAD0D-6A3C-443B-BCC5-B43C099F2C1B}" name="VOL." dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{5A2A3043-C96F-46DD-B142-DEB2458C1999}" name="UNID." dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{9BDA27C3-1490-4741-A5E9-29B583E36E56}" name="TOTAL" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>

--- a/dados/Produtos_Agrupados_Completos_conciliados.xlsx
+++ b/dados/Produtos_Agrupados_Completos_conciliados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{415A69EE-A35D-40F2-B5B3-4C91B3AF6460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04FB0A0C-1CC5-4E5D-BBCA-9CA2D9ECE2FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{86B17377-32DB-438B-8A03-02E761646E6D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{86B17377-32DB-438B-8A03-02E761646E6D}"/>
   </bookViews>
   <sheets>
     <sheet name="CONCILIADA" sheetId="3" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="DadosExternos_1" localSheetId="0" hidden="1">CONCILIADA!$A$1:$G$374</definedName>
+    <definedName name="DadosExternos_1" localSheetId="0" hidden="1">CONCILIADA!$A$1:$G$418</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3081" uniqueCount="649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3301" uniqueCount="649">
   <si>
     <t>Grupo</t>
   </si>
@@ -2220,7 +2220,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -2308,6 +2308,30 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="8" fontId="7" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2669,8 +2693,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5499586E-A189-44D8-9C58-8F69F4EC7CA4}" name="Tabela14" displayName="Tabela14" ref="A1:H374" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:H374" xr:uid="{5499586E-A189-44D8-9C58-8F69F4EC7CA4}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5499586E-A189-44D8-9C58-8F69F4EC7CA4}" name="Tabela14" displayName="Tabela14" ref="A1:H418" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:H418" xr:uid="{5499586E-A189-44D8-9C58-8F69F4EC7CA4}">
     <filterColumn colId="5">
       <filters>
         <filter val="0"/>
@@ -3028,7 +3052,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{868BC1FE-16FA-4E4B-B34E-F84713378B87}">
-  <dimension ref="A1:H374"/>
+  <dimension ref="A1:H418"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -3091,7 +3115,8 @@
         <v>254</v>
       </c>
       <c r="H2" s="2">
-        <v>0.38</v>
+        <f>VLOOKUP(A2,'Tabela de preços'!A1:H87,8,FALSE)</f>
+        <v>0.41039999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -3118,7 +3143,8 @@
         <v>258</v>
       </c>
       <c r="H3" s="2">
-        <v>0.4</v>
+        <f>VLOOKUP(A3,'Tabela de preços'!A2:H88,8,FALSE)</f>
+        <v>0.43200000000000005</v>
       </c>
     </row>
     <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -3145,7 +3171,8 @@
         <v>264</v>
       </c>
       <c r="H4" s="2">
-        <v>0.42</v>
+        <f>VLOOKUP(A4,'Tabela de preços'!A3:H89,8,FALSE)</f>
+        <v>0.4536</v>
       </c>
     </row>
     <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -3172,7 +3199,8 @@
         <v>255</v>
       </c>
       <c r="H5" s="2">
-        <v>0.44</v>
+        <f>VLOOKUP(A5,'Tabela de preços'!A4:H90,8,FALSE)</f>
+        <v>0.47520000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -3199,7 +3227,8 @@
         <v>256</v>
       </c>
       <c r="H6" s="2">
-        <v>0.47</v>
+        <f>VLOOKUP(A6,'Tabela de preços'!A5:H91,8,FALSE)</f>
+        <v>0.50759999999999994</v>
       </c>
     </row>
     <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -3226,10 +3255,11 @@
         <v>259</v>
       </c>
       <c r="H7" s="2">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <f>VLOOKUP(A7,'Tabela de preços'!A6:H92,8,FALSE)</f>
+        <v>0.5292</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1641</v>
       </c>
@@ -3253,7 +3283,8 @@
         <v>253</v>
       </c>
       <c r="H8" s="2">
-        <v>0.6</v>
+        <f>VLOOKUP(A8,'Tabela de preços'!A7:H93,8,FALSE)</f>
+        <v>0.64800000000000002</v>
       </c>
     </row>
     <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -3280,7 +3311,8 @@
         <v>257</v>
       </c>
       <c r="H9" s="2">
-        <v>0.62</v>
+        <f>VLOOKUP(A9,'Tabela de preços'!A8:H94,8,FALSE)</f>
+        <v>0.66959999999999997</v>
       </c>
     </row>
     <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -3307,7 +3339,8 @@
         <v>107</v>
       </c>
       <c r="H10" s="2">
-        <v>0.65</v>
+        <f>VLOOKUP(A10,'Tabela de preços'!A9:H95,8,FALSE)</f>
+        <v>0.70200000000000007</v>
       </c>
     </row>
     <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -3334,7 +3367,8 @@
         <v>175</v>
       </c>
       <c r="H11" s="2">
-        <v>2.8</v>
+        <f>VLOOKUP(A11,'Tabela de preços'!A10:H96,8,FALSE)</f>
+        <v>2.8839999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -3361,7 +3395,8 @@
         <v>106</v>
       </c>
       <c r="H12" s="2">
-        <v>5.18</v>
+        <f>VLOOKUP(A12,'Tabela de preços'!A11:H97,8,FALSE)</f>
+        <v>5.3353999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -3414,8 +3449,9 @@
       <c r="G14" t="s">
         <v>174</v>
       </c>
-      <c r="H14" s="2">
-        <v>2.8</v>
+      <c r="H14" s="2" t="e">
+        <f>VLOOKUP(A14,'Tabela de preços'!A13:H99,8,FALSE)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -3442,7 +3478,8 @@
         <v>176</v>
       </c>
       <c r="H15" s="2">
-        <v>6.98</v>
+        <f>VLOOKUP(A15,'Tabela de preços'!A14:H100,8,FALSE)</f>
+        <v>7.1894</v>
       </c>
     </row>
     <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -3496,7 +3533,8 @@
         <v>174</v>
       </c>
       <c r="H17" s="2">
-        <v>4.28</v>
+        <f>VLOOKUP(A17,'Tabela de preços'!A16:H102,8,FALSE)</f>
+        <v>4.4084000000000003</v>
       </c>
     </row>
     <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -4285,7 +4323,7 @@
         <v>27.880000000000003</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>1774</v>
       </c>
@@ -4690,7 +4728,7 @@
         <v>17.232307692307696</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>1690</v>
       </c>
@@ -4771,7 +4809,7 @@
         <v>17.270833333333332</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>340</v>
       </c>
@@ -4798,7 +4836,7 @@
         <v>17.961666666666662</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>341</v>
       </c>
@@ -4825,7 +4863,7 @@
         <v>18.652499999999996</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>342</v>
       </c>
@@ -5014,7 +5052,7 @@
         <v>23.488333333333333</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>1700</v>
       </c>
@@ -5041,7 +5079,7 @@
         <v>28.77</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>1697</v>
       </c>
@@ -5365,7 +5403,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>332</v>
       </c>
@@ -5527,7 +5565,7 @@
         <v>20.54</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>1699</v>
       </c>
@@ -5608,7 +5646,7 @@
         <v>19.22</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>350</v>
       </c>
@@ -6175,7 +6213,7 @@
         <v>16.175238095238093</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>87</v>
       </c>
@@ -6256,7 +6294,7 @@
         <v>18.38095238095238</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>90</v>
       </c>
@@ -6283,7 +6321,7 @@
         <v>19.116190476190475</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>91</v>
       </c>
@@ -6310,7 +6348,7 @@
         <v>19.851428571428571</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>92</v>
       </c>
@@ -6337,7 +6375,7 @@
         <v>20.586666666666666</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>93</v>
       </c>
@@ -6391,7 +6429,7 @@
         <v>22.057142857142857</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>95</v>
       </c>
@@ -6445,7 +6483,7 @@
         <v>23.527619047619048</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>97</v>
       </c>
@@ -6580,7 +6618,7 @@
         <v>29.670000000000005</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>133</v>
       </c>
@@ -6607,7 +6645,7 @@
         <v>30.471891891891893</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>134</v>
       </c>
@@ -6634,7 +6672,7 @@
         <v>31.273783783783788</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>135</v>
       </c>
@@ -6714,7 +6752,7 @@
         <v>94.88</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>1775</v>
       </c>
@@ -6822,7 +6860,7 @@
         <v>15.8424</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>358</v>
       </c>
@@ -6849,7 +6887,7 @@
         <v>16.596799999999998</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>261</v>
       </c>
@@ -6876,7 +6914,7 @@
         <v>17.351200000000002</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>262</v>
       </c>
@@ -6957,7 +6995,7 @@
         <v>19.614399999999996</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>265</v>
       </c>
@@ -7011,7 +7049,7 @@
         <v>21.123200000000001</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>267</v>
       </c>
@@ -7038,7 +7076,7 @@
         <v>21.877599999999997</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>268</v>
       </c>
@@ -7173,7 +7211,7 @@
         <v>24.895199999999999</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>1687</v>
       </c>
@@ -7415,7 +7453,7 @@
         <v>98.7</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>1778</v>
       </c>
@@ -7442,7 +7480,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>1779</v>
       </c>
@@ -7550,7 +7588,7 @@
         <v>16.59</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>274</v>
       </c>
@@ -7577,7 +7615,7 @@
         <v>17.38</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>275</v>
       </c>
@@ -7658,7 +7696,7 @@
         <v>19.75</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>278</v>
       </c>
@@ -7739,7 +7777,7 @@
         <v>22.12</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>281</v>
       </c>
@@ -7982,7 +8020,7 @@
         <v>29.229999999999997</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>1636</v>
       </c>
@@ -8036,7 +8074,7 @@
         <v>18.478536585365852</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>297</v>
       </c>
@@ -8063,7 +8101,7 @@
         <v>30.529756097560973</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>298</v>
       </c>
@@ -8090,7 +8128,7 @@
         <v>31.333170731707312</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>299</v>
       </c>
@@ -8278,7 +8316,7 @@
         <v>107.44</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>1781</v>
       </c>
@@ -11578,7 +11616,7 @@
         <v>4.6399999999999997</v>
       </c>
     </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>477</v>
       </c>
@@ -11728,7 +11766,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>418</v>
       </c>
@@ -11755,7 +11793,7 @@
         <v>6.41</v>
       </c>
     </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>475</v>
       </c>
@@ -11782,7 +11820,7 @@
         <v>7.92</v>
       </c>
     </row>
-    <row r="333" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>422</v>
       </c>
@@ -11809,7 +11847,7 @@
         <v>9.3699999999999992</v>
       </c>
     </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>426</v>
       </c>
@@ -11857,7 +11895,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>430</v>
       </c>
@@ -12805,7 +12843,7 @@
         <v>25.71</v>
       </c>
     </row>
-    <row r="373" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373">
         <v>1822</v>
       </c>
@@ -12854,6 +12892,1020 @@
       </c>
       <c r="H374" s="2">
         <v>48.5</v>
+      </c>
+    </row>
+    <row r="375" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A375" s="7">
+        <v>1644</v>
+      </c>
+      <c r="B375" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="C375" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="D375" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E375" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="F375" t="s">
+        <v>4</v>
+      </c>
+      <c r="H375" s="34">
+        <v>3.9528000000000003</v>
+      </c>
+    </row>
+    <row r="376" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A376" s="7">
+        <v>1589</v>
+      </c>
+      <c r="B376" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="C376" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="D376" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E376" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="F376" t="s">
+        <v>4</v>
+      </c>
+      <c r="H376" s="37">
+        <v>4.2876000000000003</v>
+      </c>
+    </row>
+    <row r="377" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A377" s="7">
+        <v>1590</v>
+      </c>
+      <c r="B377" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="C377" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="D377" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E377" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="F377" t="s">
+        <v>4</v>
+      </c>
+      <c r="H377" s="38">
+        <v>5.3028000000000004</v>
+      </c>
+    </row>
+    <row r="378" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A378" s="7">
+        <v>1592</v>
+      </c>
+      <c r="B378" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="C378" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="D378" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E378" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="F378" t="s">
+        <v>4</v>
+      </c>
+      <c r="H378" s="38">
+        <v>6.0804</v>
+      </c>
+    </row>
+    <row r="379" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A379" s="7">
+        <v>1593</v>
+      </c>
+      <c r="B379" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="C379" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="D379" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E379" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F379" t="s">
+        <v>4</v>
+      </c>
+      <c r="H379" s="38">
+        <v>7.83</v>
+      </c>
+    </row>
+    <row r="380" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A380" s="7">
+        <v>1594</v>
+      </c>
+      <c r="B380" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="C380" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="D380" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E380" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="F380" t="s">
+        <v>4</v>
+      </c>
+      <c r="H380" s="38">
+        <v>11.5992</v>
+      </c>
+    </row>
+    <row r="381" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A381" s="7">
+        <v>1973</v>
+      </c>
+      <c r="B381" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="C381" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="D381" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E381" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="F381" t="s">
+        <v>4</v>
+      </c>
+      <c r="H381" s="33">
+        <v>5.3567999999999998</v>
+      </c>
+    </row>
+    <row r="382" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A382" s="7">
+        <v>1595</v>
+      </c>
+      <c r="B382" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="C382" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="D382" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E382" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="F382" t="s">
+        <v>4</v>
+      </c>
+      <c r="H382" s="38">
+        <v>5.8103999999999996</v>
+      </c>
+    </row>
+    <row r="383" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A383" s="7">
+        <v>1596</v>
+      </c>
+      <c r="B383" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="C383" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="D383" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E383" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="F383" t="s">
+        <v>4</v>
+      </c>
+      <c r="H383" s="38">
+        <v>7.3224</v>
+      </c>
+    </row>
+    <row r="384" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A384" s="7">
+        <v>1597</v>
+      </c>
+      <c r="B384" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="C384" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="D384" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E384" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="F384" t="s">
+        <v>4</v>
+      </c>
+      <c r="H384" s="38">
+        <v>8.5752000000000006</v>
+      </c>
+    </row>
+    <row r="385" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A385" s="7">
+        <v>1598</v>
+      </c>
+      <c r="B385" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="C385" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="D385" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E385" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="F385" t="s">
+        <v>4</v>
+      </c>
+      <c r="H385" s="39">
+        <v>11.124000000000001</v>
+      </c>
+    </row>
+    <row r="386" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A386" s="7">
+        <v>1599</v>
+      </c>
+      <c r="B386" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="C386" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="D386" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E386" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="F386" t="s">
+        <v>4</v>
+      </c>
+      <c r="H386" s="37">
+        <v>15.9192</v>
+      </c>
+    </row>
+    <row r="387" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A387" s="7">
+        <v>1616</v>
+      </c>
+      <c r="B387" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="C387" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="D387" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E387" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="F387" t="s">
+        <v>4</v>
+      </c>
+      <c r="H387" s="38">
+        <v>4.1580000000000004</v>
+      </c>
+    </row>
+    <row r="388" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A388" s="7">
+        <v>1617</v>
+      </c>
+      <c r="B388" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="C388" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="D388" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E388" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="F388" t="s">
+        <v>4</v>
+      </c>
+      <c r="H388" s="38">
+        <v>5.1407999999999996</v>
+      </c>
+    </row>
+    <row r="389" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A389" s="7">
+        <v>1618</v>
+      </c>
+      <c r="B389" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="C389" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="D389" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E389" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F389" t="s">
+        <v>4</v>
+      </c>
+      <c r="H389" s="38">
+        <v>5.9075999999999995</v>
+      </c>
+    </row>
+    <row r="390" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A390" s="7">
+        <v>1619</v>
+      </c>
+      <c r="B390" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="C390" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="D390" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E390" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="F390" t="s">
+        <v>4</v>
+      </c>
+      <c r="H390" s="38">
+        <v>7.5924000000000005</v>
+      </c>
+    </row>
+    <row r="391" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A391" s="7">
+        <v>1620</v>
+      </c>
+      <c r="B391" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="C391" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="D391" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E391" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="F391" t="s">
+        <v>4</v>
+      </c>
+      <c r="H391" s="38">
+        <v>11.2536</v>
+      </c>
+    </row>
+    <row r="392" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A392" s="7">
+        <v>1611</v>
+      </c>
+      <c r="B392" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="C392" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="D392" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E392" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="F392" t="s">
+        <v>4</v>
+      </c>
+      <c r="H392" s="38">
+        <v>5.6268000000000002</v>
+      </c>
+    </row>
+    <row r="393" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A393" s="7">
+        <v>1612</v>
+      </c>
+      <c r="B393" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="C393" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="D393" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E393" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F393" t="s">
+        <v>4</v>
+      </c>
+      <c r="H393" s="38">
+        <v>7.1063999999999998</v>
+      </c>
+    </row>
+    <row r="394" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A394" s="7">
+        <v>1613</v>
+      </c>
+      <c r="B394" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="C394" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="D394" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E394" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="F394" t="s">
+        <v>4</v>
+      </c>
+      <c r="H394" s="38">
+        <v>8.3160000000000007</v>
+      </c>
+    </row>
+    <row r="395" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A395" s="7">
+        <v>1614</v>
+      </c>
+      <c r="B395" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="C395" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="D395" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E395" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="F395" t="s">
+        <v>4</v>
+      </c>
+      <c r="H395" s="39">
+        <v>10.789200000000001</v>
+      </c>
+    </row>
+    <row r="396" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A396" s="40">
+        <v>1615</v>
+      </c>
+      <c r="B396" s="40" t="s">
+        <v>394</v>
+      </c>
+      <c r="C396" s="40" t="s">
+        <v>392</v>
+      </c>
+      <c r="D396" s="40" t="s">
+        <v>372</v>
+      </c>
+      <c r="E396" s="41" t="s">
+        <v>400</v>
+      </c>
+      <c r="F396" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="G396" s="42"/>
+      <c r="H396" s="43">
+        <v>15.444000000000001</v>
+      </c>
+    </row>
+    <row r="397" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A397" s="7">
+        <v>1787</v>
+      </c>
+      <c r="B397" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="C397" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="D397" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E397" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="F397" t="s">
+        <v>417</v>
+      </c>
+      <c r="H397" s="44">
+        <v>4.6115999999999993</v>
+      </c>
+    </row>
+    <row r="398" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A398" s="7">
+        <v>1656</v>
+      </c>
+      <c r="B398" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="C398" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="D398" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E398" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="F398" t="s">
+        <v>417</v>
+      </c>
+      <c r="H398" s="44">
+        <v>5.0111999999999997</v>
+      </c>
+    </row>
+    <row r="399" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A399" s="7">
+        <v>1657</v>
+      </c>
+      <c r="B399" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="C399" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="D399" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E399" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="F399" t="s">
+        <v>417</v>
+      </c>
+      <c r="H399" s="45">
+        <v>6.1992000000000003</v>
+      </c>
+    </row>
+    <row r="400" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A400" s="7">
+        <v>1658</v>
+      </c>
+      <c r="B400" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="C400" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="D400" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E400" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="F400" t="s">
+        <v>417</v>
+      </c>
+      <c r="H400" s="45">
+        <v>7.0956000000000001</v>
+      </c>
+    </row>
+    <row r="401" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A401" s="7">
+        <v>1659</v>
+      </c>
+      <c r="B401" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="C401" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="D401" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E401" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F401" t="s">
+        <v>417</v>
+      </c>
+      <c r="H401" s="45">
+        <v>9.1259999999999994</v>
+      </c>
+    </row>
+    <row r="402" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A402" s="7">
+        <v>1660</v>
+      </c>
+      <c r="B402" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="C402" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="D402" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E402" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="F402" t="s">
+        <v>417</v>
+      </c>
+      <c r="H402" s="45">
+        <v>13.586399999999999</v>
+      </c>
+    </row>
+    <row r="403" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A403" s="7">
+        <v>1974</v>
+      </c>
+      <c r="B403" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="C403" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="D403" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E403" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="F403" t="s">
+        <v>417</v>
+      </c>
+      <c r="H403" s="45">
+        <v>6.3720000000000008</v>
+      </c>
+    </row>
+    <row r="404" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A404" s="7">
+        <v>1661</v>
+      </c>
+      <c r="B404" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="C404" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="D404" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E404" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="F404" t="s">
+        <v>417</v>
+      </c>
+      <c r="H404" s="45">
+        <v>6.9228000000000005</v>
+      </c>
+    </row>
+    <row r="405" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A405" s="7">
+        <v>1662</v>
+      </c>
+      <c r="B405" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="C405" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="D405" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E405" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="F405" t="s">
+        <v>417</v>
+      </c>
+      <c r="H405" s="45">
+        <v>8.5535999999999994</v>
+      </c>
+    </row>
+    <row r="406" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A406" s="7">
+        <v>1663</v>
+      </c>
+      <c r="B406" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="C406" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="D406" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E406" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F406" t="s">
+        <v>417</v>
+      </c>
+      <c r="H406" s="45">
+        <v>10.119599999999998</v>
+      </c>
+    </row>
+    <row r="407" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A407" s="7">
+        <v>1664</v>
+      </c>
+      <c r="B407" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="C407" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="D407" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E407" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="F407" t="s">
+        <v>417</v>
+      </c>
+      <c r="H407" s="45">
+        <v>12.9924</v>
+      </c>
+    </row>
+    <row r="408" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A408" s="7">
+        <v>1665</v>
+      </c>
+      <c r="B408" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="C408" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="D408" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E408" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="F408" t="s">
+        <v>417</v>
+      </c>
+      <c r="H408" s="46">
+        <v>18.7272</v>
+      </c>
+    </row>
+    <row r="409" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A409" s="7">
+        <v>1963</v>
+      </c>
+      <c r="B409" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="C409" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="D409" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E409" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="F409" t="s">
+        <v>417</v>
+      </c>
+      <c r="H409" s="44">
+        <v>4.8600000000000003</v>
+      </c>
+    </row>
+    <row r="410" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A410" s="7">
+        <v>1964</v>
+      </c>
+      <c r="B410" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="C410" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="D410" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E410" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="F410" t="s">
+        <v>417</v>
+      </c>
+      <c r="H410" s="45">
+        <v>6.0156000000000001</v>
+      </c>
+    </row>
+    <row r="411" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A411" s="7">
+        <v>1965</v>
+      </c>
+      <c r="B411" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="C411" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="D411" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E411" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="F411" t="s">
+        <v>417</v>
+      </c>
+      <c r="H411" s="45">
+        <v>6.8903999999999996</v>
+      </c>
+    </row>
+    <row r="412" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A412" s="7">
+        <v>1966</v>
+      </c>
+      <c r="B412" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="C412" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="D412" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E412" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="F412" t="s">
+        <v>417</v>
+      </c>
+      <c r="H412" s="45">
+        <v>8.8452000000000002</v>
+      </c>
+    </row>
+    <row r="413" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A413" s="7">
+        <v>1967</v>
+      </c>
+      <c r="B413" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="C413" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="D413" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E413" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="F413" t="s">
+        <v>417</v>
+      </c>
+      <c r="H413" s="45">
+        <v>13.186800000000002</v>
+      </c>
+    </row>
+    <row r="414" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A414" s="7">
+        <v>1968</v>
+      </c>
+      <c r="B414" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="C414" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="D414" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E414" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="F414" t="s">
+        <v>417</v>
+      </c>
+      <c r="H414" s="45">
+        <v>6.7284000000000006</v>
+      </c>
+    </row>
+    <row r="415" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A415" s="7">
+        <v>1969</v>
+      </c>
+      <c r="B415" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="C415" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="D415" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E415" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="F415" t="s">
+        <v>417</v>
+      </c>
+      <c r="H415" s="45">
+        <v>8.2835999999999999</v>
+      </c>
+    </row>
+    <row r="416" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A416" s="7">
+        <v>1970</v>
+      </c>
+      <c r="B416" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="C416" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="D416" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E416" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="F416" t="s">
+        <v>417</v>
+      </c>
+      <c r="H416" s="45">
+        <v>9.8064</v>
+      </c>
+    </row>
+    <row r="417" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A417" s="7">
+        <v>1971</v>
+      </c>
+      <c r="B417" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="C417" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="D417" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E417" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="F417" t="s">
+        <v>417</v>
+      </c>
+      <c r="H417" s="45">
+        <v>12.6036</v>
+      </c>
+    </row>
+    <row r="418" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A418" s="40">
+        <v>1972</v>
+      </c>
+      <c r="B418" s="40" t="s">
+        <v>394</v>
+      </c>
+      <c r="C418" s="40" t="s">
+        <v>392</v>
+      </c>
+      <c r="D418" s="40" t="s">
+        <v>372</v>
+      </c>
+      <c r="E418" s="41" t="s">
+        <v>432</v>
+      </c>
+      <c r="F418" s="42" t="s">
+        <v>417</v>
+      </c>
+      <c r="G418" s="42"/>
+      <c r="H418" s="46">
+        <v>18.176399999999997</v>
       </c>
     </row>
   </sheetData>

--- a/dados/Produtos_Agrupados_Completos_conciliados.xlsx
+++ b/dados/Produtos_Agrupados_Completos_conciliados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04FB0A0C-1CC5-4E5D-BBCA-9CA2D9ECE2FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C40CC75-DF68-40CF-B636-E19D367C4DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{86B17377-32DB-438B-8A03-02E761646E6D}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="DadosExternos_1" localSheetId="0" hidden="1">CONCILIADA!$A$1:$G$418</definedName>
+    <definedName name="DadosExternos_1" localSheetId="0" hidden="1">CONCILIADA!$A$1:$G$419</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3301" uniqueCount="649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3306" uniqueCount="649">
   <si>
     <t>Grupo</t>
   </si>
@@ -2663,13 +2663,11 @@
       <sheetName val="ESTOQUE CONSOLIDADO"/>
       <sheetName val="Plan1"/>
       <sheetName val="Plan2"/>
-      <sheetName val="ESTOQUE"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
-      <sheetData sheetId="3" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2693,15 +2691,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5499586E-A189-44D8-9C58-8F69F4EC7CA4}" name="Tabela14" displayName="Tabela14" ref="A1:H418" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:H418" xr:uid="{5499586E-A189-44D8-9C58-8F69F4EC7CA4}">
-    <filterColumn colId="5">
-      <filters>
-        <filter val="0"/>
-        <filter val="#N/D"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5499586E-A189-44D8-9C58-8F69F4EC7CA4}" name="Tabela14" displayName="Tabela14" ref="A1:H419" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:H419" xr:uid="{5499586E-A189-44D8-9C58-8F69F4EC7CA4}"/>
   <tableColumns count="8">
     <tableColumn id="2" xr3:uid="{3202AFED-4A11-4AD5-8FCF-B57F6545F53A}" uniqueName="2" name="ID_COD" queryTableFieldId="2" dataDxfId="16"/>
     <tableColumn id="1" xr3:uid="{5387F357-AA02-4B91-B30F-AB45B122F19D}" uniqueName="1" name="Grupo" queryTableFieldId="1" dataDxfId="15"/>
@@ -3052,7 +3043,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{868BC1FE-16FA-4E4B-B34E-F84713378B87}">
-  <dimension ref="A1:H418"/>
+  <dimension ref="A1:H419"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -3091,7 +3082,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3119,7 +3110,7 @@
         <v>0.41039999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3147,7 +3138,7 @@
         <v>0.43200000000000005</v>
       </c>
     </row>
-    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3175,7 +3166,7 @@
         <v>0.4536</v>
       </c>
     </row>
-    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>152</v>
       </c>
@@ -3203,7 +3194,7 @@
         <v>0.47520000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>153</v>
       </c>
@@ -3231,7 +3222,7 @@
         <v>0.50759999999999994</v>
       </c>
     </row>
-    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>154</v>
       </c>
@@ -3259,7 +3250,7 @@
         <v>0.5292</v>
       </c>
     </row>
-    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1641</v>
       </c>
@@ -3287,7 +3278,7 @@
         <v>0.64800000000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1642</v>
       </c>
@@ -3315,7 +3306,7 @@
         <v>0.66959999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1643</v>
       </c>
@@ -3343,7 +3334,7 @@
         <v>0.70200000000000007</v>
       </c>
     </row>
-    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>1587</v>
       </c>
@@ -3371,7 +3362,7 @@
         <v>2.8839999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>1588</v>
       </c>
@@ -3399,7 +3390,7 @@
         <v>5.3353999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>1586</v>
       </c>
@@ -3426,7 +3417,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>157</v>
       </c>
@@ -3454,7 +3445,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>158</v>
       </c>
@@ -3482,7 +3473,7 @@
         <v>7.1894</v>
       </c>
     </row>
-    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>155</v>
       </c>
@@ -3537,7 +3528,7 @@
         <v>4.4084000000000003</v>
       </c>
     </row>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>1640</v>
       </c>
@@ -3564,7 +3555,7 @@
         <v>7.96</v>
       </c>
     </row>
-    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>1209</v>
       </c>
@@ -3675,7 +3666,7 @@
         <v>5.991428571428572</v>
       </c>
     </row>
-    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>8</v>
       </c>
@@ -3729,7 +3720,7 @@
         <v>7.322857142857143</v>
       </c>
     </row>
-    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>10</v>
       </c>
@@ -3756,7 +3747,7 @@
         <v>7.9885714285714293</v>
       </c>
     </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>11</v>
       </c>
@@ -3810,7 +3801,7 @@
         <v>9.32</v>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>13</v>
       </c>
@@ -3891,7 +3882,7 @@
         <v>11.317142857142857</v>
       </c>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>16</v>
       </c>
@@ -3972,7 +3963,7 @@
         <v>13.314285714285715</v>
       </c>
     </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>51</v>
       </c>
@@ -4080,7 +4071,7 @@
         <v>16.525714285714287</v>
       </c>
     </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>55</v>
       </c>
@@ -4188,7 +4179,7 @@
         <v>19.28</v>
       </c>
     </row>
-    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>59</v>
       </c>
@@ -4296,7 +4287,7 @@
         <v>22.034285714285719</v>
       </c>
     </row>
-    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>1754</v>
       </c>
@@ -4323,7 +4314,7 @@
         <v>27.880000000000003</v>
       </c>
     </row>
-    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>1774</v>
       </c>
@@ -4350,7 +4341,7 @@
         <v>29.207619047619044</v>
       </c>
     </row>
-    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>307</v>
       </c>
@@ -4404,7 +4395,7 @@
         <v>8.2415384615384628</v>
       </c>
     </row>
-    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>309</v>
       </c>
@@ -4512,7 +4503,7 @@
         <v>11.238461538461538</v>
       </c>
     </row>
-    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>313</v>
       </c>
@@ -4539,7 +4530,7 @@
         <v>11.98</v>
       </c>
     </row>
-    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>314</v>
       </c>
@@ -4674,7 +4665,7 @@
         <v>15.733846153846155</v>
       </c>
     </row>
-    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>319</v>
       </c>
@@ -4701,7 +4692,7 @@
         <v>16.483076923076926</v>
       </c>
     </row>
-    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>320</v>
       </c>
@@ -4728,7 +4719,7 @@
         <v>17.232307692307696</v>
       </c>
     </row>
-    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>1690</v>
       </c>
@@ -4755,7 +4746,7 @@
         <v>18.73076923076923</v>
       </c>
     </row>
-    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>339</v>
       </c>
@@ -4782,7 +4773,7 @@
         <v>16.579999999999998</v>
       </c>
     </row>
-    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -4809,7 +4800,7 @@
         <v>17.270833333333332</v>
       </c>
     </row>
-    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>340</v>
       </c>
@@ -4836,7 +4827,7 @@
         <v>17.961666666666662</v>
       </c>
     </row>
-    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>341</v>
       </c>
@@ -4863,7 +4854,7 @@
         <v>18.652499999999996</v>
       </c>
     </row>
-    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>342</v>
       </c>
@@ -5052,7 +5043,7 @@
         <v>23.488333333333333</v>
       </c>
     </row>
-    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>1700</v>
       </c>
@@ -5079,7 +5070,7 @@
         <v>28.77</v>
       </c>
     </row>
-    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>1697</v>
       </c>
@@ -5106,7 +5097,7 @@
         <v>29.96875</v>
       </c>
     </row>
-    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>321</v>
       </c>
@@ -5133,7 +5124,7 @@
         <v>7.9</v>
       </c>
     </row>
-    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>322</v>
       </c>
@@ -5160,7 +5151,7 @@
         <v>8.69</v>
       </c>
     </row>
-    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>323</v>
       </c>
@@ -5187,7 +5178,7 @@
         <v>9.48</v>
       </c>
     </row>
-    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>324</v>
       </c>
@@ -5241,7 +5232,7 @@
         <v>11.06</v>
       </c>
     </row>
-    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>326</v>
       </c>
@@ -5268,7 +5259,7 @@
         <v>11.85</v>
       </c>
     </row>
-    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>327</v>
       </c>
@@ -5295,7 +5286,7 @@
         <v>12.64</v>
       </c>
     </row>
-    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>328</v>
       </c>
@@ -5322,7 +5313,7 @@
         <v>13.43</v>
       </c>
     </row>
-    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>329</v>
       </c>
@@ -5349,7 +5340,7 @@
         <v>14.22</v>
       </c>
     </row>
-    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>330</v>
       </c>
@@ -5403,7 +5394,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>332</v>
       </c>
@@ -5430,7 +5421,7 @@
         <v>16.59</v>
       </c>
     </row>
-    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>333</v>
       </c>
@@ -5484,7 +5475,7 @@
         <v>18.170000000000002</v>
       </c>
     </row>
-    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>335</v>
       </c>
@@ -5511,7 +5502,7 @@
         <v>18.96</v>
       </c>
     </row>
-    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>336</v>
       </c>
@@ -5538,7 +5529,7 @@
         <v>19.75</v>
       </c>
     </row>
-    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>337</v>
       </c>
@@ -5565,7 +5556,7 @@
         <v>20.54</v>
       </c>
     </row>
-    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>1699</v>
       </c>
@@ -5592,7 +5583,7 @@
         <v>13.525185185185185</v>
       </c>
     </row>
-    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>1773</v>
       </c>
@@ -5619,7 +5610,7 @@
         <v>14.948888888888888</v>
       </c>
     </row>
-    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>349</v>
       </c>
@@ -5646,7 +5637,7 @@
         <v>19.22</v>
       </c>
     </row>
-    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>350</v>
       </c>
@@ -5835,7 +5826,7 @@
         <v>24.20296296296296</v>
       </c>
     </row>
-    <row r="103" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>73</v>
       </c>
@@ -5889,7 +5880,7 @@
         <v>31.909629629629631</v>
       </c>
     </row>
-    <row r="105" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>75</v>
       </c>
@@ -6078,7 +6069,7 @@
         <v>12.499047619047618</v>
       </c>
     </row>
-    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>82</v>
       </c>
@@ -6132,7 +6123,7 @@
         <v>13.969523809523809</v>
       </c>
     </row>
-    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>84</v>
       </c>
@@ -6159,7 +6150,7 @@
         <v>14.704761904761904</v>
       </c>
     </row>
-    <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>85</v>
       </c>
@@ -6186,7 +6177,7 @@
         <v>15.440000000000001</v>
       </c>
     </row>
-    <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>86</v>
       </c>
@@ -6213,7 +6204,7 @@
         <v>16.175238095238093</v>
       </c>
     </row>
-    <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>87</v>
       </c>
@@ -6240,7 +6231,7 @@
         <v>16.910476190476189</v>
       </c>
     </row>
-    <row r="118" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>88</v>
       </c>
@@ -6267,7 +6258,7 @@
         <v>17.645714285714284</v>
       </c>
     </row>
-    <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>89</v>
       </c>
@@ -6294,7 +6285,7 @@
         <v>18.38095238095238</v>
       </c>
     </row>
-    <row r="120" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>90</v>
       </c>
@@ -6321,7 +6312,7 @@
         <v>19.116190476190475</v>
       </c>
     </row>
-    <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>91</v>
       </c>
@@ -6348,7 +6339,7 @@
         <v>19.851428571428571</v>
       </c>
     </row>
-    <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>92</v>
       </c>
@@ -6375,7 +6366,7 @@
         <v>20.586666666666666</v>
       </c>
     </row>
-    <row r="123" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>93</v>
       </c>
@@ -6402,7 +6393,7 @@
         <v>21.321904761904758</v>
       </c>
     </row>
-    <row r="124" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>94</v>
       </c>
@@ -6429,7 +6420,7 @@
         <v>22.057142857142857</v>
       </c>
     </row>
-    <row r="125" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>95</v>
       </c>
@@ -6456,7 +6447,7 @@
         <v>22.792380952380952</v>
       </c>
     </row>
-    <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>96</v>
       </c>
@@ -6483,7 +6474,7 @@
         <v>23.527619047619048</v>
       </c>
     </row>
-    <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>97</v>
       </c>
@@ -6510,7 +6501,7 @@
         <v>24.262857142857143</v>
       </c>
     </row>
-    <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>129</v>
       </c>
@@ -6591,7 +6582,7 @@
         <v>28.86810810810811</v>
       </c>
     </row>
-    <row r="131" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>132</v>
       </c>
@@ -6618,7 +6609,7 @@
         <v>29.670000000000005</v>
       </c>
     </row>
-    <row r="132" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>133</v>
       </c>
@@ -6645,7 +6636,7 @@
         <v>30.471891891891893</v>
       </c>
     </row>
-    <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>134</v>
       </c>
@@ -6672,7 +6663,7 @@
         <v>31.273783783783788</v>
       </c>
     </row>
-    <row r="134" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>135</v>
       </c>
@@ -6726,7 +6717,7 @@
         <v>32.877567567567567</v>
       </c>
     </row>
-    <row r="136" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" s="7">
         <v>1960</v>
       </c>
@@ -6752,7 +6743,7 @@
         <v>94.88</v>
       </c>
     </row>
-    <row r="137" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>1775</v>
       </c>
@@ -6833,7 +6824,7 @@
         <v>33.679459459459466</v>
       </c>
     </row>
-    <row r="140" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>357</v>
       </c>
@@ -6860,7 +6851,7 @@
         <v>15.8424</v>
       </c>
     </row>
-    <row r="141" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>358</v>
       </c>
@@ -6887,7 +6878,7 @@
         <v>16.596799999999998</v>
       </c>
     </row>
-    <row r="142" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>261</v>
       </c>
@@ -6914,7 +6905,7 @@
         <v>17.351200000000002</v>
       </c>
     </row>
-    <row r="143" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>262</v>
       </c>
@@ -6941,7 +6932,7 @@
         <v>18.105599999999999</v>
       </c>
     </row>
-    <row r="144" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>263</v>
       </c>
@@ -6968,7 +6959,7 @@
         <v>18.86</v>
       </c>
     </row>
-    <row r="145" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>264</v>
       </c>
@@ -6995,7 +6986,7 @@
         <v>19.614399999999996</v>
       </c>
     </row>
-    <row r="146" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>265</v>
       </c>
@@ -7022,7 +7013,7 @@
         <v>20.3688</v>
       </c>
     </row>
-    <row r="147" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>266</v>
       </c>
@@ -7049,7 +7040,7 @@
         <v>21.123200000000001</v>
       </c>
     </row>
-    <row r="148" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>267</v>
       </c>
@@ -7076,7 +7067,7 @@
         <v>21.877599999999997</v>
       </c>
     </row>
-    <row r="149" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>268</v>
       </c>
@@ -7211,7 +7202,7 @@
         <v>24.895199999999999</v>
       </c>
     </row>
-    <row r="154" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>1687</v>
       </c>
@@ -7400,7 +7391,7 @@
         <v>31.384736842105259</v>
       </c>
     </row>
-    <row r="161" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>296</v>
       </c>
@@ -7427,7 +7418,7 @@
         <v>32.189473684210526</v>
       </c>
     </row>
-    <row r="162" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" s="7">
         <v>1961</v>
       </c>
@@ -7453,7 +7444,7 @@
         <v>98.7</v>
       </c>
     </row>
-    <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>1778</v>
       </c>
@@ -7480,7 +7471,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="164" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>1779</v>
       </c>
@@ -7534,7 +7525,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="166" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>359</v>
       </c>
@@ -7561,7 +7552,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>273</v>
       </c>
@@ -7588,7 +7579,7 @@
         <v>16.59</v>
       </c>
     </row>
-    <row r="168" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>274</v>
       </c>
@@ -7615,7 +7606,7 @@
         <v>17.38</v>
       </c>
     </row>
-    <row r="169" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>275</v>
       </c>
@@ -7642,7 +7633,7 @@
         <v>18.170000000000002</v>
       </c>
     </row>
-    <row r="170" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>276</v>
       </c>
@@ -7669,7 +7660,7 @@
         <v>18.959999999999997</v>
       </c>
     </row>
-    <row r="171" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>277</v>
       </c>
@@ -7696,7 +7687,7 @@
         <v>19.75</v>
       </c>
     </row>
-    <row r="172" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>278</v>
       </c>
@@ -7723,7 +7714,7 @@
         <v>20.54</v>
       </c>
     </row>
-    <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>279</v>
       </c>
@@ -7750,7 +7741,7 @@
         <v>19.88</v>
       </c>
     </row>
-    <row r="174" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>280</v>
       </c>
@@ -7777,7 +7768,7 @@
         <v>22.12</v>
       </c>
     </row>
-    <row r="175" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>281</v>
       </c>
@@ -7858,7 +7849,7 @@
         <v>24.490000000000002</v>
       </c>
     </row>
-    <row r="178" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>284</v>
       </c>
@@ -7912,7 +7903,7 @@
         <v>26.069999999999997</v>
       </c>
     </row>
-    <row r="180" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" s="4">
         <v>286</v>
       </c>
@@ -8020,7 +8011,7 @@
         <v>29.229999999999997</v>
       </c>
     </row>
-    <row r="184" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>1636</v>
       </c>
@@ -8074,7 +8065,7 @@
         <v>18.478536585365852</v>
       </c>
     </row>
-    <row r="186" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>297</v>
       </c>
@@ -8101,7 +8092,7 @@
         <v>30.529756097560973</v>
       </c>
     </row>
-    <row r="187" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>298</v>
       </c>
@@ -8128,7 +8119,7 @@
         <v>31.333170731707312</v>
       </c>
     </row>
-    <row r="188" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>299</v>
       </c>
@@ -8155,7 +8146,7 @@
         <v>32.136585365853655</v>
       </c>
     </row>
-    <row r="189" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>300</v>
       </c>
@@ -8290,7 +8281,7 @@
         <v>36.153658536585361</v>
       </c>
     </row>
-    <row r="194" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" s="7">
         <v>1962</v>
       </c>
@@ -8316,7 +8307,7 @@
         <v>107.44</v>
       </c>
     </row>
-    <row r="195" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>1781</v>
       </c>
@@ -8394,7 +8385,7 @@
         <v>171</v>
       </c>
       <c r="H197" s="2">
-        <v>3.66</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
@@ -8421,7 +8412,7 @@
         <v>111</v>
       </c>
       <c r="H198" s="2">
-        <v>3.97</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
@@ -8448,7 +8439,7 @@
         <v>126</v>
       </c>
       <c r="H199" s="2">
-        <v>4.91</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
@@ -8475,7 +8466,7 @@
         <v>81</v>
       </c>
       <c r="H200" s="2">
-        <v>5.63</v>
+        <v>6.08</v>
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
@@ -8502,7 +8493,7 @@
         <v>88</v>
       </c>
       <c r="H201" s="2">
-        <v>7.25</v>
+        <v>7.83</v>
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
@@ -8550,7 +8541,7 @@
         <v>97</v>
       </c>
       <c r="H203" s="2">
-        <v>10.74</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
@@ -8598,7 +8589,7 @@
         <v>120</v>
       </c>
       <c r="H205" s="2">
-        <v>5.38</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.25">
@@ -8625,7 +8616,7 @@
         <v>132</v>
       </c>
       <c r="H206" s="2">
-        <v>6.78</v>
+        <v>7.32</v>
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.25">
@@ -8652,7 +8643,7 @@
         <v>84</v>
       </c>
       <c r="H207" s="2">
-        <v>7.94</v>
+        <v>8.58</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.25">
@@ -8679,7 +8670,7 @@
         <v>92</v>
       </c>
       <c r="H208" s="2">
-        <v>10.3</v>
+        <v>11.12</v>
       </c>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
@@ -8727,7 +8718,7 @@
         <v>102</v>
       </c>
       <c r="H210" s="2">
-        <v>14.74</v>
+        <v>15.92</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
@@ -9105,7 +9096,7 @@
         <v>3.66</v>
       </c>
     </row>
-    <row r="226" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>163</v>
       </c>
@@ -9132,7 +9123,7 @@
         <v>3.97</v>
       </c>
     </row>
-    <row r="227" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>480</v>
       </c>
@@ -9159,7 +9150,7 @@
         <v>4.91</v>
       </c>
     </row>
-    <row r="228" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>164</v>
       </c>
@@ -9186,7 +9177,7 @@
         <v>5.63</v>
       </c>
     </row>
-    <row r="229" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>165</v>
       </c>
@@ -9234,7 +9225,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="231" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>166</v>
       </c>
@@ -9282,7 +9273,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="233" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>171</v>
       </c>
@@ -9309,7 +9300,7 @@
         <v>5.38</v>
       </c>
     </row>
-    <row r="234" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>478</v>
       </c>
@@ -9336,7 +9327,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="235" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>172</v>
       </c>
@@ -9363,7 +9354,7 @@
         <v>7.94</v>
       </c>
     </row>
-    <row r="236" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>173</v>
       </c>
@@ -9411,7 +9402,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="238" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>174</v>
       </c>
@@ -9459,7 +9450,7 @@
         <v>4.2699999999999996</v>
       </c>
     </row>
-    <row r="240" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>159</v>
       </c>
@@ -9486,7 +9477,7 @@
         <v>4.6399999999999997</v>
       </c>
     </row>
-    <row r="241" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>481</v>
       </c>
@@ -9513,7 +9504,7 @@
         <v>5.74</v>
       </c>
     </row>
-    <row r="242" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>160</v>
       </c>
@@ -9540,7 +9531,7 @@
         <v>6.57</v>
       </c>
     </row>
-    <row r="243" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>161</v>
       </c>
@@ -9588,7 +9579,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="245" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>162</v>
       </c>
@@ -9636,7 +9627,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="247" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>167</v>
       </c>
@@ -9663,7 +9654,7 @@
         <v>6.41</v>
       </c>
     </row>
-    <row r="248" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>479</v>
       </c>
@@ -9690,7 +9681,7 @@
         <v>7.92</v>
       </c>
     </row>
-    <row r="249" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>168</v>
       </c>
@@ -9717,7 +9708,7 @@
         <v>9.3699999999999992</v>
       </c>
     </row>
-    <row r="250" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>169</v>
       </c>
@@ -9765,7 +9756,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="252" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>170</v>
       </c>
@@ -10170,10 +10161,10 @@
         <v>170</v>
       </c>
       <c r="H267" s="2">
-        <v>4.2699999999999996</v>
-      </c>
-    </row>
-    <row r="268" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+        <v>4.6100000000000003</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>1656</v>
       </c>
@@ -10197,7 +10188,7 @@
         <v>69</v>
       </c>
       <c r="H268" s="2">
-        <v>4.6399999999999997</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.25">
@@ -10224,7 +10215,7 @@
         <v>73</v>
       </c>
       <c r="H269" s="2">
-        <v>5.74</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.25">
@@ -10251,7 +10242,7 @@
         <v>80</v>
       </c>
       <c r="H270" s="2">
-        <v>6.57</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.25">
@@ -10278,7 +10269,7 @@
         <v>87</v>
       </c>
       <c r="H271" s="2">
-        <v>8.4499999999999993</v>
+        <v>9.1300000000000008</v>
       </c>
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.25">
@@ -10326,7 +10317,7 @@
         <v>96</v>
       </c>
       <c r="H273" s="2">
-        <v>12.58</v>
+        <v>13.59</v>
       </c>
     </row>
     <row r="274" spans="1:8" x14ac:dyDescent="0.25">
@@ -11235,7 +11226,7 @@
         <v>3.66</v>
       </c>
     </row>
-    <row r="310" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>414</v>
       </c>
@@ -11262,7 +11253,7 @@
         <v>3.85</v>
       </c>
     </row>
-    <row r="311" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>476</v>
       </c>
@@ -11289,7 +11280,7 @@
         <v>4.91</v>
       </c>
     </row>
-    <row r="312" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>419</v>
       </c>
@@ -11316,7 +11307,7 @@
         <v>5.47</v>
       </c>
     </row>
-    <row r="313" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>423</v>
       </c>
@@ -11364,7 +11355,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="315" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>427</v>
       </c>
@@ -11412,7 +11403,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="317" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>417</v>
       </c>
@@ -11439,7 +11430,7 @@
         <v>5.38</v>
       </c>
     </row>
-    <row r="318" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>474</v>
       </c>
@@ -11466,7 +11457,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="319" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>421</v>
       </c>
@@ -11493,7 +11484,7 @@
         <v>7.94</v>
       </c>
     </row>
-    <row r="320" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>425</v>
       </c>
@@ -11541,7 +11532,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="322" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>429</v>
       </c>
@@ -11589,7 +11580,7 @@
         <v>4.2699999999999996</v>
       </c>
     </row>
-    <row r="324" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>416</v>
       </c>
@@ -11616,7 +11607,7 @@
         <v>4.6399999999999997</v>
       </c>
     </row>
-    <row r="325" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>477</v>
       </c>
@@ -11643,7 +11634,7 @@
         <v>5.74</v>
       </c>
     </row>
-    <row r="326" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>420</v>
       </c>
@@ -11670,7 +11661,7 @@
         <v>6.57</v>
       </c>
     </row>
-    <row r="327" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>424</v>
       </c>
@@ -11718,7 +11709,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="329" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>428</v>
       </c>
@@ -11766,7 +11757,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="331" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>418</v>
       </c>
@@ -11793,7 +11784,7 @@
         <v>6.41</v>
       </c>
     </row>
-    <row r="332" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>475</v>
       </c>
@@ -11820,7 +11811,7 @@
         <v>7.92</v>
       </c>
     </row>
-    <row r="333" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>422</v>
       </c>
@@ -11847,7 +11838,7 @@
         <v>9.3699999999999992</v>
       </c>
     </row>
-    <row r="334" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>426</v>
       </c>
@@ -11895,7 +11886,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="336" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>430</v>
       </c>
@@ -12630,7 +12621,7 @@
         <v>17.34</v>
       </c>
     </row>
-    <row r="365" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A365">
         <v>4</v>
       </c>
@@ -12657,7 +12648,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="366" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A366">
         <v>731</v>
       </c>
@@ -12684,7 +12675,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="367" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A367">
         <v>730</v>
       </c>
@@ -12762,7 +12753,7 @@
         <v>22.79</v>
       </c>
     </row>
-    <row r="370" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A370">
         <v>1819</v>
       </c>
@@ -12843,7 +12834,7 @@
         <v>25.71</v>
       </c>
     </row>
-    <row r="373" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A373">
         <v>1822</v>
       </c>
@@ -12870,7 +12861,7 @@
         <v>24.51</v>
       </c>
     </row>
-    <row r="374" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A374">
         <v>1797</v>
       </c>
@@ -13906,6 +13897,29 @@
       <c r="G418" s="42"/>
       <c r="H418" s="46">
         <v>18.176399999999997</v>
+      </c>
+    </row>
+    <row r="419" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A419" s="7">
+        <v>1974</v>
+      </c>
+      <c r="B419" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="C419" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="D419" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="E419" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="F419" t="s">
+        <v>411</v>
+      </c>
+      <c r="H419" s="2">
+        <v>6.37</v>
       </c>
     </row>
   </sheetData>
@@ -16071,7 +16085,7 @@
       </c>
       <c r="G4" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>0</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -16093,7 +16107,7 @@
       </c>
       <c r="G5" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>14000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -16137,7 +16151,7 @@
       <c r="F7" s="13"/>
       <c r="G7" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>13000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -16229,7 +16243,7 @@
       </c>
       <c r="G11" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>648</v>
+        <v>288</v>
       </c>
     </row>
     <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -16275,7 +16289,7 @@
       <c r="F13" s="13"/>
       <c r="G13" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -16343,7 +16357,7 @@
       <c r="F16" s="13"/>
       <c r="G16" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>700</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -16411,7 +16425,7 @@
       <c r="F19" s="13"/>
       <c r="G19" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -16501,7 +16515,7 @@
       <c r="F23" s="13"/>
       <c r="G23" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -16591,7 +16605,7 @@
       <c r="F27" s="13"/>
       <c r="G27" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>120</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -16775,7 +16789,7 @@
       </c>
       <c r="G35" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>128</v>
+        <v>192</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -17839,7 +17853,7 @@
       </c>
       <c r="G82" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -17953,7 +17967,7 @@
       </c>
       <c r="G87" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>0</v>
+        <v>72</v>
       </c>
     </row>
     <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -17977,7 +17991,7 @@
       </c>
       <c r="G88" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>0</v>
+        <v>72</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -18001,7 +18015,7 @@
       </c>
       <c r="G89" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>72</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -18073,7 +18087,7 @@
       </c>
       <c r="G92" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -18097,7 +18111,7 @@
       </c>
       <c r="G93" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -18193,7 +18207,7 @@
       </c>
       <c r="G97" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -18264,7 +18278,7 @@
       </c>
       <c r="G100" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -18384,7 +18398,7 @@
       </c>
       <c r="G105" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -18408,7 +18422,7 @@
       </c>
       <c r="G106" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -18688,7 +18702,7 @@
       </c>
       <c r="G118" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -18736,7 +18750,7 @@
       </c>
       <c r="G120" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>2790</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -18760,7 +18774,7 @@
       </c>
       <c r="G121" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -18828,7 +18842,7 @@
       <c r="F124" s="13"/>
       <c r="G124" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -18920,7 +18934,7 @@
       <c r="F128" s="13"/>
       <c r="G128" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -19080,7 +19094,7 @@
       </c>
       <c r="G135" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>0</v>
+        <v>140</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -19104,7 +19118,7 @@
       </c>
       <c r="G136" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>260</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -19260,7 +19274,7 @@
       </c>
       <c r="G143" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -19390,7 +19404,7 @@
       </c>
       <c r="G149" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>5000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -19412,7 +19426,7 @@
       </c>
       <c r="G150" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>10000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -19434,7 +19448,7 @@
       </c>
       <c r="G151" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>0</v>
+        <v>72</v>
       </c>
     </row>
     <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -19456,7 +19470,7 @@
       </c>
       <c r="G152" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -19500,7 +19514,7 @@
       </c>
       <c r="G154" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -19562,7 +19576,7 @@
       </c>
       <c r="G157" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>220</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -19622,7 +19636,7 @@
       </c>
       <c r="G160" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>140</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -19642,7 +19656,7 @@
       </c>
       <c r="G161" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="162" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -19804,7 +19818,7 @@
       </c>
       <c r="G169" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>35</v>
+        <v>75</v>
       </c>
     </row>
     <row r="170" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -19846,7 +19860,7 @@
       </c>
       <c r="G171" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="172" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -19870,7 +19884,7 @@
       </c>
       <c r="G172" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
@@ -19894,7 +19908,7 @@
       </c>
       <c r="G173" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
@@ -20144,7 +20158,7 @@
       <c r="F184" s="13"/>
       <c r="G184" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="185" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -20216,7 +20230,7 @@
       </c>
       <c r="G187" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -20264,7 +20278,7 @@
       </c>
       <c r="G189" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
@@ -20308,7 +20322,7 @@
       <c r="F191" s="13"/>
       <c r="G191" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
@@ -20608,7 +20622,7 @@
       </c>
       <c r="G204" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>0</v>
+        <v>750</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
@@ -20652,7 +20666,7 @@
       <c r="F206" s="13"/>
       <c r="G206" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>750</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
@@ -20700,7 +20714,7 @@
       </c>
       <c r="G208" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -20746,7 +20760,7 @@
       <c r="F210" s="13"/>
       <c r="G210" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.25">
@@ -20794,7 +20808,7 @@
       </c>
       <c r="G212" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>0</v>
+        <v>160</v>
       </c>
     </row>
     <row r="213" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -20842,7 +20856,7 @@
       </c>
       <c r="G214" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>160</v>
+        <v>0</v>
       </c>
     </row>
     <row r="215" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -21010,7 +21024,7 @@
       </c>
       <c r="G221" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>128</v>
+        <v>0</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
@@ -21462,7 +21476,7 @@
       </c>
       <c r="G241" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.25">
@@ -21642,7 +21656,7 @@
       </c>
       <c r="G249" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>0</v>
+        <v>72</v>
       </c>
     </row>
     <row r="250" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -21822,7 +21836,7 @@
       </c>
       <c r="G258" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>0</v>
+        <v>104</v>
       </c>
     </row>
     <row r="259" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -21862,7 +21876,7 @@
       </c>
       <c r="G260" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.25">
@@ -21984,7 +21998,7 @@
       </c>
       <c r="G266" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>0</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="267" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -22024,7 +22038,7 @@
       </c>
       <c r="G268" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>21150</v>
+        <v>0</v>
       </c>
     </row>
     <row r="269" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -22168,7 +22182,7 @@
       </c>
       <c r="G275" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>110</v>
+        <v>0</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.25">
@@ -23048,7 +23062,7 @@
       </c>
       <c r="G315" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>0</v>
+        <v>900</v>
       </c>
     </row>
     <row r="316" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -23088,7 +23102,7 @@
       </c>
       <c r="G317" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="318" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -23148,7 +23162,7 @@
       <c r="F320" s="13"/>
       <c r="G320" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>156</v>
+        <v>0</v>
       </c>
     </row>
     <row r="321" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -23170,7 +23184,7 @@
       </c>
       <c r="G321" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>4500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="322" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -23242,7 +23256,7 @@
       </c>
       <c r="G324" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>0</v>
+        <v>560</v>
       </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.25">
@@ -23286,7 +23300,7 @@
       </c>
       <c r="G326" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>560</v>
+        <v>0</v>
       </c>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.25">
@@ -23376,7 +23390,7 @@
       </c>
       <c r="G330" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>0</v>
+        <v>156</v>
       </c>
     </row>
     <row r="331" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -23396,7 +23410,7 @@
       </c>
       <c r="G331" s="19">
         <f>[1]!Tabela2[[#This Row],[VOL.]]*[1]!Tabela2[[#This Row],[UNID.]]</f>
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/dados/Produtos_Agrupados_Completos_conciliados.xlsx
+++ b/dados/Produtos_Agrupados_Completos_conciliados.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C40CC75-DF68-40CF-B636-E19D367C4DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A997E423-2382-459C-A169-71921C7B393D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{86B17377-32DB-438B-8A03-02E761646E6D}"/>
   </bookViews>
@@ -2663,11 +2663,13 @@
       <sheetName val="ESTOQUE CONSOLIDADO"/>
       <sheetName val="Plan1"/>
       <sheetName val="Plan2"/>
+      <sheetName val="ESTOQUE"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
+      <sheetData sheetId="3" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2692,7 +2694,16 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5499586E-A189-44D8-9C58-8F69F4EC7CA4}" name="Tabela14" displayName="Tabela14" ref="A1:H419" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:H419" xr:uid="{5499586E-A189-44D8-9C58-8F69F4EC7CA4}"/>
+  <autoFilter ref="A1:H419" xr:uid="{5499586E-A189-44D8-9C58-8F69F4EC7CA4}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="ATADURA DE CREPE - FARMA"/>
+        <filter val="ATADURA DE CREPE - HOSPITALAR"/>
+        <filter val="ATADURAS LINHA FARMA"/>
+        <filter val="ATADURAS LINHA HOSPITALAR"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="8">
     <tableColumn id="2" xr3:uid="{3202AFED-4A11-4AD5-8FCF-B57F6545F53A}" uniqueName="2" name="ID_COD" queryTableFieldId="2" dataDxfId="16"/>
     <tableColumn id="1" xr3:uid="{5387F357-AA02-4B91-B30F-AB45B122F19D}" uniqueName="1" name="Grupo" queryTableFieldId="1" dataDxfId="15"/>
@@ -3082,7 +3093,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3110,7 +3121,7 @@
         <v>0.41039999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3138,7 +3149,7 @@
         <v>0.43200000000000005</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3166,7 +3177,7 @@
         <v>0.4536</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>152</v>
       </c>
@@ -3194,7 +3205,7 @@
         <v>0.47520000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>153</v>
       </c>
@@ -3222,7 +3233,7 @@
         <v>0.50759999999999994</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>154</v>
       </c>
@@ -3250,7 +3261,7 @@
         <v>0.5292</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1641</v>
       </c>
@@ -3278,7 +3289,7 @@
         <v>0.64800000000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1642</v>
       </c>
@@ -3306,7 +3317,7 @@
         <v>0.66959999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1643</v>
       </c>
@@ -3334,7 +3345,7 @@
         <v>0.70200000000000007</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>1587</v>
       </c>
@@ -3362,7 +3373,7 @@
         <v>2.8839999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>1588</v>
       </c>
@@ -3390,7 +3401,7 @@
         <v>5.3353999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>1586</v>
       </c>
@@ -3417,7 +3428,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>157</v>
       </c>
@@ -3445,7 +3456,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>158</v>
       </c>
@@ -3473,7 +3484,7 @@
         <v>7.1894</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>155</v>
       </c>
@@ -3500,7 +3511,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>1639</v>
       </c>
@@ -3528,7 +3539,7 @@
         <v>4.4084000000000003</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>1640</v>
       </c>
@@ -3555,7 +3566,7 @@
         <v>7.96</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>1209</v>
       </c>
@@ -3582,7 +3593,7 @@
         <v>86.5</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>5</v>
       </c>
@@ -3610,7 +3621,7 @@
         <v>4.66</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>6</v>
       </c>
@@ -3638,7 +3649,7 @@
         <v>5.3257142857142865</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>7</v>
       </c>
@@ -3666,7 +3677,7 @@
         <v>5.991428571428572</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>8</v>
       </c>
@@ -3693,7 +3704,7 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>9</v>
       </c>
@@ -3720,7 +3731,7 @@
         <v>7.322857142857143</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>10</v>
       </c>
@@ -3747,7 +3758,7 @@
         <v>7.9885714285714293</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>11</v>
       </c>
@@ -3774,7 +3785,7 @@
         <v>8.6542857142857148</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>12</v>
       </c>
@@ -3801,7 +3812,7 @@
         <v>9.32</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>13</v>
       </c>
@@ -3828,7 +3839,7 @@
         <v>10.88</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>14</v>
       </c>
@@ -3855,7 +3866,7 @@
         <v>10.651428571428573</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>15</v>
       </c>
@@ -3882,7 +3893,7 @@
         <v>11.317142857142857</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>16</v>
       </c>
@@ -3909,7 +3920,7 @@
         <v>11.982857142857144</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>17</v>
       </c>
@@ -3936,7 +3947,7 @@
         <v>12.648571428571429</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>18</v>
       </c>
@@ -3963,7 +3974,7 @@
         <v>13.314285714285715</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>51</v>
       </c>
@@ -3990,7 +4001,7 @@
         <v>14.46</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>52</v>
       </c>
@@ -4017,7 +4028,7 @@
         <v>15.148571428571429</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>53</v>
       </c>
@@ -4044,7 +4055,7 @@
         <v>15.837142857142858</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>54</v>
       </c>
@@ -4071,7 +4082,7 @@
         <v>16.525714285714287</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>55</v>
       </c>
@@ -4098,7 +4109,7 @@
         <v>17.214285714285715</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>56</v>
       </c>
@@ -4125,7 +4136,7 @@
         <v>17.902857142857144</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>57</v>
       </c>
@@ -4152,7 +4163,7 @@
         <v>18.591428571428573</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>58</v>
       </c>
@@ -4179,7 +4190,7 @@
         <v>19.28</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>59</v>
       </c>
@@ -4206,7 +4217,7 @@
         <v>19.96857142857143</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>60</v>
       </c>
@@ -4233,7 +4244,7 @@
         <v>20.657142857142858</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>61</v>
       </c>
@@ -4260,7 +4271,7 @@
         <v>21.345714285714287</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>19</v>
       </c>
@@ -4287,7 +4298,7 @@
         <v>22.034285714285719</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>1754</v>
       </c>
@@ -4314,7 +4325,7 @@
         <v>27.880000000000003</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>1774</v>
       </c>
@@ -4341,7 +4352,7 @@
         <v>29.207619047619044</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>307</v>
       </c>
@@ -4368,7 +4379,7 @@
         <v>7.4923076923076923</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>308</v>
       </c>
@@ -4395,7 +4406,7 @@
         <v>8.2415384615384628</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>309</v>
       </c>
@@ -4422,7 +4433,7 @@
         <v>8.9907692307692297</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>310</v>
       </c>
@@ -4449,7 +4460,7 @@
         <v>9.74</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>311</v>
       </c>
@@ -4476,7 +4487,7 @@
         <v>10.489230769230771</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>312</v>
       </c>
@@ -4503,7 +4514,7 @@
         <v>11.238461538461538</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>313</v>
       </c>
@@ -4530,7 +4541,7 @@
         <v>11.98</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>314</v>
       </c>
@@ -4557,7 +4568,7 @@
         <v>12.736923076923077</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>315</v>
       </c>
@@ -4584,7 +4595,7 @@
         <v>13.486153846153847</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>316</v>
       </c>
@@ -4611,7 +4622,7 @@
         <v>14.235384615384616</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>317</v>
       </c>
@@ -4638,7 +4649,7 @@
         <v>14.984615384615385</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>318</v>
       </c>
@@ -4665,7 +4676,7 @@
         <v>15.733846153846155</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>319</v>
       </c>
@@ -4692,7 +4703,7 @@
         <v>16.483076923076926</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>320</v>
       </c>
@@ -4719,7 +4730,7 @@
         <v>17.232307692307696</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>1690</v>
       </c>
@@ -4746,7 +4757,7 @@
         <v>18.73076923076923</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>339</v>
       </c>
@@ -4773,7 +4784,7 @@
         <v>16.579999999999998</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -4800,7 +4811,7 @@
         <v>17.270833333333332</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>340</v>
       </c>
@@ -4827,7 +4838,7 @@
         <v>17.961666666666662</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>341</v>
       </c>
@@ -4854,7 +4865,7 @@
         <v>18.652499999999996</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>342</v>
       </c>
@@ -4881,7 +4892,7 @@
         <v>19.34333333333333</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>343</v>
       </c>
@@ -4908,7 +4919,7 @@
         <v>20.034166666666668</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>344</v>
       </c>
@@ -4935,7 +4946,7 @@
         <v>20.724999999999998</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>345</v>
       </c>
@@ -4962,7 +4973,7 @@
         <v>21.415833333333332</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>346</v>
       </c>
@@ -4989,7 +5000,7 @@
         <v>22.106666666666666</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>347</v>
       </c>
@@ -5016,7 +5027,7 @@
         <v>22.797499999999999</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>348</v>
       </c>
@@ -5043,7 +5054,7 @@
         <v>23.488333333333333</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>1700</v>
       </c>
@@ -5070,7 +5081,7 @@
         <v>28.77</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>1697</v>
       </c>
@@ -5097,7 +5108,7 @@
         <v>29.96875</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>321</v>
       </c>
@@ -5124,7 +5135,7 @@
         <v>7.9</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>322</v>
       </c>
@@ -5151,7 +5162,7 @@
         <v>8.69</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>323</v>
       </c>
@@ -5178,7 +5189,7 @@
         <v>9.48</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>324</v>
       </c>
@@ -5205,7 +5216,7 @@
         <v>10.27</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>325</v>
       </c>
@@ -5232,7 +5243,7 @@
         <v>11.06</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>326</v>
       </c>
@@ -5259,7 +5270,7 @@
         <v>11.85</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>327</v>
       </c>
@@ -5286,7 +5297,7 @@
         <v>12.64</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>328</v>
       </c>
@@ -5313,7 +5324,7 @@
         <v>13.43</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>329</v>
       </c>
@@ -5340,7 +5351,7 @@
         <v>14.22</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>330</v>
       </c>
@@ -5367,7 +5378,7 @@
         <v>15.01</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>331</v>
       </c>
@@ -5394,7 +5405,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>332</v>
       </c>
@@ -5421,7 +5432,7 @@
         <v>16.59</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>333</v>
       </c>
@@ -5448,7 +5459,7 @@
         <v>17.38</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>334</v>
       </c>
@@ -5475,7 +5486,7 @@
         <v>18.170000000000002</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>335</v>
       </c>
@@ -5502,7 +5513,7 @@
         <v>18.96</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>336</v>
       </c>
@@ -5529,7 +5540,7 @@
         <v>19.75</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>337</v>
       </c>
@@ -5556,7 +5567,7 @@
         <v>20.54</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>1699</v>
       </c>
@@ -5583,7 +5594,7 @@
         <v>13.525185185185185</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>1773</v>
       </c>
@@ -5610,7 +5621,7 @@
         <v>14.948888888888888</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>349</v>
       </c>
@@ -5637,7 +5648,7 @@
         <v>19.22</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>350</v>
       </c>
@@ -5664,7 +5675,7 @@
         <v>19.931851851851849</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>351</v>
       </c>
@@ -5691,7 +5702,7 @@
         <v>20.6437037037037</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>352</v>
       </c>
@@ -5718,7 +5729,7 @@
         <v>21.355555555555554</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>353</v>
       </c>
@@ -5745,7 +5756,7 @@
         <v>22.067407407407408</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>354</v>
       </c>
@@ -5772,7 +5783,7 @@
         <v>22.779259259259259</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>355</v>
       </c>
@@ -5799,7 +5810,7 @@
         <v>23.49111111111111</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>356</v>
       </c>
@@ -5826,7 +5837,7 @@
         <v>24.20296296296296</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>73</v>
       </c>
@@ -5853,7 +5864,7 @@
         <v>30.77</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>74</v>
       </c>
@@ -5880,7 +5891,7 @@
         <v>31.909629629629631</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>75</v>
       </c>
@@ -5907,7 +5918,7 @@
         <v>33.049259259259259</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>76</v>
       </c>
@@ -5934,7 +5945,7 @@
         <v>34.18888888888889</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>77</v>
       </c>
@@ -5961,7 +5972,7 @@
         <v>35.328518518518521</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>78</v>
       </c>
@@ -5988,7 +5999,7 @@
         <v>36.468148148148146</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>79</v>
       </c>
@@ -6015,7 +6026,7 @@
         <v>37.607777777777777</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>80</v>
       </c>
@@ -6042,7 +6053,7 @@
         <v>38.747407407407408</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>81</v>
       </c>
@@ -6069,7 +6080,7 @@
         <v>12.499047619047618</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>82</v>
       </c>
@@ -6096,7 +6107,7 @@
         <v>13.234285714285713</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>83</v>
       </c>
@@ -6123,7 +6134,7 @@
         <v>13.969523809523809</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>84</v>
       </c>
@@ -6150,7 +6161,7 @@
         <v>14.704761904761904</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>85</v>
       </c>
@@ -6177,7 +6188,7 @@
         <v>15.440000000000001</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>86</v>
       </c>
@@ -6204,7 +6215,7 @@
         <v>16.175238095238093</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>87</v>
       </c>
@@ -6231,7 +6242,7 @@
         <v>16.910476190476189</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>88</v>
       </c>
@@ -6258,7 +6269,7 @@
         <v>17.645714285714284</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>89</v>
       </c>
@@ -6285,7 +6296,7 @@
         <v>18.38095238095238</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>90</v>
       </c>
@@ -6312,7 +6323,7 @@
         <v>19.116190476190475</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>91</v>
       </c>
@@ -6339,7 +6350,7 @@
         <v>19.851428571428571</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>92</v>
       </c>
@@ -6366,7 +6377,7 @@
         <v>20.586666666666666</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>93</v>
       </c>
@@ -6393,7 +6404,7 @@
         <v>21.321904761904758</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>94</v>
       </c>
@@ -6420,7 +6431,7 @@
         <v>22.057142857142857</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>95</v>
       </c>
@@ -6447,7 +6458,7 @@
         <v>22.792380952380952</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>96</v>
       </c>
@@ -6474,7 +6485,7 @@
         <v>23.527619047619048</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>97</v>
       </c>
@@ -6501,7 +6512,7 @@
         <v>24.262857142857143</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>129</v>
       </c>
@@ -6528,7 +6539,7 @@
         <v>27.264324324324328</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>130</v>
       </c>
@@ -6555,7 +6566,7 @@
         <v>28.066216216216215</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>131</v>
       </c>
@@ -6582,7 +6593,7 @@
         <v>28.86810810810811</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>132</v>
       </c>
@@ -6609,7 +6620,7 @@
         <v>29.670000000000005</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>133</v>
       </c>
@@ -6636,7 +6647,7 @@
         <v>30.471891891891893</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>134</v>
       </c>
@@ -6663,7 +6674,7 @@
         <v>31.273783783783788</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>135</v>
       </c>
@@ -6690,7 +6701,7 @@
         <v>32.075675675675676</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>136</v>
       </c>
@@ -6717,7 +6728,7 @@
         <v>32.877567567567567</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="7">
         <v>1960</v>
       </c>
@@ -6743,7 +6754,7 @@
         <v>94.88</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>1775</v>
       </c>
@@ -6770,7 +6781,7 @@
         <v>32.075675675675676</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>1776</v>
       </c>
@@ -6797,7 +6808,7 @@
         <v>32.877567567567567</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>1777</v>
       </c>
@@ -6824,7 +6835,7 @@
         <v>33.679459459459466</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>357</v>
       </c>
@@ -6851,7 +6862,7 @@
         <v>15.8424</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>358</v>
       </c>
@@ -6878,7 +6889,7 @@
         <v>16.596799999999998</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>261</v>
       </c>
@@ -6905,7 +6916,7 @@
         <v>17.351200000000002</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>262</v>
       </c>
@@ -6932,7 +6943,7 @@
         <v>18.105599999999999</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>263</v>
       </c>
@@ -6959,7 +6970,7 @@
         <v>18.86</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>264</v>
       </c>
@@ -6986,7 +6997,7 @@
         <v>19.614399999999996</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>265</v>
       </c>
@@ -7013,7 +7024,7 @@
         <v>20.3688</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>266</v>
       </c>
@@ -7040,7 +7051,7 @@
         <v>21.123200000000001</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>267</v>
       </c>
@@ -7067,7 +7078,7 @@
         <v>21.877599999999997</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>268</v>
       </c>
@@ -7094,7 +7105,7 @@
         <v>22.632000000000001</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>269</v>
       </c>
@@ -7121,7 +7132,7 @@
         <v>23.386399999999998</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>270</v>
       </c>
@@ -7148,7 +7159,7 @@
         <v>23.7636</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>271</v>
       </c>
@@ -7175,7 +7186,7 @@
         <v>24.140799999999999</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>272</v>
       </c>
@@ -7202,7 +7213,7 @@
         <v>24.895199999999999</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>1687</v>
       </c>
@@ -7229,7 +7240,7 @@
         <v>19.313684210526315</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>290</v>
       </c>
@@ -7256,7 +7267,7 @@
         <v>27.361052631578943</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>291</v>
       </c>
@@ -7283,7 +7294,7 @@
         <v>28.16578947368421</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>292</v>
       </c>
@@ -7310,7 +7321,7 @@
         <v>28.970526315789471</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>293</v>
       </c>
@@ -7337,7 +7348,7 @@
         <v>29.775263157894734</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>294</v>
       </c>
@@ -7364,7 +7375,7 @@
         <v>30.58</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>295</v>
       </c>
@@ -7391,7 +7402,7 @@
         <v>31.384736842105259</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>296</v>
       </c>
@@ -7418,7 +7429,7 @@
         <v>32.189473684210526</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="7">
         <v>1961</v>
       </c>
@@ -7444,7 +7455,7 @@
         <v>98.7</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>1778</v>
       </c>
@@ -7471,7 +7482,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>1779</v>
       </c>
@@ -7498,7 +7509,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>1780</v>
       </c>
@@ -7525,7 +7536,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>359</v>
       </c>
@@ -7552,7 +7563,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>273</v>
       </c>
@@ -7579,7 +7590,7 @@
         <v>16.59</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>274</v>
       </c>
@@ -7606,7 +7617,7 @@
         <v>17.38</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>275</v>
       </c>
@@ -7633,7 +7644,7 @@
         <v>18.170000000000002</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>276</v>
       </c>
@@ -7660,7 +7671,7 @@
         <v>18.959999999999997</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>277</v>
       </c>
@@ -7687,7 +7698,7 @@
         <v>19.75</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>278</v>
       </c>
@@ -7714,7 +7725,7 @@
         <v>20.54</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>279</v>
       </c>
@@ -7741,7 +7752,7 @@
         <v>19.88</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>280</v>
       </c>
@@ -7768,7 +7779,7 @@
         <v>22.12</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>281</v>
       </c>
@@ -7795,7 +7806,7 @@
         <v>22.91</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>282</v>
       </c>
@@ -7822,7 +7833,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>283</v>
       </c>
@@ -7849,7 +7860,7 @@
         <v>24.490000000000002</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>284</v>
       </c>
@@ -7876,7 +7887,7 @@
         <v>25.28</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>285</v>
       </c>
@@ -7903,7 +7914,7 @@
         <v>26.069999999999997</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="4">
         <v>286</v>
       </c>
@@ -7930,7 +7941,7 @@
         <v>26.86</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>287</v>
       </c>
@@ -7957,7 +7968,7 @@
         <v>27.65</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>288</v>
       </c>
@@ -7984,7 +7995,7 @@
         <v>28.44</v>
       </c>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>289</v>
       </c>
@@ -8011,7 +8022,7 @@
         <v>29.229999999999997</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>1636</v>
       </c>
@@ -8038,7 +8049,7 @@
         <v>16.068292682926828</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>1637</v>
       </c>
@@ -8065,7 +8076,7 @@
         <v>18.478536585365852</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>297</v>
       </c>
@@ -8092,7 +8103,7 @@
         <v>30.529756097560973</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>298</v>
       </c>
@@ -8119,7 +8130,7 @@
         <v>31.333170731707312</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>299</v>
       </c>
@@ -8146,7 +8157,7 @@
         <v>32.136585365853655</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>300</v>
       </c>
@@ -8173,7 +8184,7 @@
         <v>32.94</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>301</v>
       </c>
@@ -8200,7 +8211,7 @@
         <v>33.74341463414634</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>302</v>
       </c>
@@ -8227,7 +8238,7 @@
         <v>34.546829268292683</v>
       </c>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>303</v>
       </c>
@@ -8254,7 +8265,7 @@
         <v>35.350243902439018</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>304</v>
       </c>
@@ -8281,7 +8292,7 @@
         <v>36.153658536585361</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="7">
         <v>1962</v>
       </c>
@@ -8307,7 +8318,7 @@
         <v>107.44</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>1781</v>
       </c>
@@ -8334,7 +8345,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>1782</v>
       </c>
@@ -10542,7 +10553,7 @@
         <v>70</v>
       </c>
       <c r="H282" s="2">
-        <v>3.85</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.25">
@@ -10569,7 +10580,7 @@
         <v>75</v>
       </c>
       <c r="H283" s="2">
-        <v>4.76</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.25">
@@ -10596,7 +10607,7 @@
         <v>140</v>
       </c>
       <c r="H284" s="2">
-        <v>5.47</v>
+        <v>5.91</v>
       </c>
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.25">
@@ -10623,7 +10634,7 @@
         <v>153</v>
       </c>
       <c r="H285" s="2">
-        <v>7.03</v>
+        <v>7.59</v>
       </c>
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.25">
@@ -10671,7 +10682,7 @@
         <v>99</v>
       </c>
       <c r="H287" s="2">
-        <v>10.42</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="288" spans="1:8" x14ac:dyDescent="0.25">
@@ -10719,7 +10730,7 @@
         <v>122</v>
       </c>
       <c r="H289" s="2">
-        <v>5.21</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="290" spans="1:8" x14ac:dyDescent="0.25">
@@ -10746,7 +10757,7 @@
         <v>79</v>
       </c>
       <c r="H290" s="2">
-        <v>6.58</v>
+        <v>7.11</v>
       </c>
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.25">
@@ -10773,7 +10784,7 @@
         <v>86</v>
       </c>
       <c r="H291" s="2">
-        <v>7.7</v>
+        <v>8.32</v>
       </c>
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.25">
@@ -10800,7 +10811,7 @@
         <v>94</v>
       </c>
       <c r="H292" s="2">
-        <v>9.99</v>
+        <v>10.79</v>
       </c>
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.25">
@@ -10848,7 +10859,7 @@
         <v>168</v>
       </c>
       <c r="H294" s="2">
-        <v>14.3</v>
+        <v>15.44</v>
       </c>
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.25">
@@ -12621,7 +12632,7 @@
         <v>17.34</v>
       </c>
     </row>
-    <row r="365" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365">
         <v>4</v>
       </c>
@@ -12648,7 +12659,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="366" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366">
         <v>731</v>
       </c>
@@ -12675,7 +12686,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="367" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367">
         <v>730</v>
       </c>
@@ -12702,7 +12713,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="368" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368">
         <v>495</v>
       </c>
@@ -12726,7 +12737,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="369" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369">
         <v>2019</v>
       </c>
@@ -12753,7 +12764,7 @@
         <v>22.79</v>
       </c>
     </row>
-    <row r="370" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370">
         <v>1819</v>
       </c>
@@ -12780,7 +12791,7 @@
         <v>16.87</v>
       </c>
     </row>
-    <row r="371" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371">
         <v>2011</v>
       </c>
@@ -12807,7 +12818,7 @@
         <v>58.6</v>
       </c>
     </row>
-    <row r="372" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372">
         <v>2010</v>
       </c>
@@ -12834,7 +12845,7 @@
         <v>25.71</v>
       </c>
     </row>
-    <row r="373" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373">
         <v>1822</v>
       </c>
@@ -12861,7 +12872,7 @@
         <v>24.51</v>
       </c>
     </row>
-    <row r="374" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374">
         <v>1797</v>
       </c>
@@ -12904,6 +12915,10 @@
       <c r="F375" t="s">
         <v>4</v>
       </c>
+      <c r="G375" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - FARMA 08CM x 1,20M</v>
+      </c>
       <c r="H375" s="34">
         <v>3.9528000000000003</v>
       </c>
@@ -12927,6 +12942,10 @@
       <c r="F376" t="s">
         <v>4</v>
       </c>
+      <c r="G376" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - FARMA 10CM x 1,20M</v>
+      </c>
       <c r="H376" s="37">
         <v>4.2876000000000003</v>
       </c>
@@ -12950,6 +12969,10 @@
       <c r="F377" t="s">
         <v>4</v>
       </c>
+      <c r="G377" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - FARMA 12CM x 1,20M</v>
+      </c>
       <c r="H377" s="38">
         <v>5.3028000000000004</v>
       </c>
@@ -12973,6 +12996,10 @@
       <c r="F378" t="s">
         <v>4</v>
       </c>
+      <c r="G378" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - FARMA 15CM x 1,20M</v>
+      </c>
       <c r="H378" s="38">
         <v>6.0804</v>
       </c>
@@ -12996,6 +13023,10 @@
       <c r="F379" t="s">
         <v>4</v>
       </c>
+      <c r="G379" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - FARMA 20CM x 1,20M</v>
+      </c>
       <c r="H379" s="38">
         <v>7.83</v>
       </c>
@@ -13019,6 +13050,10 @@
       <c r="F380" t="s">
         <v>4</v>
       </c>
+      <c r="G380" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - FARMA 30CM x 1,20M</v>
+      </c>
       <c r="H380" s="38">
         <v>11.5992</v>
       </c>
@@ -13042,6 +13077,10 @@
       <c r="F381" t="s">
         <v>4</v>
       </c>
+      <c r="G381" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - FARMA 08CM x 1,80M</v>
+      </c>
       <c r="H381" s="33">
         <v>5.3567999999999998</v>
       </c>
@@ -13065,6 +13104,10 @@
       <c r="F382" t="s">
         <v>4</v>
       </c>
+      <c r="G382" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - FARMA 10CM x 1,80M</v>
+      </c>
       <c r="H382" s="38">
         <v>5.8103999999999996</v>
       </c>
@@ -13088,6 +13131,10 @@
       <c r="F383" t="s">
         <v>4</v>
       </c>
+      <c r="G383" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - FARMA 12CM x 1,80M</v>
+      </c>
       <c r="H383" s="38">
         <v>7.3224</v>
       </c>
@@ -13111,6 +13158,10 @@
       <c r="F384" t="s">
         <v>4</v>
       </c>
+      <c r="G384" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - FARMA 15CM x 1,80M</v>
+      </c>
       <c r="H384" s="38">
         <v>8.5752000000000006</v>
       </c>
@@ -13134,6 +13185,10 @@
       <c r="F385" t="s">
         <v>4</v>
       </c>
+      <c r="G385" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - FARMA 20CM x 1,80M</v>
+      </c>
       <c r="H385" s="39">
         <v>11.124000000000001</v>
       </c>
@@ -13157,6 +13212,10 @@
       <c r="F386" t="s">
         <v>4</v>
       </c>
+      <c r="G386" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - FARMA 30CM x 1,80M</v>
+      </c>
       <c r="H386" s="37">
         <v>15.9192</v>
       </c>
@@ -13180,6 +13239,10 @@
       <c r="F387" t="s">
         <v>4</v>
       </c>
+      <c r="G387" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - HOSPITALAR 10CM x 1,20M</v>
+      </c>
       <c r="H387" s="38">
         <v>4.1580000000000004</v>
       </c>
@@ -13203,6 +13266,10 @@
       <c r="F388" t="s">
         <v>4</v>
       </c>
+      <c r="G388" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - HOSPITALAR 12CM x 1,20M</v>
+      </c>
       <c r="H388" s="38">
         <v>5.1407999999999996</v>
       </c>
@@ -13226,6 +13293,10 @@
       <c r="F389" t="s">
         <v>4</v>
       </c>
+      <c r="G389" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - HOSPITALAR 15CM x 1,20M</v>
+      </c>
       <c r="H389" s="38">
         <v>5.9075999999999995</v>
       </c>
@@ -13249,6 +13320,10 @@
       <c r="F390" t="s">
         <v>4</v>
       </c>
+      <c r="G390" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - HOSPITALAR 20CM x 1,20M</v>
+      </c>
       <c r="H390" s="38">
         <v>7.5924000000000005</v>
       </c>
@@ -13272,6 +13347,10 @@
       <c r="F391" t="s">
         <v>4</v>
       </c>
+      <c r="G391" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - HOSPITALAR 30CM x 1,20M</v>
+      </c>
       <c r="H391" s="38">
         <v>11.2536</v>
       </c>
@@ -13295,6 +13374,10 @@
       <c r="F392" t="s">
         <v>4</v>
       </c>
+      <c r="G392" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - HOSPITALAR 10CM x 1,80M</v>
+      </c>
       <c r="H392" s="38">
         <v>5.6268000000000002</v>
       </c>
@@ -13318,6 +13401,10 @@
       <c r="F393" t="s">
         <v>4</v>
       </c>
+      <c r="G393" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - HOSPITALAR 12CM x 1,80M</v>
+      </c>
       <c r="H393" s="38">
         <v>7.1063999999999998</v>
       </c>
@@ -13341,6 +13428,10 @@
       <c r="F394" t="s">
         <v>4</v>
       </c>
+      <c r="G394" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - HOSPITALAR 15CM x 1,80M</v>
+      </c>
       <c r="H394" s="38">
         <v>8.3160000000000007</v>
       </c>
@@ -13364,6 +13455,10 @@
       <c r="F395" t="s">
         <v>4</v>
       </c>
+      <c r="G395" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - HOSPITALAR 20CM x 1,80M</v>
+      </c>
       <c r="H395" s="39">
         <v>10.789200000000001</v>
       </c>
@@ -13387,7 +13482,10 @@
       <c r="F396" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="G396" s="42"/>
+      <c r="G396" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - HOSPITALAR 30CM x 1,80M</v>
+      </c>
       <c r="H396" s="43">
         <v>15.444000000000001</v>
       </c>
@@ -13411,6 +13509,10 @@
       <c r="F397" t="s">
         <v>417</v>
       </c>
+      <c r="G397" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - FARMA 08CM x 1,20M</v>
+      </c>
       <c r="H397" s="44">
         <v>4.6115999999999993</v>
       </c>
@@ -13434,6 +13536,10 @@
       <c r="F398" t="s">
         <v>417</v>
       </c>
+      <c r="G398" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - FARMA 10CM x 1,20M</v>
+      </c>
       <c r="H398" s="44">
         <v>5.0111999999999997</v>
       </c>
@@ -13457,6 +13563,10 @@
       <c r="F399" t="s">
         <v>417</v>
       </c>
+      <c r="G399" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - FARMA 12CM x 1,20M</v>
+      </c>
       <c r="H399" s="45">
         <v>6.1992000000000003</v>
       </c>
@@ -13480,6 +13590,10 @@
       <c r="F400" t="s">
         <v>417</v>
       </c>
+      <c r="G400" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - FARMA 15CM x 1,20M</v>
+      </c>
       <c r="H400" s="45">
         <v>7.0956000000000001</v>
       </c>
@@ -13503,6 +13617,10 @@
       <c r="F401" t="s">
         <v>417</v>
       </c>
+      <c r="G401" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - FARMA 20CM x 1,20M</v>
+      </c>
       <c r="H401" s="45">
         <v>9.1259999999999994</v>
       </c>
@@ -13526,6 +13644,10 @@
       <c r="F402" t="s">
         <v>417</v>
       </c>
+      <c r="G402" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - FARMA 30CM x 1,20M</v>
+      </c>
       <c r="H402" s="45">
         <v>13.586399999999999</v>
       </c>
@@ -13549,6 +13671,10 @@
       <c r="F403" t="s">
         <v>417</v>
       </c>
+      <c r="G403" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - FARMA 08CM x 1,80M</v>
+      </c>
       <c r="H403" s="45">
         <v>6.3720000000000008</v>
       </c>
@@ -13572,6 +13698,10 @@
       <c r="F404" t="s">
         <v>417</v>
       </c>
+      <c r="G404" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - FARMA 10CM x 1,80M</v>
+      </c>
       <c r="H404" s="45">
         <v>6.9228000000000005</v>
       </c>
@@ -13595,6 +13725,10 @@
       <c r="F405" t="s">
         <v>417</v>
       </c>
+      <c r="G405" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - FARMA 12CM x 1,80M</v>
+      </c>
       <c r="H405" s="45">
         <v>8.5535999999999994</v>
       </c>
@@ -13618,6 +13752,10 @@
       <c r="F406" t="s">
         <v>417</v>
       </c>
+      <c r="G406" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - FARMA 15CM x 1,80M</v>
+      </c>
       <c r="H406" s="45">
         <v>10.119599999999998</v>
       </c>
@@ -13641,6 +13779,10 @@
       <c r="F407" t="s">
         <v>417</v>
       </c>
+      <c r="G407" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - FARMA 20CM x 1,80M</v>
+      </c>
       <c r="H407" s="45">
         <v>12.9924</v>
       </c>
@@ -13664,6 +13806,10 @@
       <c r="F408" t="s">
         <v>417</v>
       </c>
+      <c r="G408" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - FARMA 30CM x 1,80M</v>
+      </c>
       <c r="H408" s="46">
         <v>18.7272</v>
       </c>
@@ -13687,6 +13833,10 @@
       <c r="F409" t="s">
         <v>417</v>
       </c>
+      <c r="G409" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - HOSPITALAR 10CM x 1,20M</v>
+      </c>
       <c r="H409" s="44">
         <v>4.8600000000000003</v>
       </c>
@@ -13710,6 +13860,10 @@
       <c r="F410" t="s">
         <v>417</v>
       </c>
+      <c r="G410" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - HOSPITALAR 12CM x 1,20M</v>
+      </c>
       <c r="H410" s="45">
         <v>6.0156000000000001</v>
       </c>
@@ -13733,6 +13887,10 @@
       <c r="F411" t="s">
         <v>417</v>
       </c>
+      <c r="G411" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - HOSPITALAR 15CM x 1,20M</v>
+      </c>
       <c r="H411" s="45">
         <v>6.8903999999999996</v>
       </c>
@@ -13756,6 +13914,10 @@
       <c r="F412" t="s">
         <v>417</v>
       </c>
+      <c r="G412" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - HOSPITALAR 20CM x 1,20M</v>
+      </c>
       <c r="H412" s="45">
         <v>8.8452000000000002</v>
       </c>
@@ -13779,6 +13941,10 @@
       <c r="F413" t="s">
         <v>417</v>
       </c>
+      <c r="G413" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - HOSPITALAR 30CM x 1,20M</v>
+      </c>
       <c r="H413" s="45">
         <v>13.186800000000002</v>
       </c>
@@ -13802,6 +13968,10 @@
       <c r="F414" t="s">
         <v>417</v>
       </c>
+      <c r="G414" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - HOSPITALAR 10CM x 1,80M</v>
+      </c>
       <c r="H414" s="45">
         <v>6.7284000000000006</v>
       </c>
@@ -13825,6 +13995,10 @@
       <c r="F415" t="s">
         <v>417</v>
       </c>
+      <c r="G415" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - HOSPITALAR 12CM x 1,80M</v>
+      </c>
       <c r="H415" s="45">
         <v>8.2835999999999999</v>
       </c>
@@ -13848,6 +14022,10 @@
       <c r="F416" t="s">
         <v>417</v>
       </c>
+      <c r="G416" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - HOSPITALAR 15CM x 1,80M</v>
+      </c>
       <c r="H416" s="45">
         <v>9.8064</v>
       </c>
@@ -13871,6 +14049,10 @@
       <c r="F417" t="s">
         <v>417</v>
       </c>
+      <c r="G417" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - HOSPITALAR 20CM x 1,80M</v>
+      </c>
       <c r="H417" s="45">
         <v>12.6036</v>
       </c>
@@ -13894,7 +14076,10 @@
       <c r="F418" s="42" t="s">
         <v>417</v>
       </c>
-      <c r="G418" s="42"/>
+      <c r="G418" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - HOSPITALAR 30CM x 1,80M</v>
+      </c>
       <c r="H418" s="46">
         <v>18.176399999999997</v>
       </c>
@@ -13917,6 +14102,10 @@
       </c>
       <c r="F419" t="s">
         <v>411</v>
+      </c>
+      <c r="G419" t="str">
+        <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
+        <v>ATADURA DE CREPE - FARMA 08CM x 1,80M</v>
       </c>
       <c r="H419" s="2">
         <v>6.37</v>

--- a/dados/Produtos_Agrupados_Completos_conciliados.xlsx
+++ b/dados/Produtos_Agrupados_Completos_conciliados.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37ED9916-41A0-4286-8D91-0795EBFA2E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{549D400E-FFFE-49B0-8E9D-864369D3CF98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{86B17377-32DB-438B-8A03-02E761646E6D}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Estoque" sheetId="6" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="DadosExternos_1" localSheetId="0" hidden="1">CONCILIADA!$A$1:$G$419</definedName>
+    <definedName name="DadosExternos_1" localSheetId="0" hidden="1">CONCILIADA!$A$1:$G$469</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3393" uniqueCount="530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3527" uniqueCount="535">
   <si>
     <t>Grupo</t>
   </si>
@@ -1642,6 +1642,21 @@
   </si>
   <si>
     <t>GAZE NAO ESTÉRIL 09 FIOS</t>
+  </si>
+  <si>
+    <t>CAMPO 25X28</t>
+  </si>
+  <si>
+    <t>ESTERIL 11 FIOS</t>
+  </si>
+  <si>
+    <t>COMPRESSA</t>
+  </si>
+  <si>
+    <t>ROLO</t>
+  </si>
+  <si>
+    <t>ultra Textil</t>
   </si>
 </sst>
 </file>
@@ -1847,7 +1862,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -1925,7 +1940,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1944,6 +1958,21 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="17">
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;gramas&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2229,21 +2258,6 @@
         <horizontal/>
       </border>
     </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;gramas&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2275,23 +2289,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5499586E-A189-44D8-9C58-8F69F4EC7CA4}" name="Tabela14" displayName="Tabela14" ref="A1:H419" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:H419" xr:uid="{5499586E-A189-44D8-9C58-8F69F4EC7CA4}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="ATADURA DE CREPE - FARMA"/>
-        <filter val="ATADURA DE CREPE - HOSPITALAR"/>
-        <filter val="ATADURAS LINHA FARMA"/>
-        <filter val="ATADURAS LINHA HOSPITALAR"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5499586E-A189-44D8-9C58-8F69F4EC7CA4}" name="Tabela14" displayName="Tabela14" ref="A1:H469" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:H469" xr:uid="{5499586E-A189-44D8-9C58-8F69F4EC7CA4}"/>
   <tableColumns count="8">
-    <tableColumn id="2" xr3:uid="{3202AFED-4A11-4AD5-8FCF-B57F6545F53A}" uniqueName="2" name="ID_COD" queryTableFieldId="2" dataDxfId="16"/>
-    <tableColumn id="1" xr3:uid="{5387F357-AA02-4B91-B30F-AB45B122F19D}" uniqueName="1" name="Grupo" queryTableFieldId="1" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{AF8B37DC-8D9E-415B-8540-844DCFD3C2C2}" uniqueName="3" name="Descrição" queryTableFieldId="3" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{15BCD1FE-6E96-4337-BF2C-1D0977BEE2EA}" uniqueName="4" name="Linha" queryTableFieldId="4" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{5AEAA593-AC57-42D0-80C6-A7ADC3170E25}" uniqueName="5" name="Gramatura" queryTableFieldId="5" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{3202AFED-4A11-4AD5-8FCF-B57F6545F53A}" uniqueName="2" name="ID_COD" queryTableFieldId="2" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{5387F357-AA02-4B91-B30F-AB45B122F19D}" uniqueName="1" name="Grupo" queryTableFieldId="1" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{AF8B37DC-8D9E-415B-8540-844DCFD3C2C2}" uniqueName="3" name="Descrição" queryTableFieldId="3" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{15BCD1FE-6E96-4337-BF2C-1D0977BEE2EA}" uniqueName="4" name="Linha" queryTableFieldId="4" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{5AEAA593-AC57-42D0-80C6-A7ADC3170E25}" uniqueName="5" name="Gramatura" queryTableFieldId="5" dataDxfId="0"/>
     <tableColumn id="6" xr3:uid="{F34DF2E2-4CF9-47F8-995C-D81C98BE9A01}" uniqueName="6" name="CX_EMB" queryTableFieldId="6"/>
     <tableColumn id="7" xr3:uid="{A488A8F9-38D4-4F27-9DEA-CC2F81D9C55C}" uniqueName="7" name="DESCRICAONF" queryTableFieldId="7"/>
     <tableColumn id="9" xr3:uid="{079BA53C-EB2B-4DA2-B65C-026F685E0107}" uniqueName="9" name="PRECO" queryTableFieldId="9" dataCellStyle="Moeda"/>
@@ -2311,29 +2316,23 @@
     <tableColumn id="5" xr3:uid="{03935235-5821-4D37-9442-36D791826C89}" name="Unid_Caixa"/>
     <tableColumn id="6" xr3:uid="{D35B3B9C-9008-4300-92B8-8167B4A2CCB6}" name="Linha"/>
     <tableColumn id="7" xr3:uid="{AC4BD377-A729-4B2F-8A6E-77B18350EAA3}" name="Gramat"/>
-    <tableColumn id="8" xr3:uid="{774C2D1E-0273-4A4C-B69B-084FE44C378A}" name="Preco" dataDxfId="11"/>
+    <tableColumn id="8" xr3:uid="{774C2D1E-0273-4A4C-B69B-084FE44C378A}" name="Preco" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B6E4AB22-CC81-46A5-8E9D-BA15DF99BBB0}" name="Tabela2" displayName="Tabela2" ref="A1:G400" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
-  <autoFilter ref="A1:G400" xr:uid="{B6E4AB22-CC81-46A5-8E9D-BA15DF99BBB0}">
-    <filterColumn colId="5">
-      <filters blank="1">
-        <filter val="0"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B6E4AB22-CC81-46A5-8E9D-BA15DF99BBB0}" name="Tabela2" displayName="Tabela2" ref="A1:G400" totalsRowShown="0" headerRowDxfId="15" headerRowBorderDxfId="14" tableBorderDxfId="13" totalsRowBorderDxfId="12">
+  <autoFilter ref="A1:G400" xr:uid="{B6E4AB22-CC81-46A5-8E9D-BA15DF99BBB0}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{49F9A101-1F65-4A1E-A291-21E325604A24}" name="COD" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{B6B5DE3B-A99A-4156-AA8B-3D83F4E34F3F}" name="DESCRIÇÃO" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{3D38594D-4732-42D1-8F09-82A15D4753CB}" name="PESO" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{73AD5E7C-295D-4E24-AF22-1C03AAA6FE04}" name="TIPO" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{897DAD0D-6A3C-443B-BCC5-B43C099F2C1B}" name="VOL." dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{5A2A3043-C96F-46DD-B142-DEB2458C1999}" name="UNID." dataDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{9BDA27C3-1490-4741-A5E9-29B583E36E56}" name="TOTAL" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{49F9A101-1F65-4A1E-A291-21E325604A24}" name="COD" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{B6B5DE3B-A99A-4156-AA8B-3D83F4E34F3F}" name="DESCRIÇÃO" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{3D38594D-4732-42D1-8F09-82A15D4753CB}" name="PESO" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{73AD5E7C-295D-4E24-AF22-1C03AAA6FE04}" name="TIPO" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{897DAD0D-6A3C-443B-BCC5-B43C099F2C1B}" name="VOL." dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{5A2A3043-C96F-46DD-B142-DEB2458C1999}" name="UNID." dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{9BDA27C3-1490-4741-A5E9-29B583E36E56}" name="TOTAL" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2636,7 +2635,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{868BC1FE-16FA-4E4B-B34E-F84713378B87}">
-  <dimension ref="A1:H419"/>
+  <dimension ref="A1:H469"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -2675,7 +2674,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2703,7 +2702,7 @@
         <v>0.41039999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2731,7 +2730,7 @@
         <v>0.43200000000000005</v>
       </c>
     </row>
-    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2759,7 +2758,7 @@
         <v>0.4536</v>
       </c>
     </row>
-    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>152</v>
       </c>
@@ -2787,7 +2786,7 @@
         <v>0.47520000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>153</v>
       </c>
@@ -2815,7 +2814,7 @@
         <v>0.50759999999999994</v>
       </c>
     </row>
-    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>154</v>
       </c>
@@ -2843,7 +2842,7 @@
         <v>0.5292</v>
       </c>
     </row>
-    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1641</v>
       </c>
@@ -2871,7 +2870,7 @@
         <v>0.64800000000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1642</v>
       </c>
@@ -2899,7 +2898,7 @@
         <v>0.66959999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1643</v>
       </c>
@@ -2927,7 +2926,7 @@
         <v>0.70200000000000007</v>
       </c>
     </row>
-    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>1587</v>
       </c>
@@ -2955,7 +2954,7 @@
         <v>2.8839999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>1588</v>
       </c>
@@ -2983,7 +2982,7 @@
         <v>5.3353999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>1586</v>
       </c>
@@ -3010,7 +3009,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>157</v>
       </c>
@@ -3038,7 +3037,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>158</v>
       </c>
@@ -3066,7 +3065,7 @@
         <v>7.1894</v>
       </c>
     </row>
-    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>155</v>
       </c>
@@ -3093,7 +3092,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>1639</v>
       </c>
@@ -3121,7 +3120,7 @@
         <v>4.4084000000000003</v>
       </c>
     </row>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>1640</v>
       </c>
@@ -3148,7 +3147,7 @@
         <v>7.96</v>
       </c>
     </row>
-    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>1209</v>
       </c>
@@ -3175,7 +3174,7 @@
         <v>86.5</v>
       </c>
     </row>
-    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>5</v>
       </c>
@@ -3203,7 +3202,7 @@
         <v>4.66</v>
       </c>
     </row>
-    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>6</v>
       </c>
@@ -3231,7 +3230,7 @@
         <v>5.3257142857142865</v>
       </c>
     </row>
-    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>7</v>
       </c>
@@ -3259,7 +3258,7 @@
         <v>5.991428571428572</v>
       </c>
     </row>
-    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>8</v>
       </c>
@@ -3286,7 +3285,7 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>9</v>
       </c>
@@ -3313,7 +3312,7 @@
         <v>7.322857142857143</v>
       </c>
     </row>
-    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>10</v>
       </c>
@@ -3340,7 +3339,7 @@
         <v>7.9885714285714293</v>
       </c>
     </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>11</v>
       </c>
@@ -3367,7 +3366,7 @@
         <v>8.6542857142857148</v>
       </c>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>12</v>
       </c>
@@ -3394,7 +3393,7 @@
         <v>9.32</v>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>13</v>
       </c>
@@ -3421,7 +3420,7 @@
         <v>10.88</v>
       </c>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>14</v>
       </c>
@@ -3448,7 +3447,7 @@
         <v>10.651428571428573</v>
       </c>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>15</v>
       </c>
@@ -3475,7 +3474,7 @@
         <v>11.317142857142857</v>
       </c>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>16</v>
       </c>
@@ -3502,7 +3501,7 @@
         <v>11.982857142857144</v>
       </c>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>17</v>
       </c>
@@ -3529,7 +3528,7 @@
         <v>12.648571428571429</v>
       </c>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>18</v>
       </c>
@@ -3556,7 +3555,7 @@
         <v>13.314285714285715</v>
       </c>
     </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>51</v>
       </c>
@@ -3583,7 +3582,7 @@
         <v>14.46</v>
       </c>
     </row>
-    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>52</v>
       </c>
@@ -3610,7 +3609,7 @@
         <v>15.148571428571429</v>
       </c>
     </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>53</v>
       </c>
@@ -3637,7 +3636,7 @@
         <v>15.837142857142858</v>
       </c>
     </row>
-    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>54</v>
       </c>
@@ -3664,7 +3663,7 @@
         <v>16.525714285714287</v>
       </c>
     </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>55</v>
       </c>
@@ -3691,7 +3690,7 @@
         <v>17.214285714285715</v>
       </c>
     </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>56</v>
       </c>
@@ -3718,7 +3717,7 @@
         <v>17.902857142857144</v>
       </c>
     </row>
-    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>57</v>
       </c>
@@ -3745,7 +3744,7 @@
         <v>18.591428571428573</v>
       </c>
     </row>
-    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>58</v>
       </c>
@@ -3772,7 +3771,7 @@
         <v>19.28</v>
       </c>
     </row>
-    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>59</v>
       </c>
@@ -3799,7 +3798,7 @@
         <v>19.96857142857143</v>
       </c>
     </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>60</v>
       </c>
@@ -3826,7 +3825,7 @@
         <v>20.657142857142858</v>
       </c>
     </row>
-    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>61</v>
       </c>
@@ -3853,7 +3852,7 @@
         <v>21.345714285714287</v>
       </c>
     </row>
-    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>19</v>
       </c>
@@ -3880,7 +3879,7 @@
         <v>22.034285714285719</v>
       </c>
     </row>
-    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>1754</v>
       </c>
@@ -3907,7 +3906,7 @@
         <v>27.880000000000003</v>
       </c>
     </row>
-    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>1774</v>
       </c>
@@ -3934,7 +3933,7 @@
         <v>29.207619047619044</v>
       </c>
     </row>
-    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>307</v>
       </c>
@@ -3961,7 +3960,7 @@
         <v>7.4923076923076923</v>
       </c>
     </row>
-    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>308</v>
       </c>
@@ -3988,7 +3987,7 @@
         <v>8.2415384615384628</v>
       </c>
     </row>
-    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>309</v>
       </c>
@@ -4015,7 +4014,7 @@
         <v>8.9907692307692297</v>
       </c>
     </row>
-    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>310</v>
       </c>
@@ -4042,7 +4041,7 @@
         <v>9.74</v>
       </c>
     </row>
-    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>311</v>
       </c>
@@ -4069,7 +4068,7 @@
         <v>10.489230769230771</v>
       </c>
     </row>
-    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>312</v>
       </c>
@@ -4096,7 +4095,7 @@
         <v>11.238461538461538</v>
       </c>
     </row>
-    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>313</v>
       </c>
@@ -4123,7 +4122,7 @@
         <v>11.98</v>
       </c>
     </row>
-    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>314</v>
       </c>
@@ -4150,7 +4149,7 @@
         <v>12.736923076923077</v>
       </c>
     </row>
-    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>315</v>
       </c>
@@ -4177,7 +4176,7 @@
         <v>13.486153846153847</v>
       </c>
     </row>
-    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>316</v>
       </c>
@@ -4204,7 +4203,7 @@
         <v>14.235384615384616</v>
       </c>
     </row>
-    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>317</v>
       </c>
@@ -4231,7 +4230,7 @@
         <v>14.984615384615385</v>
       </c>
     </row>
-    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>318</v>
       </c>
@@ -4258,7 +4257,7 @@
         <v>15.733846153846155</v>
       </c>
     </row>
-    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>319</v>
       </c>
@@ -4285,7 +4284,7 @@
         <v>16.483076923076926</v>
       </c>
     </row>
-    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>320</v>
       </c>
@@ -4312,7 +4311,7 @@
         <v>17.232307692307696</v>
       </c>
     </row>
-    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>1690</v>
       </c>
@@ -4339,7 +4338,7 @@
         <v>18.73076923076923</v>
       </c>
     </row>
-    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>339</v>
       </c>
@@ -4366,7 +4365,7 @@
         <v>16.579999999999998</v>
       </c>
     </row>
-    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -4393,7 +4392,7 @@
         <v>17.270833333333332</v>
       </c>
     </row>
-    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>340</v>
       </c>
@@ -4420,7 +4419,7 @@
         <v>17.961666666666662</v>
       </c>
     </row>
-    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>341</v>
       </c>
@@ -4447,7 +4446,7 @@
         <v>18.652499999999996</v>
       </c>
     </row>
-    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>342</v>
       </c>
@@ -4474,7 +4473,7 @@
         <v>19.34333333333333</v>
       </c>
     </row>
-    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>343</v>
       </c>
@@ -4501,7 +4500,7 @@
         <v>20.034166666666668</v>
       </c>
     </row>
-    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>344</v>
       </c>
@@ -4528,7 +4527,7 @@
         <v>20.724999999999998</v>
       </c>
     </row>
-    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>345</v>
       </c>
@@ -4555,7 +4554,7 @@
         <v>21.415833333333332</v>
       </c>
     </row>
-    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>346</v>
       </c>
@@ -4582,7 +4581,7 @@
         <v>22.106666666666666</v>
       </c>
     </row>
-    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>347</v>
       </c>
@@ -4609,7 +4608,7 @@
         <v>22.797499999999999</v>
       </c>
     </row>
-    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>348</v>
       </c>
@@ -4636,7 +4635,7 @@
         <v>23.488333333333333</v>
       </c>
     </row>
-    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>1700</v>
       </c>
@@ -4663,7 +4662,7 @@
         <v>28.77</v>
       </c>
     </row>
-    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>1697</v>
       </c>
@@ -4690,7 +4689,7 @@
         <v>29.96875</v>
       </c>
     </row>
-    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>321</v>
       </c>
@@ -4717,7 +4716,7 @@
         <v>7.9</v>
       </c>
     </row>
-    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>322</v>
       </c>
@@ -4744,7 +4743,7 @@
         <v>8.69</v>
       </c>
     </row>
-    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>323</v>
       </c>
@@ -4771,7 +4770,7 @@
         <v>9.48</v>
       </c>
     </row>
-    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>324</v>
       </c>
@@ -4798,7 +4797,7 @@
         <v>10.27</v>
       </c>
     </row>
-    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>325</v>
       </c>
@@ -4825,7 +4824,7 @@
         <v>11.06</v>
       </c>
     </row>
-    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>326</v>
       </c>
@@ -4852,7 +4851,7 @@
         <v>11.85</v>
       </c>
     </row>
-    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>327</v>
       </c>
@@ -4879,7 +4878,7 @@
         <v>12.64</v>
       </c>
     </row>
-    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>328</v>
       </c>
@@ -4906,7 +4905,7 @@
         <v>13.43</v>
       </c>
     </row>
-    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>329</v>
       </c>
@@ -4933,7 +4932,7 @@
         <v>14.22</v>
       </c>
     </row>
-    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>330</v>
       </c>
@@ -4960,7 +4959,7 @@
         <v>15.01</v>
       </c>
     </row>
-    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>331</v>
       </c>
@@ -4987,7 +4986,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>332</v>
       </c>
@@ -5014,7 +5013,7 @@
         <v>16.59</v>
       </c>
     </row>
-    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>333</v>
       </c>
@@ -5041,7 +5040,7 @@
         <v>17.38</v>
       </c>
     </row>
-    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>334</v>
       </c>
@@ -5068,7 +5067,7 @@
         <v>18.170000000000002</v>
       </c>
     </row>
-    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>335</v>
       </c>
@@ -5095,7 +5094,7 @@
         <v>18.96</v>
       </c>
     </row>
-    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>336</v>
       </c>
@@ -5122,7 +5121,7 @@
         <v>19.75</v>
       </c>
     </row>
-    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>337</v>
       </c>
@@ -5149,7 +5148,7 @@
         <v>20.54</v>
       </c>
     </row>
-    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>1699</v>
       </c>
@@ -5176,7 +5175,7 @@
         <v>13.525185185185185</v>
       </c>
     </row>
-    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>1773</v>
       </c>
@@ -5203,7 +5202,7 @@
         <v>14.948888888888888</v>
       </c>
     </row>
-    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>349</v>
       </c>
@@ -5230,7 +5229,7 @@
         <v>19.22</v>
       </c>
     </row>
-    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>350</v>
       </c>
@@ -5257,7 +5256,7 @@
         <v>19.931851851851849</v>
       </c>
     </row>
-    <row r="97" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>351</v>
       </c>
@@ -5284,7 +5283,7 @@
         <v>20.6437037037037</v>
       </c>
     </row>
-    <row r="98" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>352</v>
       </c>
@@ -5311,7 +5310,7 @@
         <v>21.355555555555554</v>
       </c>
     </row>
-    <row r="99" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>353</v>
       </c>
@@ -5338,7 +5337,7 @@
         <v>22.067407407407408</v>
       </c>
     </row>
-    <row r="100" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>354</v>
       </c>
@@ -5365,7 +5364,7 @@
         <v>22.779259259259259</v>
       </c>
     </row>
-    <row r="101" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>355</v>
       </c>
@@ -5392,7 +5391,7 @@
         <v>23.49111111111111</v>
       </c>
     </row>
-    <row r="102" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>356</v>
       </c>
@@ -5419,7 +5418,7 @@
         <v>24.20296296296296</v>
       </c>
     </row>
-    <row r="103" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>73</v>
       </c>
@@ -5446,7 +5445,7 @@
         <v>30.77</v>
       </c>
     </row>
-    <row r="104" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>74</v>
       </c>
@@ -5473,7 +5472,7 @@
         <v>31.909629629629631</v>
       </c>
     </row>
-    <row r="105" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>75</v>
       </c>
@@ -5500,7 +5499,7 @@
         <v>33.049259259259259</v>
       </c>
     </row>
-    <row r="106" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>76</v>
       </c>
@@ -5527,7 +5526,7 @@
         <v>34.18888888888889</v>
       </c>
     </row>
-    <row r="107" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>77</v>
       </c>
@@ -5554,7 +5553,7 @@
         <v>35.328518518518521</v>
       </c>
     </row>
-    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>78</v>
       </c>
@@ -5581,7 +5580,7 @@
         <v>36.468148148148146</v>
       </c>
     </row>
-    <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>79</v>
       </c>
@@ -5608,7 +5607,7 @@
         <v>37.607777777777777</v>
       </c>
     </row>
-    <row r="110" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>80</v>
       </c>
@@ -5635,7 +5634,7 @@
         <v>38.747407407407408</v>
       </c>
     </row>
-    <row r="111" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>81</v>
       </c>
@@ -5662,7 +5661,7 @@
         <v>12.499047619047618</v>
       </c>
     </row>
-    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>82</v>
       </c>
@@ -5689,7 +5688,7 @@
         <v>13.234285714285713</v>
       </c>
     </row>
-    <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>83</v>
       </c>
@@ -5716,7 +5715,7 @@
         <v>13.969523809523809</v>
       </c>
     </row>
-    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>84</v>
       </c>
@@ -5743,7 +5742,7 @@
         <v>14.704761904761904</v>
       </c>
     </row>
-    <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>85</v>
       </c>
@@ -5770,7 +5769,7 @@
         <v>15.440000000000001</v>
       </c>
     </row>
-    <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>86</v>
       </c>
@@ -5797,7 +5796,7 @@
         <v>16.175238095238093</v>
       </c>
     </row>
-    <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>87</v>
       </c>
@@ -5824,7 +5823,7 @@
         <v>16.910476190476189</v>
       </c>
     </row>
-    <row r="118" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>88</v>
       </c>
@@ -5851,7 +5850,7 @@
         <v>17.645714285714284</v>
       </c>
     </row>
-    <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>89</v>
       </c>
@@ -5878,7 +5877,7 @@
         <v>18.38095238095238</v>
       </c>
     </row>
-    <row r="120" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>90</v>
       </c>
@@ -5905,7 +5904,7 @@
         <v>19.116190476190475</v>
       </c>
     </row>
-    <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>91</v>
       </c>
@@ -5932,7 +5931,7 @@
         <v>19.851428571428571</v>
       </c>
     </row>
-    <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>92</v>
       </c>
@@ -5959,7 +5958,7 @@
         <v>20.586666666666666</v>
       </c>
     </row>
-    <row r="123" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>93</v>
       </c>
@@ -5986,7 +5985,7 @@
         <v>21.321904761904758</v>
       </c>
     </row>
-    <row r="124" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>94</v>
       </c>
@@ -6013,7 +6012,7 @@
         <v>22.057142857142857</v>
       </c>
     </row>
-    <row r="125" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>95</v>
       </c>
@@ -6040,7 +6039,7 @@
         <v>22.792380952380952</v>
       </c>
     </row>
-    <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>96</v>
       </c>
@@ -6067,7 +6066,7 @@
         <v>23.527619047619048</v>
       </c>
     </row>
-    <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>97</v>
       </c>
@@ -6094,7 +6093,7 @@
         <v>24.262857142857143</v>
       </c>
     </row>
-    <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>129</v>
       </c>
@@ -6121,7 +6120,7 @@
         <v>27.264324324324328</v>
       </c>
     </row>
-    <row r="129" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>130</v>
       </c>
@@ -6148,7 +6147,7 @@
         <v>28.066216216216215</v>
       </c>
     </row>
-    <row r="130" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>131</v>
       </c>
@@ -6175,7 +6174,7 @@
         <v>28.86810810810811</v>
       </c>
     </row>
-    <row r="131" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>132</v>
       </c>
@@ -6202,7 +6201,7 @@
         <v>29.670000000000005</v>
       </c>
     </row>
-    <row r="132" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>133</v>
       </c>
@@ -6229,7 +6228,7 @@
         <v>30.471891891891893</v>
       </c>
     </row>
-    <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>134</v>
       </c>
@@ -6256,7 +6255,7 @@
         <v>31.273783783783788</v>
       </c>
     </row>
-    <row r="134" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>135</v>
       </c>
@@ -6283,7 +6282,7 @@
         <v>32.075675675675676</v>
       </c>
     </row>
-    <row r="135" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>136</v>
       </c>
@@ -6310,7 +6309,7 @@
         <v>32.877567567567567</v>
       </c>
     </row>
-    <row r="136" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" s="7">
         <v>1960</v>
       </c>
@@ -6336,7 +6335,7 @@
         <v>94.88</v>
       </c>
     </row>
-    <row r="137" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>1775</v>
       </c>
@@ -6363,7 +6362,7 @@
         <v>32.075675675675676</v>
       </c>
     </row>
-    <row r="138" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>1776</v>
       </c>
@@ -6390,7 +6389,7 @@
         <v>32.877567567567567</v>
       </c>
     </row>
-    <row r="139" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>1777</v>
       </c>
@@ -6417,7 +6416,7 @@
         <v>33.679459459459466</v>
       </c>
     </row>
-    <row r="140" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>357</v>
       </c>
@@ -6444,7 +6443,7 @@
         <v>15.8424</v>
       </c>
     </row>
-    <row r="141" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>358</v>
       </c>
@@ -6471,7 +6470,7 @@
         <v>16.596799999999998</v>
       </c>
     </row>
-    <row r="142" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>261</v>
       </c>
@@ -6498,7 +6497,7 @@
         <v>17.351200000000002</v>
       </c>
     </row>
-    <row r="143" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>262</v>
       </c>
@@ -6525,7 +6524,7 @@
         <v>18.105599999999999</v>
       </c>
     </row>
-    <row r="144" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>263</v>
       </c>
@@ -6552,7 +6551,7 @@
         <v>18.86</v>
       </c>
     </row>
-    <row r="145" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>264</v>
       </c>
@@ -6579,7 +6578,7 @@
         <v>19.614399999999996</v>
       </c>
     </row>
-    <row r="146" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>265</v>
       </c>
@@ -6606,7 +6605,7 @@
         <v>20.3688</v>
       </c>
     </row>
-    <row r="147" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>266</v>
       </c>
@@ -6633,7 +6632,7 @@
         <v>21.123200000000001</v>
       </c>
     </row>
-    <row r="148" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>267</v>
       </c>
@@ -6660,7 +6659,7 @@
         <v>21.877599999999997</v>
       </c>
     </row>
-    <row r="149" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>268</v>
       </c>
@@ -6687,7 +6686,7 @@
         <v>22.632000000000001</v>
       </c>
     </row>
-    <row r="150" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>269</v>
       </c>
@@ -6714,7 +6713,7 @@
         <v>23.386399999999998</v>
       </c>
     </row>
-    <row r="151" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>270</v>
       </c>
@@ -6741,7 +6740,7 @@
         <v>23.7636</v>
       </c>
     </row>
-    <row r="152" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>271</v>
       </c>
@@ -6768,7 +6767,7 @@
         <v>24.140799999999999</v>
       </c>
     </row>
-    <row r="153" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>272</v>
       </c>
@@ -6795,7 +6794,7 @@
         <v>24.895199999999999</v>
       </c>
     </row>
-    <row r="154" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>1687</v>
       </c>
@@ -6822,7 +6821,7 @@
         <v>19.313684210526315</v>
       </c>
     </row>
-    <row r="155" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>290</v>
       </c>
@@ -6849,7 +6848,7 @@
         <v>27.361052631578943</v>
       </c>
     </row>
-    <row r="156" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>291</v>
       </c>
@@ -6876,7 +6875,7 @@
         <v>28.16578947368421</v>
       </c>
     </row>
-    <row r="157" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>292</v>
       </c>
@@ -6903,7 +6902,7 @@
         <v>28.970526315789471</v>
       </c>
     </row>
-    <row r="158" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>293</v>
       </c>
@@ -6930,7 +6929,7 @@
         <v>29.775263157894734</v>
       </c>
     </row>
-    <row r="159" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>294</v>
       </c>
@@ -6957,7 +6956,7 @@
         <v>30.58</v>
       </c>
     </row>
-    <row r="160" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>295</v>
       </c>
@@ -6984,7 +6983,7 @@
         <v>31.384736842105259</v>
       </c>
     </row>
-    <row r="161" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>296</v>
       </c>
@@ -7011,7 +7010,7 @@
         <v>32.189473684210526</v>
       </c>
     </row>
-    <row r="162" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" s="7">
         <v>1961</v>
       </c>
@@ -7037,7 +7036,7 @@
         <v>98.7</v>
       </c>
     </row>
-    <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>1778</v>
       </c>
@@ -7064,7 +7063,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="164" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>1779</v>
       </c>
@@ -7091,7 +7090,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="165" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>1780</v>
       </c>
@@ -7118,7 +7117,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="166" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>359</v>
       </c>
@@ -7145,7 +7144,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>273</v>
       </c>
@@ -7172,7 +7171,7 @@
         <v>16.59</v>
       </c>
     </row>
-    <row r="168" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>274</v>
       </c>
@@ -7199,7 +7198,7 @@
         <v>17.38</v>
       </c>
     </row>
-    <row r="169" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>275</v>
       </c>
@@ -7226,7 +7225,7 @@
         <v>18.170000000000002</v>
       </c>
     </row>
-    <row r="170" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>276</v>
       </c>
@@ -7253,7 +7252,7 @@
         <v>18.959999999999997</v>
       </c>
     </row>
-    <row r="171" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>277</v>
       </c>
@@ -7280,7 +7279,7 @@
         <v>19.75</v>
       </c>
     </row>
-    <row r="172" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>278</v>
       </c>
@@ -7307,7 +7306,7 @@
         <v>20.54</v>
       </c>
     </row>
-    <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>279</v>
       </c>
@@ -7334,7 +7333,7 @@
         <v>19.88</v>
       </c>
     </row>
-    <row r="174" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>280</v>
       </c>
@@ -7361,7 +7360,7 @@
         <v>22.12</v>
       </c>
     </row>
-    <row r="175" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>281</v>
       </c>
@@ -7388,7 +7387,7 @@
         <v>22.91</v>
       </c>
     </row>
-    <row r="176" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>282</v>
       </c>
@@ -7415,7 +7414,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="177" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>283</v>
       </c>
@@ -7442,7 +7441,7 @@
         <v>24.490000000000002</v>
       </c>
     </row>
-    <row r="178" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>284</v>
       </c>
@@ -7469,7 +7468,7 @@
         <v>25.28</v>
       </c>
     </row>
-    <row r="179" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>285</v>
       </c>
@@ -7496,7 +7495,7 @@
         <v>26.069999999999997</v>
       </c>
     </row>
-    <row r="180" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" s="4">
         <v>286</v>
       </c>
@@ -7523,7 +7522,7 @@
         <v>26.86</v>
       </c>
     </row>
-    <row r="181" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>287</v>
       </c>
@@ -7550,7 +7549,7 @@
         <v>27.65</v>
       </c>
     </row>
-    <row r="182" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>288</v>
       </c>
@@ -7577,7 +7576,7 @@
         <v>28.44</v>
       </c>
     </row>
-    <row r="183" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>289</v>
       </c>
@@ -7604,7 +7603,7 @@
         <v>29.229999999999997</v>
       </c>
     </row>
-    <row r="184" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>1636</v>
       </c>
@@ -7631,7 +7630,7 @@
         <v>16.068292682926828</v>
       </c>
     </row>
-    <row r="185" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>1637</v>
       </c>
@@ -7658,7 +7657,7 @@
         <v>18.478536585365852</v>
       </c>
     </row>
-    <row r="186" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>297</v>
       </c>
@@ -7685,7 +7684,7 @@
         <v>30.529756097560973</v>
       </c>
     </row>
-    <row r="187" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>298</v>
       </c>
@@ -7712,7 +7711,7 @@
         <v>31.333170731707312</v>
       </c>
     </row>
-    <row r="188" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>299</v>
       </c>
@@ -7739,7 +7738,7 @@
         <v>32.136585365853655</v>
       </c>
     </row>
-    <row r="189" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>300</v>
       </c>
@@ -7766,7 +7765,7 @@
         <v>32.94</v>
       </c>
     </row>
-    <row r="190" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>301</v>
       </c>
@@ -7793,7 +7792,7 @@
         <v>33.74341463414634</v>
       </c>
     </row>
-    <row r="191" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>302</v>
       </c>
@@ -7820,7 +7819,7 @@
         <v>34.546829268292683</v>
       </c>
     </row>
-    <row r="192" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>303</v>
       </c>
@@ -7847,7 +7846,7 @@
         <v>35.350243902439018</v>
       </c>
     </row>
-    <row r="193" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>304</v>
       </c>
@@ -7874,7 +7873,7 @@
         <v>36.153658536585361</v>
       </c>
     </row>
-    <row r="194" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" s="7">
         <v>1962</v>
       </c>
@@ -7900,7 +7899,7 @@
         <v>107.44</v>
       </c>
     </row>
-    <row r="195" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>1781</v>
       </c>
@@ -7927,7 +7926,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="196" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>1782</v>
       </c>
@@ -7971,7 +7970,7 @@
         <v>322</v>
       </c>
       <c r="F197">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G197" t="s">
@@ -7998,7 +7997,7 @@
         <v>322</v>
       </c>
       <c r="F198">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>110</v>
       </c>
       <c r="G198" t="s">
@@ -8025,7 +8024,7 @@
         <v>322</v>
       </c>
       <c r="F199">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>110</v>
       </c>
       <c r="G199" t="s">
@@ -8052,7 +8051,7 @@
         <v>322</v>
       </c>
       <c r="F200">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>90</v>
       </c>
       <c r="G200" t="s">
@@ -8079,7 +8078,7 @@
         <v>322</v>
       </c>
       <c r="F201">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>70</v>
       </c>
       <c r="G201" t="s">
@@ -8103,7 +8102,7 @@
         <v>322</v>
       </c>
       <c r="F202" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H202" s="2" t="e">
@@ -8127,7 +8126,7 @@
         <v>322</v>
       </c>
       <c r="F203">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>50</v>
       </c>
       <c r="G203" t="s">
@@ -8151,7 +8150,7 @@
         <v>322</v>
       </c>
       <c r="F204" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H204" s="2" t="e">
@@ -8175,7 +8174,7 @@
         <v>322</v>
       </c>
       <c r="F205">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>100</v>
       </c>
       <c r="G205" t="s">
@@ -8202,7 +8201,7 @@
         <v>322</v>
       </c>
       <c r="F206">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>90</v>
       </c>
       <c r="G206" t="s">
@@ -8229,7 +8228,7 @@
         <v>322</v>
       </c>
       <c r="F207">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>75</v>
       </c>
       <c r="G207" t="s">
@@ -8256,7 +8255,7 @@
         <v>322</v>
       </c>
       <c r="F208">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>60</v>
       </c>
       <c r="G208" t="s">
@@ -8280,7 +8279,7 @@
         <v>322</v>
       </c>
       <c r="F209" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H209" s="2" t="e">
@@ -8304,7 +8303,7 @@
         <v>322</v>
       </c>
       <c r="F210">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>40</v>
       </c>
       <c r="G210" t="s">
@@ -8328,7 +8327,7 @@
         <v>322</v>
       </c>
       <c r="F211" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H211" s="2">
@@ -8352,7 +8351,7 @@
         <v>322</v>
       </c>
       <c r="F212">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G212" t="s">
@@ -8379,7 +8378,7 @@
         <v>322</v>
       </c>
       <c r="F213">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G213" t="s">
@@ -8406,7 +8405,7 @@
         <v>322</v>
       </c>
       <c r="F214">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G214" t="s">
@@ -8433,7 +8432,7 @@
         <v>322</v>
       </c>
       <c r="F215">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G215" t="s">
@@ -8457,7 +8456,7 @@
         <v>322</v>
       </c>
       <c r="F216" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H216" s="2" t="e">
@@ -8481,7 +8480,7 @@
         <v>322</v>
       </c>
       <c r="F217">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G217" t="s">
@@ -8505,7 +8504,7 @@
         <v>322</v>
       </c>
       <c r="F218" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H218" s="2" t="e">
@@ -8529,7 +8528,7 @@
         <v>322</v>
       </c>
       <c r="F219">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G219" t="s">
@@ -8556,7 +8555,7 @@
         <v>322</v>
       </c>
       <c r="F220">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G220" t="s">
@@ -8583,7 +8582,7 @@
         <v>322</v>
       </c>
       <c r="F221">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G221" t="s">
@@ -8610,7 +8609,7 @@
         <v>322</v>
       </c>
       <c r="F222">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G222" t="s">
@@ -8634,7 +8633,7 @@
         <v>322</v>
       </c>
       <c r="F223" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H223" s="2" t="e">
@@ -8658,7 +8657,7 @@
         <v>322</v>
       </c>
       <c r="F224">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G224" t="s">
@@ -8682,7 +8681,7 @@
         <v>322</v>
       </c>
       <c r="F225" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H225" s="2">
@@ -8706,7 +8705,7 @@
         <v>322</v>
       </c>
       <c r="F226">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>110</v>
       </c>
       <c r="G226" t="s">
@@ -8733,7 +8732,7 @@
         <v>322</v>
       </c>
       <c r="F227">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>110</v>
       </c>
       <c r="G227" t="s">
@@ -8760,7 +8759,7 @@
         <v>322</v>
       </c>
       <c r="F228">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>90</v>
       </c>
       <c r="G228" t="s">
@@ -8787,7 +8786,7 @@
         <v>322</v>
       </c>
       <c r="F229">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>70</v>
       </c>
       <c r="G229" t="s">
@@ -8811,7 +8810,7 @@
         <v>322</v>
       </c>
       <c r="F230" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H230" s="2" t="e">
@@ -8835,7 +8834,7 @@
         <v>322</v>
       </c>
       <c r="F231">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>50</v>
       </c>
       <c r="G231" t="s">
@@ -8859,7 +8858,7 @@
         <v>322</v>
       </c>
       <c r="F232" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H232" s="2" t="e">
@@ -8883,7 +8882,7 @@
         <v>322</v>
       </c>
       <c r="F233">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>100</v>
       </c>
       <c r="G233" t="s">
@@ -8910,7 +8909,7 @@
         <v>322</v>
       </c>
       <c r="F234">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>90</v>
       </c>
       <c r="G234" t="s">
@@ -8937,7 +8936,7 @@
         <v>322</v>
       </c>
       <c r="F235">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>75</v>
       </c>
       <c r="G235" t="s">
@@ -8964,7 +8963,7 @@
         <v>322</v>
       </c>
       <c r="F236">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>60</v>
       </c>
       <c r="G236" t="s">
@@ -8988,7 +8987,7 @@
         <v>322</v>
       </c>
       <c r="F237" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H237" s="2" t="e">
@@ -9012,7 +9011,7 @@
         <v>322</v>
       </c>
       <c r="F238">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>40</v>
       </c>
       <c r="G238" t="s">
@@ -9036,7 +9035,7 @@
         <v>322</v>
       </c>
       <c r="F239" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H239" s="2">
@@ -9060,7 +9059,7 @@
         <v>322</v>
       </c>
       <c r="F240">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>110</v>
       </c>
       <c r="G240" t="s">
@@ -9087,7 +9086,7 @@
         <v>322</v>
       </c>
       <c r="F241">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>110</v>
       </c>
       <c r="G241" t="s">
@@ -9114,7 +9113,7 @@
         <v>322</v>
       </c>
       <c r="F242">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>80</v>
       </c>
       <c r="G242" t="s">
@@ -9141,7 +9140,7 @@
         <v>322</v>
       </c>
       <c r="F243">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>70</v>
       </c>
       <c r="G243" t="s">
@@ -9165,7 +9164,7 @@
         <v>322</v>
       </c>
       <c r="F244" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H244" s="2" t="e">
@@ -9189,7 +9188,7 @@
         <v>322</v>
       </c>
       <c r="F245">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>45</v>
       </c>
       <c r="G245" t="s">
@@ -9213,7 +9212,7 @@
         <v>322</v>
       </c>
       <c r="F246" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H246" s="2" t="e">
@@ -9237,7 +9236,7 @@
         <v>322</v>
       </c>
       <c r="F247">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>90</v>
       </c>
       <c r="G247" t="s">
@@ -9264,7 +9263,7 @@
         <v>322</v>
       </c>
       <c r="F248">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>80</v>
       </c>
       <c r="G248" t="s">
@@ -9291,7 +9290,7 @@
         <v>322</v>
       </c>
       <c r="F249">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>70</v>
       </c>
       <c r="G249" t="s">
@@ -9318,7 +9317,7 @@
         <v>322</v>
       </c>
       <c r="F250">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>60</v>
       </c>
       <c r="G250" t="s">
@@ -9342,7 +9341,7 @@
         <v>322</v>
       </c>
       <c r="F251" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H251" s="2" t="e">
@@ -9366,7 +9365,7 @@
         <v>322</v>
       </c>
       <c r="F252">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>35</v>
       </c>
       <c r="G252" t="s">
@@ -9390,7 +9389,7 @@
         <v>322</v>
       </c>
       <c r="F253" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H253" s="2">
@@ -9414,7 +9413,7 @@
         <v>322</v>
       </c>
       <c r="F254">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G254" t="s">
@@ -9441,7 +9440,7 @@
         <v>322</v>
       </c>
       <c r="F255">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G255" t="s">
@@ -9468,7 +9467,7 @@
         <v>322</v>
       </c>
       <c r="F256">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G256" t="s">
@@ -9495,7 +9494,7 @@
         <v>322</v>
       </c>
       <c r="F257">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G257" t="s">
@@ -9519,7 +9518,7 @@
         <v>322</v>
       </c>
       <c r="F258" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H258" s="2" t="e">
@@ -9543,7 +9542,7 @@
         <v>322</v>
       </c>
       <c r="F259">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G259" t="s">
@@ -9567,7 +9566,7 @@
         <v>322</v>
       </c>
       <c r="F260" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H260" s="2" t="e">
@@ -9591,7 +9590,7 @@
         <v>322</v>
       </c>
       <c r="F261">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G261" t="s">
@@ -9618,7 +9617,7 @@
         <v>322</v>
       </c>
       <c r="F262">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G262" t="s">
@@ -9645,7 +9644,7 @@
         <v>322</v>
       </c>
       <c r="F263">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G263" t="s">
@@ -9672,7 +9671,7 @@
         <v>322</v>
       </c>
       <c r="F264">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G264" t="s">
@@ -9696,7 +9695,7 @@
         <v>322</v>
       </c>
       <c r="F265" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H265" s="2" t="e">
@@ -9720,7 +9719,7 @@
         <v>322</v>
       </c>
       <c r="F266">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G266" t="s">
@@ -9747,7 +9746,7 @@
         <v>322</v>
       </c>
       <c r="F267">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G267" t="s">
@@ -9774,7 +9773,7 @@
         <v>322</v>
       </c>
       <c r="F268">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>110</v>
       </c>
       <c r="G268" t="s">
@@ -9801,7 +9800,7 @@
         <v>322</v>
       </c>
       <c r="F269">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>110</v>
       </c>
       <c r="G269" t="s">
@@ -9828,7 +9827,7 @@
         <v>322</v>
       </c>
       <c r="F270">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>80</v>
       </c>
       <c r="G270" t="s">
@@ -9855,7 +9854,7 @@
         <v>322</v>
       </c>
       <c r="F271">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>70</v>
       </c>
       <c r="G271" t="s">
@@ -9879,7 +9878,7 @@
         <v>322</v>
       </c>
       <c r="F272" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H272" s="2" t="e">
@@ -9903,7 +9902,7 @@
         <v>322</v>
       </c>
       <c r="F273">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>45</v>
       </c>
       <c r="G273" t="s">
@@ -9927,7 +9926,7 @@
         <v>322</v>
       </c>
       <c r="F274" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H274" s="2" t="e">
@@ -9951,7 +9950,7 @@
         <v>322</v>
       </c>
       <c r="F275">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>90</v>
       </c>
       <c r="G275" t="s">
@@ -9978,7 +9977,7 @@
         <v>322</v>
       </c>
       <c r="F276">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>80</v>
       </c>
       <c r="G276" t="s">
@@ -10005,7 +10004,7 @@
         <v>322</v>
       </c>
       <c r="F277">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>70</v>
       </c>
       <c r="G277" t="s">
@@ -10032,7 +10031,7 @@
         <v>322</v>
       </c>
       <c r="F278">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>60</v>
       </c>
       <c r="G278" t="s">
@@ -10056,7 +10055,7 @@
         <v>322</v>
       </c>
       <c r="F279" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H279" s="2" t="e">
@@ -10080,7 +10079,7 @@
         <v>322</v>
       </c>
       <c r="F280">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>35</v>
       </c>
       <c r="G280" t="s">
@@ -10104,7 +10103,7 @@
         <v>322</v>
       </c>
       <c r="F281" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H281" s="2" t="e">
@@ -10128,7 +10127,7 @@
         <v>322</v>
       </c>
       <c r="F282">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G282" t="s">
@@ -10155,7 +10154,7 @@
         <v>322</v>
       </c>
       <c r="F283">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G283" t="s">
@@ -10182,7 +10181,7 @@
         <v>322</v>
       </c>
       <c r="F284">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G284" t="s">
@@ -10209,7 +10208,7 @@
         <v>322</v>
       </c>
       <c r="F285">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G285" t="s">
@@ -10233,7 +10232,7 @@
         <v>322</v>
       </c>
       <c r="F286" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H286" s="2" t="e">
@@ -10257,7 +10256,7 @@
         <v>322</v>
       </c>
       <c r="F287">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G287" t="s">
@@ -10281,7 +10280,7 @@
         <v>322</v>
       </c>
       <c r="F288" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H288" s="2" t="e">
@@ -10305,7 +10304,7 @@
         <v>322</v>
       </c>
       <c r="F289">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G289" t="s">
@@ -10332,7 +10331,7 @@
         <v>322</v>
       </c>
       <c r="F290">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G290" t="s">
@@ -10359,7 +10358,7 @@
         <v>322</v>
       </c>
       <c r="F291">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G291" t="s">
@@ -10386,7 +10385,7 @@
         <v>322</v>
       </c>
       <c r="F292">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G292" t="s">
@@ -10410,7 +10409,7 @@
         <v>322</v>
       </c>
       <c r="F293" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H293" s="2" t="e">
@@ -10434,7 +10433,7 @@
         <v>322</v>
       </c>
       <c r="F294">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G294" t="s">
@@ -10458,7 +10457,7 @@
         <v>322</v>
       </c>
       <c r="F295" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H295" s="2">
@@ -10482,7 +10481,7 @@
         <v>322</v>
       </c>
       <c r="F296">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G296" t="s">
@@ -10509,7 +10508,7 @@
         <v>322</v>
       </c>
       <c r="F297">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G297" t="s">
@@ -10536,7 +10535,7 @@
         <v>322</v>
       </c>
       <c r="F298">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G298" t="s">
@@ -10563,7 +10562,7 @@
         <v>322</v>
       </c>
       <c r="F299">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G299" t="s">
@@ -10587,7 +10586,7 @@
         <v>322</v>
       </c>
       <c r="F300" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H300" s="2" t="e">
@@ -10611,7 +10610,7 @@
         <v>322</v>
       </c>
       <c r="F301">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G301" t="s">
@@ -10635,7 +10634,7 @@
         <v>322</v>
       </c>
       <c r="F302" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H302" s="2" t="e">
@@ -10659,7 +10658,7 @@
         <v>322</v>
       </c>
       <c r="F303">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G303" t="s">
@@ -10686,7 +10685,7 @@
         <v>322</v>
       </c>
       <c r="F304">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G304" t="s">
@@ -10713,7 +10712,7 @@
         <v>322</v>
       </c>
       <c r="F305">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G305" t="s">
@@ -10740,7 +10739,7 @@
         <v>322</v>
       </c>
       <c r="F306">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G306" t="s">
@@ -10764,7 +10763,7 @@
         <v>322</v>
       </c>
       <c r="F307" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H307" s="2" t="e">
@@ -10788,7 +10787,7 @@
         <v>322</v>
       </c>
       <c r="F308">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G308" t="s">
@@ -10812,7 +10811,7 @@
         <v>322</v>
       </c>
       <c r="F309" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H309">
@@ -10836,7 +10835,7 @@
         <v>322</v>
       </c>
       <c r="F310">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>110</v>
       </c>
       <c r="G310" t="s">
@@ -10863,7 +10862,7 @@
         <v>322</v>
       </c>
       <c r="F311">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>86</v>
       </c>
       <c r="G311" t="s">
@@ -10890,7 +10889,7 @@
         <v>322</v>
       </c>
       <c r="F312">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>70</v>
       </c>
       <c r="G312" t="s">
@@ -10917,7 +10916,7 @@
         <v>322</v>
       </c>
       <c r="F313">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>52</v>
       </c>
       <c r="G313" t="s">
@@ -10941,7 +10940,7 @@
         <v>322</v>
       </c>
       <c r="F314" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H314" s="2" t="e">
@@ -10965,7 +10964,7 @@
         <v>322</v>
       </c>
       <c r="F315">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>42</v>
       </c>
       <c r="G315" t="s">
@@ -10989,7 +10988,7 @@
         <v>322</v>
       </c>
       <c r="F316" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H316" s="2" t="e">
@@ -11013,7 +11012,7 @@
         <v>322</v>
       </c>
       <c r="F317">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>86</v>
       </c>
       <c r="G317" t="s">
@@ -11040,7 +11039,7 @@
         <v>322</v>
       </c>
       <c r="F318">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>70</v>
       </c>
       <c r="G318" t="s">
@@ -11067,7 +11066,7 @@
         <v>322</v>
       </c>
       <c r="F319">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>60</v>
       </c>
       <c r="G319" t="s">
@@ -11094,7 +11093,7 @@
         <v>322</v>
       </c>
       <c r="F320">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>44</v>
       </c>
       <c r="G320" t="s">
@@ -11118,7 +11117,7 @@
         <v>322</v>
       </c>
       <c r="F321" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H321" s="2" t="e">
@@ -11142,7 +11141,7 @@
         <v>322</v>
       </c>
       <c r="F322">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>28</v>
       </c>
       <c r="G322" t="s">
@@ -11166,7 +11165,7 @@
         <v>322</v>
       </c>
       <c r="F323" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H323" s="2">
@@ -11190,7 +11189,7 @@
         <v>322</v>
       </c>
       <c r="F324">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>100</v>
       </c>
       <c r="G324" t="s">
@@ -11217,7 +11216,7 @@
         <v>322</v>
       </c>
       <c r="F325">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G325" t="s">
@@ -11244,7 +11243,7 @@
         <v>322</v>
       </c>
       <c r="F326">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>66</v>
       </c>
       <c r="G326" t="s">
@@ -11271,7 +11270,7 @@
         <v>322</v>
       </c>
       <c r="F327">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>48</v>
       </c>
       <c r="G327" t="s">
@@ -11295,7 +11294,7 @@
         <v>322</v>
       </c>
       <c r="F328" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H328" s="2" t="e">
@@ -11319,7 +11318,7 @@
         <v>322</v>
       </c>
       <c r="F329">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>32</v>
       </c>
       <c r="G329" t="s">
@@ -11343,7 +11342,7 @@
         <v>322</v>
       </c>
       <c r="F330" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H330" s="2" t="e">
@@ -11367,7 +11366,7 @@
         <v>322</v>
       </c>
       <c r="F331">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G331" t="s">
@@ -11394,7 +11393,7 @@
         <v>322</v>
       </c>
       <c r="F332">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G332" t="s">
@@ -11421,7 +11420,7 @@
         <v>322</v>
       </c>
       <c r="F333">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G333" t="s">
@@ -11448,7 +11447,7 @@
         <v>322</v>
       </c>
       <c r="F334">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G334" t="s">
@@ -11472,7 +11471,7 @@
         <v>322</v>
       </c>
       <c r="F335" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H335" s="2" t="e">
@@ -11496,7 +11495,7 @@
         <v>322</v>
       </c>
       <c r="F336">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G336" t="s">
@@ -11520,7 +11519,7 @@
         <v>322</v>
       </c>
       <c r="F337" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H337" s="2">
@@ -11544,7 +11543,7 @@
         <v>322</v>
       </c>
       <c r="F338">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G338" t="s">
@@ -11571,7 +11570,7 @@
         <v>322</v>
       </c>
       <c r="F339">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G339" t="s">
@@ -11598,7 +11597,7 @@
         <v>322</v>
       </c>
       <c r="F340">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G340" t="s">
@@ -11625,7 +11624,7 @@
         <v>322</v>
       </c>
       <c r="F341">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G341" t="s">
@@ -11649,7 +11648,7 @@
         <v>322</v>
       </c>
       <c r="F342" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H342" s="2" t="e">
@@ -11673,7 +11672,7 @@
         <v>322</v>
       </c>
       <c r="F343">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G343" t="s">
@@ -11697,7 +11696,7 @@
         <v>322</v>
       </c>
       <c r="F344" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H344" s="2" t="e">
@@ -11721,7 +11720,7 @@
         <v>322</v>
       </c>
       <c r="F345">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G345" t="s">
@@ -11748,7 +11747,7 @@
         <v>322</v>
       </c>
       <c r="F346">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G346" t="s">
@@ -11775,7 +11774,7 @@
         <v>322</v>
       </c>
       <c r="F347">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G347" t="s">
@@ -11802,7 +11801,7 @@
         <v>322</v>
       </c>
       <c r="F348">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G348" t="s">
@@ -11826,7 +11825,7 @@
         <v>322</v>
       </c>
       <c r="F349" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H349" s="2" t="e">
@@ -11850,7 +11849,7 @@
         <v>322</v>
       </c>
       <c r="F350">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G350" t="s">
@@ -11874,7 +11873,7 @@
         <v>322</v>
       </c>
       <c r="F351" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H351" s="2">
@@ -11898,7 +11897,7 @@
         <v>322</v>
       </c>
       <c r="F352">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G352" t="s">
@@ -11925,7 +11924,7 @@
         <v>322</v>
       </c>
       <c r="F353">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G353" t="s">
@@ -11952,7 +11951,7 @@
         <v>322</v>
       </c>
       <c r="F354">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G354" t="s">
@@ -11979,7 +11978,7 @@
         <v>322</v>
       </c>
       <c r="F355">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G355" t="s">
@@ -12003,7 +12002,7 @@
         <v>322</v>
       </c>
       <c r="F356" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H356" s="2" t="e">
@@ -12027,7 +12026,7 @@
         <v>322</v>
       </c>
       <c r="F357">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G357" t="s">
@@ -12051,7 +12050,7 @@
         <v>322</v>
       </c>
       <c r="F358" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H358" s="2" t="e">
@@ -12075,7 +12074,7 @@
         <v>322</v>
       </c>
       <c r="F359">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G359" t="s">
@@ -12102,7 +12101,7 @@
         <v>322</v>
       </c>
       <c r="F360">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G360" t="s">
@@ -12129,7 +12128,7 @@
         <v>322</v>
       </c>
       <c r="F361">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G361" t="s">
@@ -12156,7 +12155,7 @@
         <v>322</v>
       </c>
       <c r="F362">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G362" t="s">
@@ -12180,7 +12179,7 @@
         <v>322</v>
       </c>
       <c r="F363" t="e">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>#N/A</v>
       </c>
       <c r="H363" s="2" t="e">
@@ -12204,7 +12203,7 @@
         <v>322</v>
       </c>
       <c r="F364">
-        <f>VLOOKUP(Tabela14[[#This Row],[ID_COD]],Tabela2[],6,0)</f>
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
         <v>0</v>
       </c>
       <c r="G364" t="s">
@@ -12214,7 +12213,7 @@
         <v>17.34</v>
       </c>
     </row>
-    <row r="365" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A365">
         <v>4</v>
       </c>
@@ -12241,7 +12240,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="366" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A366">
         <v>731</v>
       </c>
@@ -12268,7 +12267,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="367" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A367">
         <v>730</v>
       </c>
@@ -12295,7 +12294,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="368" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A368">
         <v>495</v>
       </c>
@@ -12319,7 +12318,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="369" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A369">
         <v>2019</v>
       </c>
@@ -12346,7 +12345,7 @@
         <v>22.79</v>
       </c>
     </row>
-    <row r="370" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A370">
         <v>1819</v>
       </c>
@@ -12373,7 +12372,7 @@
         <v>16.87</v>
       </c>
     </row>
-    <row r="371" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A371">
         <v>2011</v>
       </c>
@@ -12400,7 +12399,7 @@
         <v>58.6</v>
       </c>
     </row>
-    <row r="372" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A372">
         <v>2010</v>
       </c>
@@ -12427,7 +12426,7 @@
         <v>25.71</v>
       </c>
     </row>
-    <row r="373" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A373">
         <v>1822</v>
       </c>
@@ -12454,7 +12453,7 @@
         <v>24.51</v>
       </c>
     </row>
-    <row r="374" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A374">
         <v>1797</v>
       </c>
@@ -12494,8 +12493,9 @@
       <c r="E375" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="F375" t="s">
-        <v>4</v>
+      <c r="F375">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>0</v>
       </c>
       <c r="G375" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
@@ -12521,8 +12521,9 @@
       <c r="E376" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="F376" t="s">
-        <v>4</v>
+      <c r="F376">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>110</v>
       </c>
       <c r="G376" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
@@ -12548,8 +12549,9 @@
       <c r="E377" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="F377" t="s">
-        <v>4</v>
+      <c r="F377">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>110</v>
       </c>
       <c r="G377" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
@@ -12575,8 +12577,9 @@
       <c r="E378" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="F378" t="s">
-        <v>4</v>
+      <c r="F378">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>90</v>
       </c>
       <c r="G378" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
@@ -12602,8 +12605,9 @@
       <c r="E379" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="F379" t="s">
-        <v>4</v>
+      <c r="F379">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>70</v>
       </c>
       <c r="G379" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
@@ -12629,8 +12633,9 @@
       <c r="E380" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="F380" t="s">
-        <v>4</v>
+      <c r="F380">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>50</v>
       </c>
       <c r="G380" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
@@ -12656,8 +12661,9 @@
       <c r="E381" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="F381" t="s">
-        <v>4</v>
+      <c r="F381">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>0</v>
       </c>
       <c r="G381" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
@@ -12683,8 +12689,9 @@
       <c r="E382" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="F382" t="s">
-        <v>4</v>
+      <c r="F382">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>100</v>
       </c>
       <c r="G382" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
@@ -12710,8 +12717,9 @@
       <c r="E383" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="F383" t="s">
-        <v>4</v>
+      <c r="F383">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>90</v>
       </c>
       <c r="G383" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
@@ -12737,8 +12745,9 @@
       <c r="E384" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="F384" t="s">
-        <v>4</v>
+      <c r="F384">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>75</v>
       </c>
       <c r="G384" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
@@ -12764,8 +12773,9 @@
       <c r="E385" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="F385" t="s">
-        <v>4</v>
+      <c r="F385">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>60</v>
       </c>
       <c r="G385" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
@@ -12791,8 +12801,9 @@
       <c r="E386" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="F386" t="s">
-        <v>4</v>
+      <c r="F386">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>40</v>
       </c>
       <c r="G386" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
@@ -12818,8 +12829,9 @@
       <c r="E387" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="F387" t="s">
-        <v>4</v>
+      <c r="F387">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>0</v>
       </c>
       <c r="G387" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
@@ -12845,8 +12857,9 @@
       <c r="E388" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="F388" t="s">
-        <v>4</v>
+      <c r="F388">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>0</v>
       </c>
       <c r="G388" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
@@ -12872,8 +12885,9 @@
       <c r="E389" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="F389" t="s">
-        <v>4</v>
+      <c r="F389">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>0</v>
       </c>
       <c r="G389" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
@@ -12899,8 +12913,9 @@
       <c r="E390" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="F390" t="s">
-        <v>4</v>
+      <c r="F390">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>0</v>
       </c>
       <c r="G390" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
@@ -12926,8 +12941,9 @@
       <c r="E391" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="F391" t="s">
-        <v>4</v>
+      <c r="F391">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>0</v>
       </c>
       <c r="G391" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
@@ -12953,8 +12969,9 @@
       <c r="E392" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="F392" t="s">
-        <v>4</v>
+      <c r="F392">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>0</v>
       </c>
       <c r="G392" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
@@ -12980,8 +12997,9 @@
       <c r="E393" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="F393" t="s">
-        <v>4</v>
+      <c r="F393">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>0</v>
       </c>
       <c r="G393" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
@@ -13007,8 +13025,9 @@
       <c r="E394" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="F394" t="s">
-        <v>4</v>
+      <c r="F394">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>0</v>
       </c>
       <c r="G394" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
@@ -13034,8 +13053,9 @@
       <c r="E395" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="F395" t="s">
-        <v>4</v>
+      <c r="F395">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>0</v>
       </c>
       <c r="G395" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
@@ -13061,14 +13081,15 @@
       <c r="E396" s="32" t="s">
         <v>400</v>
       </c>
-      <c r="F396" s="33" t="s">
-        <v>4</v>
+      <c r="F396">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>0</v>
       </c>
       <c r="G396" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
         <v>ATADURA DE CREPE - HOSPITALAR 30CM x 1,80M</v>
       </c>
-      <c r="H396" s="34">
+      <c r="H396" s="33">
         <v>15.444000000000001</v>
       </c>
     </row>
@@ -13088,14 +13109,15 @@
       <c r="E397" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="F397" t="s">
-        <v>417</v>
+      <c r="F397">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>0</v>
       </c>
       <c r="G397" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
         <v>ATADURA DE CREPE - FARMA 08CM x 1,20M</v>
       </c>
-      <c r="H397" s="35">
+      <c r="H397" s="34">
         <v>4.6115999999999993</v>
       </c>
     </row>
@@ -13115,14 +13137,15 @@
       <c r="E398" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="F398" t="s">
-        <v>417</v>
+      <c r="F398">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>110</v>
       </c>
       <c r="G398" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
         <v>ATADURA DE CREPE - FARMA 10CM x 1,20M</v>
       </c>
-      <c r="H398" s="35">
+      <c r="H398" s="34">
         <v>5.0111999999999997</v>
       </c>
     </row>
@@ -13142,14 +13165,15 @@
       <c r="E399" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="F399" t="s">
-        <v>417</v>
+      <c r="F399">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>110</v>
       </c>
       <c r="G399" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
         <v>ATADURA DE CREPE - FARMA 12CM x 1,20M</v>
       </c>
-      <c r="H399" s="36">
+      <c r="H399" s="35">
         <v>6.1992000000000003</v>
       </c>
     </row>
@@ -13169,14 +13193,15 @@
       <c r="E400" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="F400" t="s">
-        <v>417</v>
+      <c r="F400">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>80</v>
       </c>
       <c r="G400" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
         <v>ATADURA DE CREPE - FARMA 15CM x 1,20M</v>
       </c>
-      <c r="H400" s="36">
+      <c r="H400" s="35">
         <v>7.0956000000000001</v>
       </c>
     </row>
@@ -13196,14 +13221,15 @@
       <c r="E401" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="F401" t="s">
-        <v>417</v>
+      <c r="F401">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>70</v>
       </c>
       <c r="G401" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
         <v>ATADURA DE CREPE - FARMA 20CM x 1,20M</v>
       </c>
-      <c r="H401" s="36">
+      <c r="H401" s="35">
         <v>9.1259999999999994</v>
       </c>
     </row>
@@ -13223,14 +13249,15 @@
       <c r="E402" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="F402" t="s">
-        <v>417</v>
+      <c r="F402">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>45</v>
       </c>
       <c r="G402" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
         <v>ATADURA DE CREPE - FARMA 30CM x 1,20M</v>
       </c>
-      <c r="H402" s="36">
+      <c r="H402" s="35">
         <v>13.586399999999999</v>
       </c>
     </row>
@@ -13250,14 +13277,15 @@
       <c r="E403" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="F403" t="s">
-        <v>417</v>
+      <c r="F403" t="e">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>#N/A</v>
       </c>
       <c r="G403" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
         <v>ATADURA DE CREPE - FARMA 08CM x 1,80M</v>
       </c>
-      <c r="H403" s="36">
+      <c r="H403" s="35">
         <v>6.3720000000000008</v>
       </c>
     </row>
@@ -13277,14 +13305,15 @@
       <c r="E404" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="F404" t="s">
-        <v>417</v>
+      <c r="F404">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>90</v>
       </c>
       <c r="G404" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
         <v>ATADURA DE CREPE - FARMA 10CM x 1,80M</v>
       </c>
-      <c r="H404" s="36">
+      <c r="H404" s="35">
         <v>6.9228000000000005</v>
       </c>
     </row>
@@ -13304,14 +13333,15 @@
       <c r="E405" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="F405" t="s">
-        <v>417</v>
+      <c r="F405">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>80</v>
       </c>
       <c r="G405" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
         <v>ATADURA DE CREPE - FARMA 12CM x 1,80M</v>
       </c>
-      <c r="H405" s="36">
+      <c r="H405" s="35">
         <v>8.5535999999999994</v>
       </c>
     </row>
@@ -13331,14 +13361,15 @@
       <c r="E406" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="F406" t="s">
-        <v>417</v>
+      <c r="F406">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>70</v>
       </c>
       <c r="G406" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
         <v>ATADURA DE CREPE - FARMA 15CM x 1,80M</v>
       </c>
-      <c r="H406" s="36">
+      <c r="H406" s="35">
         <v>10.119599999999998</v>
       </c>
     </row>
@@ -13358,14 +13389,15 @@
       <c r="E407" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="F407" t="s">
-        <v>417</v>
+      <c r="F407">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>60</v>
       </c>
       <c r="G407" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
         <v>ATADURA DE CREPE - FARMA 20CM x 1,80M</v>
       </c>
-      <c r="H407" s="36">
+      <c r="H407" s="35">
         <v>12.9924</v>
       </c>
     </row>
@@ -13385,14 +13417,15 @@
       <c r="E408" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="F408" t="s">
-        <v>417</v>
+      <c r="F408">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>35</v>
       </c>
       <c r="G408" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
         <v>ATADURA DE CREPE - FARMA 30CM x 1,80M</v>
       </c>
-      <c r="H408" s="37">
+      <c r="H408" s="36">
         <v>18.7272</v>
       </c>
     </row>
@@ -13412,14 +13445,15 @@
       <c r="E409" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="F409" t="s">
-        <v>417</v>
+      <c r="F409" t="e">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>#N/A</v>
       </c>
       <c r="G409" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
         <v>ATADURA DE CREPE - HOSPITALAR 10CM x 1,20M</v>
       </c>
-      <c r="H409" s="35">
+      <c r="H409" s="34">
         <v>4.8600000000000003</v>
       </c>
     </row>
@@ -13439,14 +13473,15 @@
       <c r="E410" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="F410" t="s">
-        <v>417</v>
+      <c r="F410" t="e">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>#N/A</v>
       </c>
       <c r="G410" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
         <v>ATADURA DE CREPE - HOSPITALAR 12CM x 1,20M</v>
       </c>
-      <c r="H410" s="36">
+      <c r="H410" s="35">
         <v>6.0156000000000001</v>
       </c>
     </row>
@@ -13466,14 +13501,15 @@
       <c r="E411" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="F411" t="s">
-        <v>417</v>
+      <c r="F411" t="e">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>#N/A</v>
       </c>
       <c r="G411" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
         <v>ATADURA DE CREPE - HOSPITALAR 15CM x 1,20M</v>
       </c>
-      <c r="H411" s="36">
+      <c r="H411" s="35">
         <v>6.8903999999999996</v>
       </c>
     </row>
@@ -13493,14 +13529,15 @@
       <c r="E412" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="F412" t="s">
-        <v>417</v>
+      <c r="F412" t="e">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>#N/A</v>
       </c>
       <c r="G412" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
         <v>ATADURA DE CREPE - HOSPITALAR 20CM x 1,20M</v>
       </c>
-      <c r="H412" s="36">
+      <c r="H412" s="35">
         <v>8.8452000000000002</v>
       </c>
     </row>
@@ -13520,14 +13557,15 @@
       <c r="E413" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="F413" t="s">
-        <v>417</v>
+      <c r="F413" t="e">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>#N/A</v>
       </c>
       <c r="G413" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
         <v>ATADURA DE CREPE - HOSPITALAR 30CM x 1,20M</v>
       </c>
-      <c r="H413" s="36">
+      <c r="H413" s="35">
         <v>13.186800000000002</v>
       </c>
     </row>
@@ -13547,14 +13585,15 @@
       <c r="E414" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="F414" t="s">
-        <v>417</v>
+      <c r="F414" t="e">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>#N/A</v>
       </c>
       <c r="G414" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
         <v>ATADURA DE CREPE - HOSPITALAR 10CM x 1,80M</v>
       </c>
-      <c r="H414" s="36">
+      <c r="H414" s="35">
         <v>6.7284000000000006</v>
       </c>
     </row>
@@ -13574,14 +13613,15 @@
       <c r="E415" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="F415" t="s">
-        <v>417</v>
+      <c r="F415" t="e">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>#N/A</v>
       </c>
       <c r="G415" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
         <v>ATADURA DE CREPE - HOSPITALAR 12CM x 1,80M</v>
       </c>
-      <c r="H415" s="36">
+      <c r="H415" s="35">
         <v>8.2835999999999999</v>
       </c>
     </row>
@@ -13601,14 +13641,15 @@
       <c r="E416" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="F416" t="s">
-        <v>417</v>
+      <c r="F416" t="e">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>#N/A</v>
       </c>
       <c r="G416" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
         <v>ATADURA DE CREPE - HOSPITALAR 15CM x 1,80M</v>
       </c>
-      <c r="H416" s="36">
+      <c r="H416" s="35">
         <v>9.8064</v>
       </c>
     </row>
@@ -13628,14 +13669,15 @@
       <c r="E417" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="F417" t="s">
-        <v>417</v>
+      <c r="F417" t="e">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>#N/A</v>
       </c>
       <c r="G417" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
         <v>ATADURA DE CREPE - HOSPITALAR 20CM x 1,80M</v>
       </c>
-      <c r="H417" s="36">
+      <c r="H417" s="35">
         <v>12.6036</v>
       </c>
     </row>
@@ -13655,14 +13697,15 @@
       <c r="E418" s="32" t="s">
         <v>432</v>
       </c>
-      <c r="F418" s="33" t="s">
-        <v>417</v>
+      <c r="F418" t="e">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>#N/A</v>
       </c>
       <c r="G418" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
         <v>ATADURA DE CREPE - HOSPITALAR 30CM x 1,80M</v>
       </c>
-      <c r="H418" s="37">
+      <c r="H418" s="36">
         <v>18.176399999999997</v>
       </c>
     </row>
@@ -13682,8 +13725,9 @@
       <c r="E419" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="F419" t="s">
-        <v>411</v>
+      <c r="F419" t="e">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>#N/A</v>
       </c>
       <c r="G419" t="str">
         <f>CONCATENATE(Tabela14[[#This Row],[Grupo]]," ",Tabela14[[#This Row],[Descrição]])</f>
@@ -13691,6 +13735,1067 @@
       </c>
       <c r="H419" s="2">
         <v>6.37</v>
+      </c>
+    </row>
+    <row r="420" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A420" s="7">
+        <v>37</v>
+      </c>
+      <c r="B420" t="s">
+        <v>520</v>
+      </c>
+      <c r="C420" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D420" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="E420">
+        <v>130</v>
+      </c>
+      <c r="F420">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="G420" t="s">
+        <v>520</v>
+      </c>
+      <c r="H420" s="2">
+        <v>9.24</v>
+      </c>
+    </row>
+    <row r="421" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A421" s="7">
+        <v>62</v>
+      </c>
+      <c r="B421" t="s">
+        <v>521</v>
+      </c>
+      <c r="C421" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D421" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="E421">
+        <v>240</v>
+      </c>
+      <c r="F421">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="G421" t="s">
+        <v>521</v>
+      </c>
+      <c r="H421" s="2">
+        <v>16.68</v>
+      </c>
+    </row>
+    <row r="422" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A422" s="7">
+        <v>1924</v>
+      </c>
+      <c r="B422" t="s">
+        <v>207</v>
+      </c>
+      <c r="C422" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D422" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E422" t="s">
+        <v>522</v>
+      </c>
+      <c r="F422">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="G422" t="s">
+        <v>207</v>
+      </c>
+      <c r="H422" s="2">
+        <v>16.61</v>
+      </c>
+    </row>
+    <row r="423" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A423" s="7">
+        <v>1950</v>
+      </c>
+      <c r="B423" t="s">
+        <v>207</v>
+      </c>
+      <c r="C423" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D423" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="E423" t="s">
+        <v>523</v>
+      </c>
+      <c r="F423">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="G423" t="s">
+        <v>207</v>
+      </c>
+      <c r="H423" s="2">
+        <v>12.53</v>
+      </c>
+    </row>
+    <row r="424" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A424" s="7">
+        <v>112</v>
+      </c>
+      <c r="B424" t="s">
+        <v>228</v>
+      </c>
+      <c r="C424" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D424" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="E424">
+        <v>210</v>
+      </c>
+      <c r="F424">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="G424" t="s">
+        <v>228</v>
+      </c>
+      <c r="H424" s="2">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="425" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A425" s="7">
+        <v>2073</v>
+      </c>
+      <c r="B425" t="s">
+        <v>176</v>
+      </c>
+      <c r="C425" s="7" t="s">
+        <v>530</v>
+      </c>
+      <c r="D425" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="E425">
+        <v>8</v>
+      </c>
+      <c r="F425">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="G425" t="s">
+        <v>176</v>
+      </c>
+      <c r="H425" s="2">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="426" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A426" s="7">
+        <v>2070</v>
+      </c>
+      <c r="B426" t="s">
+        <v>187</v>
+      </c>
+      <c r="C426" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D426" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E426">
+        <v>210</v>
+      </c>
+      <c r="F426">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="G426" t="s">
+        <v>187</v>
+      </c>
+      <c r="H426" s="2">
+        <v>15.98</v>
+      </c>
+    </row>
+    <row r="427" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A427" s="7">
+        <v>2090</v>
+      </c>
+      <c r="B427" t="s">
+        <v>265</v>
+      </c>
+      <c r="C427" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D427" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="E427">
+        <v>240</v>
+      </c>
+      <c r="F427">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="G427" t="s">
+        <v>265</v>
+      </c>
+      <c r="H427" s="2">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="428" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A428" s="7">
+        <v>2091</v>
+      </c>
+      <c r="B428" t="s">
+        <v>525</v>
+      </c>
+      <c r="C428" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D428" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="E428">
+        <v>270</v>
+      </c>
+      <c r="F428">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="G428" t="s">
+        <v>525</v>
+      </c>
+      <c r="H428" s="2">
+        <v>17.38</v>
+      </c>
+    </row>
+    <row r="429" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A429" s="7">
+        <v>1959</v>
+      </c>
+      <c r="B429" t="s">
+        <v>304</v>
+      </c>
+      <c r="C429" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D429" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="E429">
+        <v>435</v>
+      </c>
+      <c r="F429">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="G429" t="s">
+        <v>304</v>
+      </c>
+      <c r="H429" s="2">
+        <v>30.77</v>
+      </c>
+    </row>
+    <row r="430" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A430" s="7">
+        <v>2147</v>
+      </c>
+      <c r="B430" t="s">
+        <v>207</v>
+      </c>
+      <c r="C430" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D430" s="7" t="s">
+        <v>534</v>
+      </c>
+      <c r="E430">
+        <v>200</v>
+      </c>
+      <c r="F430">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="G430" t="s">
+        <v>207</v>
+      </c>
+      <c r="H430" s="2"/>
+    </row>
+    <row r="431" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A431" s="7">
+        <v>2115</v>
+      </c>
+      <c r="B431" t="s">
+        <v>228</v>
+      </c>
+      <c r="C431" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D431" s="7" t="s">
+        <v>534</v>
+      </c>
+      <c r="E431">
+        <v>270</v>
+      </c>
+      <c r="F431">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="G431" t="s">
+        <v>228</v>
+      </c>
+      <c r="H431" s="2">
+        <v>16.86</v>
+      </c>
+    </row>
+    <row r="432" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A432" s="7">
+        <v>2127</v>
+      </c>
+      <c r="B432" t="s">
+        <v>265</v>
+      </c>
+      <c r="C432" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D432" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E432">
+        <v>100</v>
+      </c>
+      <c r="F432">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="G432" t="s">
+        <v>265</v>
+      </c>
+      <c r="H432" s="2">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="433" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A433" s="7">
+        <v>2128</v>
+      </c>
+      <c r="B433" t="s">
+        <v>301</v>
+      </c>
+      <c r="C433" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D433" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E433">
+        <v>130</v>
+      </c>
+      <c r="F433">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="G433" t="s">
+        <v>301</v>
+      </c>
+      <c r="H433" s="2">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="434" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A434" s="7">
+        <v>2129</v>
+      </c>
+      <c r="B434" t="s">
+        <v>526</v>
+      </c>
+      <c r="C434" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D434" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E434">
+        <v>150</v>
+      </c>
+      <c r="F434">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="G434" t="s">
+        <v>526</v>
+      </c>
+      <c r="H434" s="2">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="435" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A435" s="7">
+        <v>2183</v>
+      </c>
+      <c r="B435" t="s">
+        <v>528</v>
+      </c>
+      <c r="C435" s="7" t="s">
+        <v>531</v>
+      </c>
+      <c r="D435" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="E435">
+        <v>0</v>
+      </c>
+      <c r="F435">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="G435" t="s">
+        <v>528</v>
+      </c>
+      <c r="H435" s="2">
+        <v>18.86</v>
+      </c>
+    </row>
+    <row r="436" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A436" s="7">
+        <v>2184</v>
+      </c>
+      <c r="B436" t="s">
+        <v>529</v>
+      </c>
+      <c r="C436" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D436" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="E436">
+        <v>210</v>
+      </c>
+      <c r="F436">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="G436" t="s">
+        <v>529</v>
+      </c>
+      <c r="H436" s="2">
+        <v>13.31</v>
+      </c>
+    </row>
+    <row r="437" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A437" s="7">
+        <v>1957</v>
+      </c>
+      <c r="B437" t="s">
+        <v>267</v>
+      </c>
+      <c r="C437" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="D437" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="E437">
+        <v>400</v>
+      </c>
+      <c r="F437">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="G437" t="s">
+        <v>267</v>
+      </c>
+      <c r="H437" s="2">
+        <v>27.88</v>
+      </c>
+    </row>
+    <row r="438" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A438" s="7">
+        <v>2185</v>
+      </c>
+      <c r="B438" t="s">
+        <v>280</v>
+      </c>
+      <c r="C438" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="D438" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="E438">
+        <v>240</v>
+      </c>
+      <c r="F438">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="G438" t="s">
+        <v>280</v>
+      </c>
+      <c r="H438" s="2">
+        <v>17.23</v>
+      </c>
+    </row>
+    <row r="439" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A439" s="7">
+        <v>2186</v>
+      </c>
+      <c r="B439" t="s">
+        <v>301</v>
+      </c>
+      <c r="C439" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="D439" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="E439">
+        <v>270</v>
+      </c>
+      <c r="F439">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="G439" t="s">
+        <v>301</v>
+      </c>
+      <c r="H439" s="2">
+        <v>20.54</v>
+      </c>
+    </row>
+    <row r="440" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A440" s="7">
+        <v>116</v>
+      </c>
+      <c r="B440" t="s">
+        <v>228</v>
+      </c>
+      <c r="C440" s="7" t="s">
+        <v>533</v>
+      </c>
+      <c r="D440" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E440">
+        <v>250</v>
+      </c>
+      <c r="F440">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="G440" t="s">
+        <v>228</v>
+      </c>
+      <c r="H440" s="2">
+        <v>15.41</v>
+      </c>
+    </row>
+    <row r="441" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A441" s="7">
+        <v>2063</v>
+      </c>
+      <c r="B441" t="s">
+        <v>304</v>
+      </c>
+      <c r="C441" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="D441" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="E441">
+        <v>450</v>
+      </c>
+      <c r="F441">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="G441" t="s">
+        <v>304</v>
+      </c>
+      <c r="H441" s="2">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="442" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A442" s="7">
+        <v>2204</v>
+      </c>
+      <c r="B442" t="s">
+        <v>207</v>
+      </c>
+      <c r="C442" s="7" t="s">
+        <v>533</v>
+      </c>
+      <c r="D442" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="E442">
+        <v>800</v>
+      </c>
+      <c r="F442">
+        <f>_xlfn.XLOOKUP(Tabela14[[#This Row],[ID_COD]],Estoque!A:A,Estoque!F:F)</f>
+        <v>0</v>
+      </c>
+      <c r="G442" t="s">
+        <v>207</v>
+      </c>
+      <c r="H442" s="2">
+        <v>51.61</v>
+      </c>
+    </row>
+    <row r="443" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A443" s="7">
+        <v>1600</v>
+      </c>
+      <c r="B443" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="C443" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D443" t="s">
+        <v>444</v>
+      </c>
+      <c r="G443" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="H443" s="2"/>
+    </row>
+    <row r="444" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A444" s="7">
+        <v>1602</v>
+      </c>
+      <c r="B444" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="C444" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D444" t="s">
+        <v>444</v>
+      </c>
+      <c r="G444" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="H444" s="2"/>
+    </row>
+    <row r="445" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A445" s="7">
+        <v>1605</v>
+      </c>
+      <c r="B445" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="C445" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D445" t="s">
+        <v>445</v>
+      </c>
+      <c r="G445" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="H445" s="2"/>
+    </row>
+    <row r="446" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A446" s="7">
+        <v>1608</v>
+      </c>
+      <c r="B446" s="7" t="s">
+        <v>494</v>
+      </c>
+      <c r="C446" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D446" t="s">
+        <v>445</v>
+      </c>
+      <c r="G446" s="7" t="s">
+        <v>494</v>
+      </c>
+      <c r="H446" s="2"/>
+    </row>
+    <row r="447" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A447" s="7">
+        <v>1646</v>
+      </c>
+      <c r="B447" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="C447" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D447" s="7"/>
+      <c r="G447" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="H447" s="2"/>
+    </row>
+    <row r="448" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A448" s="7">
+        <v>1648</v>
+      </c>
+      <c r="B448" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="C448" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D448" s="7"/>
+      <c r="G448" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="H448" s="2"/>
+    </row>
+    <row r="449" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A449" s="7">
+        <v>1651</v>
+      </c>
+      <c r="B449" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="C449" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D449" s="7"/>
+      <c r="G449" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="H449" s="2"/>
+    </row>
+    <row r="450" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A450" s="7">
+        <v>1653</v>
+      </c>
+      <c r="B450" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="C450" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D450" s="7"/>
+      <c r="G450" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="H450" s="2"/>
+    </row>
+    <row r="451" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A451" s="7">
+        <v>1616</v>
+      </c>
+      <c r="B451" s="7" t="s">
+        <v>497</v>
+      </c>
+      <c r="C451" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D451" s="7"/>
+      <c r="G451" s="7" t="s">
+        <v>497</v>
+      </c>
+      <c r="H451" s="2"/>
+    </row>
+    <row r="452" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A452" s="7">
+        <v>1618</v>
+      </c>
+      <c r="B452" s="7" t="s">
+        <v>499</v>
+      </c>
+      <c r="C452" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D452" s="7"/>
+      <c r="G452" s="7" t="s">
+        <v>499</v>
+      </c>
+      <c r="H452" s="2"/>
+    </row>
+    <row r="453" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A453" s="7">
+        <v>1611</v>
+      </c>
+      <c r="B453" s="7" t="s">
+        <v>502</v>
+      </c>
+      <c r="C453" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D453" s="7"/>
+      <c r="G453" s="7" t="s">
+        <v>502</v>
+      </c>
+      <c r="H453" s="2"/>
+    </row>
+    <row r="454" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A454" s="7">
+        <v>1613</v>
+      </c>
+      <c r="B454" s="7" t="s">
+        <v>504</v>
+      </c>
+      <c r="C454" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D454" s="7"/>
+      <c r="G454" s="7" t="s">
+        <v>504</v>
+      </c>
+      <c r="H454" s="2"/>
+    </row>
+    <row r="455" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A455" s="7">
+        <v>1621</v>
+      </c>
+      <c r="B455" s="7" t="s">
+        <v>507</v>
+      </c>
+      <c r="C455" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D455" s="7"/>
+      <c r="G455" s="7" t="s">
+        <v>507</v>
+      </c>
+      <c r="H455" s="2"/>
+    </row>
+    <row r="456" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A456" s="7">
+        <v>1623</v>
+      </c>
+      <c r="B456" s="7" t="s">
+        <v>509</v>
+      </c>
+      <c r="C456" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D456" s="7"/>
+      <c r="G456" s="7" t="s">
+        <v>509</v>
+      </c>
+      <c r="H456" s="2"/>
+    </row>
+    <row r="457" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A457" s="7">
+        <v>1626</v>
+      </c>
+      <c r="B457" s="7" t="s">
+        <v>512</v>
+      </c>
+      <c r="C457" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D457" s="7"/>
+      <c r="G457" s="7" t="s">
+        <v>512</v>
+      </c>
+      <c r="H457" s="2"/>
+    </row>
+    <row r="458" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A458" s="7">
+        <v>1628</v>
+      </c>
+      <c r="B458" s="7" t="s">
+        <v>514</v>
+      </c>
+      <c r="C458" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D458" s="7"/>
+      <c r="G458" s="7" t="s">
+        <v>514</v>
+      </c>
+      <c r="H458" s="2"/>
+    </row>
+    <row r="459" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A459" s="7">
+        <v>418</v>
+      </c>
+      <c r="B459" s="7" t="s">
+        <v>512</v>
+      </c>
+      <c r="C459" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D459" s="7"/>
+      <c r="G459" s="7" t="s">
+        <v>512</v>
+      </c>
+      <c r="H459" s="2"/>
+    </row>
+    <row r="460" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A460" s="7">
+        <v>422</v>
+      </c>
+      <c r="B460" s="7" t="s">
+        <v>514</v>
+      </c>
+      <c r="C460" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D460" s="7"/>
+      <c r="G460" s="7" t="s">
+        <v>514</v>
+      </c>
+      <c r="H460" s="2"/>
+    </row>
+    <row r="461" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A461" s="7">
+        <v>1666</v>
+      </c>
+      <c r="B461" s="7" t="s">
+        <v>497</v>
+      </c>
+      <c r="C461" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D461" s="7"/>
+      <c r="G461" s="7" t="s">
+        <v>497</v>
+      </c>
+      <c r="H461" s="2"/>
+    </row>
+    <row r="462" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A462" s="7">
+        <v>1668</v>
+      </c>
+      <c r="B462" s="7" t="s">
+        <v>499</v>
+      </c>
+      <c r="C462" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D462" s="7"/>
+      <c r="G462" s="7" t="s">
+        <v>499</v>
+      </c>
+      <c r="H462" s="2"/>
+    </row>
+    <row r="463" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A463" s="7">
+        <v>1671</v>
+      </c>
+      <c r="B463" s="7" t="s">
+        <v>502</v>
+      </c>
+      <c r="C463" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D463" s="7"/>
+      <c r="G463" s="7" t="s">
+        <v>502</v>
+      </c>
+      <c r="H463" s="2"/>
+    </row>
+    <row r="464" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A464" s="7">
+        <v>1673</v>
+      </c>
+      <c r="B464" s="7" t="s">
+        <v>504</v>
+      </c>
+      <c r="C464" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D464" s="7"/>
+      <c r="G464" s="7" t="s">
+        <v>504</v>
+      </c>
+      <c r="H464" s="2"/>
+    </row>
+    <row r="465" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A465" s="7">
+        <v>1676</v>
+      </c>
+      <c r="B465" s="7" t="s">
+        <v>507</v>
+      </c>
+      <c r="C465" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D465" s="7"/>
+      <c r="G465" s="7" t="s">
+        <v>507</v>
+      </c>
+      <c r="H465" s="2"/>
+    </row>
+    <row r="466" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A466" s="7">
+        <v>1678</v>
+      </c>
+      <c r="B466" s="7" t="s">
+        <v>509</v>
+      </c>
+      <c r="C466" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D466" s="7"/>
+      <c r="G466" s="7" t="s">
+        <v>509</v>
+      </c>
+      <c r="H466" s="2"/>
+    </row>
+    <row r="467" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A467" s="7">
+        <v>1681</v>
+      </c>
+      <c r="B467" s="7" t="s">
+        <v>512</v>
+      </c>
+      <c r="C467" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D467" s="7"/>
+      <c r="G467" s="7" t="s">
+        <v>512</v>
+      </c>
+      <c r="H467" s="2"/>
+    </row>
+    <row r="468" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A468" s="7">
+        <v>1683</v>
+      </c>
+      <c r="B468" s="7" t="s">
+        <v>514</v>
+      </c>
+      <c r="C468" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D468" s="7"/>
+      <c r="G468" s="7" t="s">
+        <v>514</v>
+      </c>
+      <c r="H468" s="2"/>
+    </row>
+    <row r="469" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A469" s="7">
+        <v>2010</v>
+      </c>
+      <c r="B469" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="C469" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="D469" s="7"/>
+      <c r="G469" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="H469" s="2">
+        <v>20.49</v>
       </c>
     </row>
   </sheetData>
